--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340579</v>
+        <v>128339514</v>
       </c>
       <c r="B2" t="n">
         <v>56864</v>
@@ -704,9 +704,14 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574542</v>
+        <v>574577</v>
       </c>
       <c r="R2" t="n">
-        <v>7088660</v>
+        <v>7088748</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +753,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,60 +770,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340643</v>
+        <v>128338916</v>
       </c>
       <c r="B3" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574570</v>
+        <v>574622</v>
       </c>
       <c r="R3" t="n">
-        <v>7088645</v>
+        <v>7088618</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +855,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +877,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128339514</v>
+        <v>128340579</v>
       </c>
       <c r="B4" t="n">
         <v>56864</v>
@@ -928,14 +918,9 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574577</v>
+        <v>574542</v>
       </c>
       <c r="R4" t="n">
-        <v>7088748</v>
+        <v>7088660</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +962,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,65 +994,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338916</v>
+        <v>128340643</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574622</v>
+        <v>574570</v>
       </c>
       <c r="R5" t="n">
-        <v>7088618</v>
+        <v>7088645</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,14 +1074,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339216</v>
+        <v>128340568</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>78698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574620</v>
+        <v>574551</v>
       </c>
       <c r="R6" t="n">
-        <v>7088666</v>
+        <v>7088652</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,24 +1181,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340410</v>
+        <v>128339216</v>
       </c>
       <c r="B7" t="n">
-        <v>92661</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574543</v>
+        <v>574620</v>
       </c>
       <c r="R7" t="n">
-        <v>7088692</v>
+        <v>7088666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340568</v>
+        <v>128340410</v>
       </c>
       <c r="B8" t="n">
-        <v>78698</v>
+        <v>92661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574551</v>
+        <v>574543</v>
       </c>
       <c r="R8" t="n">
-        <v>7088652</v>
+        <v>7088692</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,9 +1395,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,12 +1422,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128339039</v>
+        <v>128340360</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,39 +2873,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574613</v>
+        <v>574548</v>
       </c>
       <c r="R23" t="n">
-        <v>7088652</v>
+        <v>7088705</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2932,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2947,12 +2942,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2967,19 +2957,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338853</v>
+        <v>128339039</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -3010,19 +3000,19 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574647</v>
+        <v>574613</v>
       </c>
       <c r="R24" t="n">
-        <v>7088580</v>
+        <v>7088652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,7 +3044,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3064,7 +3054,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3084,60 +3074,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128341564</v>
+        <v>128338853</v>
       </c>
       <c r="B25" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R25" t="n">
-        <v>7088593</v>
+        <v>7088580</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3164,9 +3159,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3181,44 +3191,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128340360</v>
+        <v>128341564</v>
       </c>
       <c r="B26" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,13 +3238,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574548</v>
+        <v>574445</v>
       </c>
       <c r="R26" t="n">
-        <v>7088705</v>
+        <v>7088593</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3261,19 +3271,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,62 +3288,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128339431</v>
+        <v>128340667</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574614</v>
+        <v>574565</v>
       </c>
       <c r="R27" t="n">
-        <v>7088709</v>
+        <v>7088619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3385,12 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3405,44 +3395,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339483</v>
+        <v>128339278</v>
       </c>
       <c r="B28" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3457,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574580</v>
+        <v>574615</v>
       </c>
       <c r="R28" t="n">
-        <v>7088751</v>
+        <v>7088675</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3490,9 +3480,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3507,19 +3512,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339278</v>
+        <v>128338795</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3555,14 +3560,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574615</v>
+        <v>574657</v>
       </c>
       <c r="R29" t="n">
-        <v>7088675</v>
+        <v>7088592</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3599,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,12 +3609,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,12 +3629,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3743,45 +3748,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128340667</v>
+        <v>128339431</v>
       </c>
       <c r="B31" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574565</v>
+        <v>574614</v>
       </c>
       <c r="R31" t="n">
-        <v>7088619</v>
+        <v>7088709</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3813,7 +3823,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3823,7 +3833,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3838,44 +3853,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338795</v>
+        <v>128339483</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,17 +3901,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574657</v>
+        <v>574580</v>
       </c>
       <c r="R32" t="n">
-        <v>7088592</v>
+        <v>7088751</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3923,24 +3938,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,12 +3955,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339234</v>
+        <v>128340784</v>
       </c>
       <c r="B36" t="n">
-        <v>80038</v>
+        <v>92673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574647</v>
+        <v>574541</v>
       </c>
       <c r="R36" t="n">
-        <v>7088700</v>
+        <v>7088525</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4390,32 +4390,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128340784</v>
+        <v>128339234</v>
       </c>
       <c r="B37" t="n">
-        <v>92673</v>
+        <v>80038</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574541</v>
+        <v>574647</v>
       </c>
       <c r="R37" t="n">
-        <v>7088525</v>
+        <v>7088700</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5741,50 +5741,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128339103</v>
+        <v>128341543</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>80170</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R50" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5817,11 +5812,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5848,7 +5838,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128339352</v>
+        <v>128339103</v>
       </c>
       <c r="B51" t="n">
         <v>57672</v>
@@ -5888,13 +5878,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574614</v>
+        <v>574625</v>
       </c>
       <c r="R51" t="n">
-        <v>7088680</v>
+        <v>7088640</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5921,24 +5911,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5953,12 +5933,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6179,10 +6159,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341658</v>
+        <v>128339352</v>
       </c>
       <c r="B54" t="n">
-        <v>78698</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6190,37 +6170,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574614</v>
       </c>
       <c r="R54" t="n">
-        <v>7088595</v>
+        <v>7088680</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6247,9 +6232,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6264,44 +6264,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341543</v>
+        <v>128341658</v>
       </c>
       <c r="B55" t="n">
-        <v>80170</v>
+        <v>78698</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6314,7 +6314,7 @@
         <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088593</v>
+        <v>7088595</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340933</v>
+        <v>128340363</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,42 +7872,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574498</v>
+        <v>574523</v>
       </c>
       <c r="R70" t="n">
-        <v>7088556</v>
+        <v>7088723</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7934,24 +7929,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7966,65 +7946,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128341109</v>
+        <v>128339554</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>80162</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574429</v>
+        <v>574560</v>
       </c>
       <c r="R71" t="n">
-        <v>7088591</v>
+        <v>7088771</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8051,24 +8026,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8083,22 +8043,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340639</v>
+        <v>128340344</v>
       </c>
       <c r="B72" t="n">
-        <v>78790</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8106,34 +8066,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574574</v>
+        <v>574557</v>
       </c>
       <c r="R72" t="n">
-        <v>7088635</v>
+        <v>7088695</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8165,7 +8130,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8175,7 +8140,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8190,22 +8160,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340670</v>
+        <v>128340563</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>92838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8213,39 +8183,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574568</v>
+        <v>574549</v>
       </c>
       <c r="R73" t="n">
-        <v>7088607</v>
+        <v>7088658</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8277,7 +8242,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8287,12 +8252,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8307,22 +8267,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340363</v>
+        <v>128340933</v>
       </c>
       <c r="B74" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8330,37 +8290,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574523</v>
+        <v>574498</v>
       </c>
       <c r="R74" t="n">
-        <v>7088723</v>
+        <v>7088556</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8387,9 +8352,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8404,22 +8384,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128340563</v>
+        <v>128341109</v>
       </c>
       <c r="B75" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8427,34 +8407,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574549</v>
+        <v>574429</v>
       </c>
       <c r="R75" t="n">
-        <v>7088658</v>
+        <v>7088591</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8486,7 +8471,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8496,7 +8481,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8511,44 +8501,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128339554</v>
+        <v>128340639</v>
       </c>
       <c r="B76" t="n">
-        <v>80162</v>
+        <v>78790</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8558,13 +8548,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574560</v>
+        <v>574574</v>
       </c>
       <c r="R76" t="n">
-        <v>7088771</v>
+        <v>7088635</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8591,9 +8581,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8608,19 +8608,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128340344</v>
+        <v>128340670</v>
       </c>
       <c r="B77" t="n">
         <v>57672</v>
@@ -8651,7 +8651,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574557</v>
+        <v>574568</v>
       </c>
       <c r="R77" t="n">
-        <v>7088695</v>
+        <v>7088607</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340568</v>
+        <v>128339216</v>
       </c>
       <c r="B6" t="n">
-        <v>78698</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1124,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574551</v>
+        <v>574620</v>
       </c>
       <c r="R6" t="n">
-        <v>7088652</v>
+        <v>7088666</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,9 +1186,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339216</v>
+        <v>128340410</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>92661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574620</v>
+        <v>574543</v>
       </c>
       <c r="R7" t="n">
-        <v>7088666</v>
+        <v>7088692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340410</v>
+        <v>128340568</v>
       </c>
       <c r="B8" t="n">
-        <v>92661</v>
+        <v>78698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574543</v>
+        <v>574551</v>
       </c>
       <c r="R8" t="n">
-        <v>7088692</v>
+        <v>7088652</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,19 +1405,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,12 +1422,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B10" t="n">
-        <v>80134</v>
+        <v>78698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R10" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B11" t="n">
-        <v>78698</v>
+        <v>80134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R11" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2163,48 +2163,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B16" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R16" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,19 +2231,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,60 +2248,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B17" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2328,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128340667</v>
+        <v>128340549</v>
       </c>
       <c r="B27" t="n">
-        <v>92645</v>
+        <v>90390</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574565</v>
+        <v>574555</v>
       </c>
       <c r="R27" t="n">
-        <v>7088619</v>
+        <v>7088647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339278</v>
+        <v>128339431</v>
       </c>
       <c r="B28" t="n">
         <v>57672</v>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574615</v>
+        <v>574614</v>
       </c>
       <c r="R28" t="n">
-        <v>7088675</v>
+        <v>7088709</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3524,32 +3524,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128338795</v>
+        <v>128339483</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3560,17 +3560,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574657</v>
+        <v>574580</v>
       </c>
       <c r="R29" t="n">
-        <v>7088592</v>
+        <v>7088751</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3597,24 +3597,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3629,44 +3614,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128340549</v>
+        <v>128340667</v>
       </c>
       <c r="B30" t="n">
-        <v>90390</v>
+        <v>92645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574555</v>
+        <v>574565</v>
       </c>
       <c r="R30" t="n">
-        <v>7088647</v>
+        <v>7088619</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3711,7 +3696,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3706,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3733,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339431</v>
+        <v>128339278</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3788,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574614</v>
+        <v>574615</v>
       </c>
       <c r="R31" t="n">
-        <v>7088709</v>
+        <v>7088675</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,7 +3808,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3833,7 +3818,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3865,32 +3850,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128339483</v>
+        <v>128338795</v>
       </c>
       <c r="B32" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3901,17 +3886,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574580</v>
+        <v>574657</v>
       </c>
       <c r="R32" t="n">
-        <v>7088751</v>
+        <v>7088592</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3938,9 +3923,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,12 +3955,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128340692</v>
+        <v>128339243</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,39 +4702,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574557</v>
+        <v>574646</v>
       </c>
       <c r="R40" t="n">
-        <v>7088560</v>
+        <v>7088700</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4767,11 +4762,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4798,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128339243</v>
+        <v>128340692</v>
       </c>
       <c r="B41" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,34 +4799,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574646</v>
+        <v>574557</v>
       </c>
       <c r="R41" t="n">
-        <v>7088700</v>
+        <v>7088560</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4869,6 +4864,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5741,45 +5741,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128341543</v>
+        <v>128339103</v>
       </c>
       <c r="B50" t="n">
-        <v>80170</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574445</v>
+        <v>574625</v>
       </c>
       <c r="R50" t="n">
-        <v>7088593</v>
+        <v>7088640</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5812,6 +5817,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5838,7 +5848,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128339103</v>
+        <v>128339352</v>
       </c>
       <c r="B51" t="n">
         <v>57672</v>
@@ -5878,13 +5888,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574625</v>
+        <v>574614</v>
       </c>
       <c r="R51" t="n">
-        <v>7088640</v>
+        <v>7088680</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5911,14 +5921,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre och färska spår</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5933,12 +5953,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6159,10 +6179,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339352</v>
+        <v>128341658</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>78698</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6170,42 +6190,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574614</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088680</v>
+        <v>7088595</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6232,24 +6247,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6264,44 +6264,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B55" t="n">
-        <v>78698</v>
+        <v>80170</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6314,7 +6314,7 @@
         <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6373,32 +6373,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128341588</v>
+        <v>128339188</v>
       </c>
       <c r="B56" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R56" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,9 +6441,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6458,22 +6468,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339188</v>
+        <v>128339538</v>
       </c>
       <c r="B57" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6481,34 +6491,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574647</v>
+        <v>574598</v>
       </c>
       <c r="R57" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6540,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6550,7 +6565,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6565,65 +6585,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339538</v>
+        <v>128339624</v>
       </c>
       <c r="B58" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574598</v>
+        <v>574580</v>
       </c>
       <c r="R58" t="n">
-        <v>7088728</v>
+        <v>7088767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6650,24 +6665,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6682,19 +6682,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339624</v>
+        <v>128339929</v>
       </c>
       <c r="B59" t="n">
         <v>92645</v>
@@ -6729,13 +6729,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574580</v>
+        <v>574555</v>
       </c>
       <c r="R59" t="n">
-        <v>7088767</v>
+        <v>7088696</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6762,9 +6762,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6779,19 +6789,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339929</v>
+        <v>128341588</v>
       </c>
       <c r="B60" t="n">
         <v>92645</v>
@@ -6826,13 +6836,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574555</v>
+        <v>574445</v>
       </c>
       <c r="R60" t="n">
-        <v>7088696</v>
+        <v>7088594</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6859,19 +6869,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,12 +6886,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7958,32 +7958,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128339554</v>
+        <v>128340563</v>
       </c>
       <c r="B71" t="n">
-        <v>80162</v>
+        <v>92838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,13 +7993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574560</v>
+        <v>574549</v>
       </c>
       <c r="R71" t="n">
-        <v>7088771</v>
+        <v>7088658</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8026,9 +8026,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8043,65 +8053,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340344</v>
+        <v>128339554</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>80162</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574557</v>
+        <v>574560</v>
       </c>
       <c r="R72" t="n">
-        <v>7088695</v>
+        <v>7088771</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8128,24 +8133,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8160,22 +8150,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340563</v>
+        <v>128340344</v>
       </c>
       <c r="B73" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8183,34 +8173,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574549</v>
+        <v>574557</v>
       </c>
       <c r="R73" t="n">
-        <v>7088658</v>
+        <v>7088695</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8242,7 +8237,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8252,7 +8247,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8267,12 +8267,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128339514</v>
+        <v>128340579</v>
       </c>
       <c r="B2" t="n">
         <v>56864</v>
@@ -704,14 +704,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574577</v>
+        <v>574542</v>
       </c>
       <c r="R2" t="n">
-        <v>7088748</v>
+        <v>7088660</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +748,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,50 +780,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338916</v>
+        <v>128339514</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574622</v>
+        <v>574577</v>
       </c>
       <c r="R3" t="n">
-        <v>7088618</v>
+        <v>7088748</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +873,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340579</v>
+        <v>128338916</v>
       </c>
       <c r="B4" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574542</v>
+        <v>574622</v>
       </c>
       <c r="R4" t="n">
-        <v>7088660</v>
+        <v>7088618</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,24 +972,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2862,32 +2862,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128340360</v>
+        <v>128341564</v>
       </c>
       <c r="B23" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574548</v>
+        <v>574445</v>
       </c>
       <c r="R23" t="n">
-        <v>7088705</v>
+        <v>7088593</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,19 +2930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,12 +2947,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3203,32 +3193,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128341564</v>
+        <v>128340360</v>
       </c>
       <c r="B26" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,13 +3228,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574445</v>
+        <v>574548</v>
       </c>
       <c r="R26" t="n">
-        <v>7088593</v>
+        <v>7088705</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3271,9 +3261,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,12 +3288,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -5741,53 +5741,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128339103</v>
+        <v>128340512</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574625</v>
+        <v>574550</v>
       </c>
       <c r="R50" t="n">
-        <v>7088640</v>
+        <v>7088660</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5814,14 +5809,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,22 +5836,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128339352</v>
+        <v>128340602</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>92670</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5859,39 +5859,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574614</v>
+        <v>574553</v>
       </c>
       <c r="R51" t="n">
-        <v>7088680</v>
+        <v>7088642</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5923,7 +5918,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5933,12 +5928,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5953,44 +5943,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128340512</v>
+        <v>128341658</v>
       </c>
       <c r="B52" t="n">
-        <v>92645</v>
+        <v>78698</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6000,13 +5990,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R52" t="n">
-        <v>7088660</v>
+        <v>7088595</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6033,19 +6023,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6060,44 +6040,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128340602</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>92670</v>
+        <v>80170</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6107,13 +6087,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088642</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6140,19 +6120,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6167,22 +6137,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341658</v>
+        <v>128339103</v>
       </c>
       <c r="B54" t="n">
-        <v>78698</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6190,34 +6160,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574625</v>
       </c>
       <c r="R54" t="n">
-        <v>7088595</v>
+        <v>7088640</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6250,6 +6225,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6276,48 +6256,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341543</v>
+        <v>128339352</v>
       </c>
       <c r="B55" t="n">
-        <v>80170</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574614</v>
       </c>
       <c r="R55" t="n">
-        <v>7088593</v>
+        <v>7088680</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6344,9 +6329,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,12 +6361,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128343065</v>
+        <v>128340020</v>
       </c>
       <c r="B63" t="n">
-        <v>79031</v>
+        <v>78698</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574485</v>
+        <v>574526</v>
       </c>
       <c r="R63" t="n">
-        <v>7088660</v>
+        <v>7088741</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128340645</v>
+        <v>128339617</v>
       </c>
       <c r="B64" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,34 +7220,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574571</v>
+        <v>574563</v>
       </c>
       <c r="R64" t="n">
-        <v>7088636</v>
+        <v>7088745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7279,7 +7284,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7289,7 +7294,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7304,22 +7314,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128340020</v>
+        <v>128340645</v>
       </c>
       <c r="B65" t="n">
-        <v>78698</v>
+        <v>78789</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7327,21 +7337,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7351,13 +7361,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574526</v>
+        <v>574571</v>
       </c>
       <c r="R65" t="n">
-        <v>7088741</v>
+        <v>7088636</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7384,9 +7394,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7401,22 +7421,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128339617</v>
+        <v>128343065</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7424,42 +7444,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574563</v>
+        <v>574485</v>
       </c>
       <c r="R66" t="n">
-        <v>7088745</v>
+        <v>7088660</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7486,24 +7501,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7958,32 +7958,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340563</v>
+        <v>128339554</v>
       </c>
       <c r="B71" t="n">
-        <v>92838</v>
+        <v>80162</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,13 +7993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574549</v>
+        <v>574560</v>
       </c>
       <c r="R71" t="n">
-        <v>7088658</v>
+        <v>7088771</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8026,19 +8026,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8053,60 +8043,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128339554</v>
+        <v>128340344</v>
       </c>
       <c r="B72" t="n">
-        <v>80162</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574560</v>
+        <v>574557</v>
       </c>
       <c r="R72" t="n">
-        <v>7088771</v>
+        <v>7088695</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8133,9 +8128,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8150,22 +8160,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340344</v>
+        <v>128340563</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>92838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8173,39 +8183,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574557</v>
+        <v>574549</v>
       </c>
       <c r="R73" t="n">
-        <v>7088695</v>
+        <v>7088658</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8237,7 +8242,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8247,12 +8252,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8267,12 +8267,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339216</v>
+        <v>128340568</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>78698</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574620</v>
+        <v>574551</v>
       </c>
       <c r="R6" t="n">
-        <v>7088666</v>
+        <v>7088652</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,24 +1181,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,12 +1198,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1337,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340568</v>
+        <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>78698</v>
+        <v>92645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574551</v>
+        <v>574438</v>
       </c>
       <c r="R8" t="n">
-        <v>7088652</v>
+        <v>7088595</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,9 +1385,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,57 +1412,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341140</v>
+        <v>128339216</v>
       </c>
       <c r="B9" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574438</v>
+        <v>574620</v>
       </c>
       <c r="R9" t="n">
-        <v>7088595</v>
+        <v>7088666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B10" t="n">
-        <v>78698</v>
+        <v>80134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R10" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B11" t="n">
-        <v>80134</v>
+        <v>78698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R11" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2163,48 +2163,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R16" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2231,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,60 +2258,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,19 +2338,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340512</v>
+        <v>128341543</v>
       </c>
       <c r="B50" t="n">
-        <v>92645</v>
+        <v>80170</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R50" t="n">
-        <v>7088660</v>
+        <v>7088593</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,19 +5809,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,22 +5826,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340602</v>
+        <v>128339103</v>
       </c>
       <c r="B51" t="n">
-        <v>92670</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5859,37 +5849,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574553</v>
+        <v>574625</v>
       </c>
       <c r="R51" t="n">
-        <v>7088642</v>
+        <v>7088640</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5916,19 +5911,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:19</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5943,44 +5933,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128341658</v>
+        <v>128340512</v>
       </c>
       <c r="B52" t="n">
-        <v>78698</v>
+        <v>92645</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5990,13 +5980,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R52" t="n">
-        <v>7088595</v>
+        <v>7088660</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6023,9 +6013,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6040,44 +6040,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128340602</v>
       </c>
       <c r="B53" t="n">
-        <v>80170</v>
+        <v>92670</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574553</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088642</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6120,9 +6120,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6137,19 +6147,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339103</v>
+        <v>128339352</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6189,13 +6199,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574625</v>
+        <v>574614</v>
       </c>
       <c r="R54" t="n">
-        <v>7088640</v>
+        <v>7088680</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6222,14 +6232,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre och färska spår</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6244,22 +6264,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128339352</v>
+        <v>128341658</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>78698</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6267,42 +6287,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574614</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088680</v>
+        <v>7088595</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6329,24 +6344,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,44 +6361,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339188</v>
+        <v>128341588</v>
       </c>
       <c r="B56" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574647</v>
+        <v>574445</v>
       </c>
       <c r="R56" t="n">
-        <v>7088696</v>
+        <v>7088594</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,19 +6441,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6468,62 +6458,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339538</v>
+        <v>128339929</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574598</v>
+        <v>574555</v>
       </c>
       <c r="R57" t="n">
-        <v>7088728</v>
+        <v>7088696</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6555,7 +6540,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6565,12 +6550,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,32 +6674,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339929</v>
+        <v>128339188</v>
       </c>
       <c r="B59" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6729,7 +6709,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574555</v>
+        <v>574647</v>
       </c>
       <c r="R59" t="n">
         <v>7088696</v>
@@ -6764,7 +6744,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6774,7 +6754,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6789,60 +6769,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128341588</v>
+        <v>128339538</v>
       </c>
       <c r="B60" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574445</v>
+        <v>574598</v>
       </c>
       <c r="R60" t="n">
-        <v>7088594</v>
+        <v>7088728</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6869,9 +6854,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,12 +6886,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128340020</v>
+        <v>128343065</v>
       </c>
       <c r="B63" t="n">
-        <v>78698</v>
+        <v>79031</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574526</v>
+        <v>574485</v>
       </c>
       <c r="R63" t="n">
-        <v>7088741</v>
+        <v>7088660</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128339617</v>
+        <v>128340645</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,39 +7220,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574563</v>
+        <v>574571</v>
       </c>
       <c r="R64" t="n">
-        <v>7088745</v>
+        <v>7088636</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7284,7 +7279,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7294,12 +7289,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7314,22 +7304,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128340645</v>
+        <v>128340020</v>
       </c>
       <c r="B65" t="n">
-        <v>78789</v>
+        <v>78698</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7337,21 +7327,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7361,13 +7351,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574571</v>
+        <v>574526</v>
       </c>
       <c r="R65" t="n">
-        <v>7088636</v>
+        <v>7088741</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7394,19 +7384,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7421,22 +7401,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128343065</v>
+        <v>128339617</v>
       </c>
       <c r="B66" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,37 +7424,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574485</v>
+        <v>574563</v>
       </c>
       <c r="R66" t="n">
-        <v>7088660</v>
+        <v>7088745</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7501,9 +7486,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7958,32 +7958,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128339554</v>
+        <v>128340563</v>
       </c>
       <c r="B71" t="n">
-        <v>80162</v>
+        <v>92838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,13 +7993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574560</v>
+        <v>574549</v>
       </c>
       <c r="R71" t="n">
-        <v>7088771</v>
+        <v>7088658</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8026,9 +8026,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8043,65 +8053,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340344</v>
+        <v>128339554</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>80162</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574557</v>
+        <v>574560</v>
       </c>
       <c r="R72" t="n">
-        <v>7088695</v>
+        <v>7088771</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8128,24 +8133,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8160,22 +8150,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340563</v>
+        <v>128340344</v>
       </c>
       <c r="B73" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8183,34 +8173,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574549</v>
+        <v>574557</v>
       </c>
       <c r="R73" t="n">
-        <v>7088658</v>
+        <v>7088695</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8242,7 +8237,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8252,7 +8247,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8267,12 +8267,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339514</v>
+        <v>128340643</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>92645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,47 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574577</v>
+        <v>574570</v>
       </c>
       <c r="R3" t="n">
-        <v>7088748</v>
+        <v>7088645</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,9 +860,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,50 +887,55 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338916</v>
+        <v>128339514</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574622</v>
+        <v>574577</v>
       </c>
       <c r="R4" t="n">
-        <v>7088618</v>
+        <v>7088748</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -975,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,48 +1006,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340643</v>
+        <v>128338916</v>
       </c>
       <c r="B5" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574570</v>
+        <v>574622</v>
       </c>
       <c r="R5" t="n">
-        <v>7088645</v>
+        <v>7088618</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1079,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B10" t="n">
-        <v>80134</v>
+        <v>78698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R10" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B11" t="n">
-        <v>78698</v>
+        <v>80134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R11" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2163,48 +2163,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B16" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R16" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,19 +2231,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,60 +2248,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B17" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2328,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2474,32 +2474,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343851</v>
+        <v>128340725</v>
       </c>
       <c r="B19" t="n">
-        <v>92639</v>
+        <v>80163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574522</v>
+        <v>574548</v>
       </c>
       <c r="R19" t="n">
-        <v>7088573</v>
+        <v>7088558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128340725</v>
+        <v>128340679</v>
       </c>
       <c r="B20" t="n">
-        <v>80163</v>
+        <v>92645</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574548</v>
+        <v>574565</v>
       </c>
       <c r="R20" t="n">
-        <v>7088558</v>
+        <v>7088589</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,32 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128340679</v>
+        <v>128343851</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574565</v>
+        <v>574522</v>
       </c>
       <c r="R21" t="n">
-        <v>7088589</v>
+        <v>7088573</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -4992,10 +4992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128339678</v>
+        <v>128339546</v>
       </c>
       <c r="B43" t="n">
-        <v>56864</v>
+        <v>92645</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5003,39 +5003,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574545</v>
+        <v>574558</v>
       </c>
       <c r="R43" t="n">
-        <v>7088725</v>
+        <v>7088774</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5068,11 +5063,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5099,32 +5089,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128339546</v>
+        <v>128340722</v>
       </c>
       <c r="B44" t="n">
-        <v>92645</v>
+        <v>80134</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5134,13 +5124,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574558</v>
+        <v>574563</v>
       </c>
       <c r="R44" t="n">
-        <v>7088774</v>
+        <v>7088549</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5167,9 +5157,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5184,22 +5184,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128339432</v>
+        <v>128340649</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79649</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5207,39 +5207,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574618</v>
+        <v>574573</v>
       </c>
       <c r="R45" t="n">
-        <v>7088746</v>
+        <v>7088640</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,7 +5266,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,12 +5276,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5313,10 +5303,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128340722</v>
+        <v>128339432</v>
       </c>
       <c r="B46" t="n">
-        <v>80134</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5324,34 +5314,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574563</v>
+        <v>574618</v>
       </c>
       <c r="R46" t="n">
-        <v>7088549</v>
+        <v>7088746</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5383,7 +5378,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5393,7 +5388,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5420,48 +5420,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128340649</v>
+        <v>128339678</v>
       </c>
       <c r="B47" t="n">
-        <v>79649</v>
+        <v>56864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574573</v>
+        <v>574545</v>
       </c>
       <c r="R47" t="n">
-        <v>7088640</v>
+        <v>7088725</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5488,19 +5493,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:23</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5515,12 +5515,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B50" t="n">
-        <v>80170</v>
+        <v>92645</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R50" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,9 +5809,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5826,22 +5836,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128339103</v>
+        <v>128340602</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>92670</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5849,42 +5859,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574625</v>
+        <v>574553</v>
       </c>
       <c r="R51" t="n">
-        <v>7088640</v>
+        <v>7088642</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5911,14 +5916,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5933,44 +5943,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128340512</v>
+        <v>128341658</v>
       </c>
       <c r="B52" t="n">
-        <v>92645</v>
+        <v>78698</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5980,13 +5990,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R52" t="n">
-        <v>7088660</v>
+        <v>7088595</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6013,19 +6023,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6040,44 +6040,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128340602</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>92670</v>
+        <v>80170</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088642</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6120,19 +6120,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6147,19 +6137,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339352</v>
+        <v>128339103</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6199,13 +6189,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574614</v>
+        <v>574625</v>
       </c>
       <c r="R54" t="n">
-        <v>7088680</v>
+        <v>7088640</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6232,24 +6222,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6264,22 +6244,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341658</v>
+        <v>128339352</v>
       </c>
       <c r="B55" t="n">
-        <v>78698</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6287,37 +6267,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574614</v>
       </c>
       <c r="R55" t="n">
-        <v>7088595</v>
+        <v>7088680</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6344,9 +6329,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,44 +6361,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128341588</v>
+        <v>128339188</v>
       </c>
       <c r="B56" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R56" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,9 +6441,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6458,57 +6468,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339929</v>
+        <v>128339538</v>
       </c>
       <c r="B57" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574555</v>
+        <v>574598</v>
       </c>
       <c r="R57" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6540,7 +6555,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6550,7 +6565,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,32 +6694,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339188</v>
+        <v>128339929</v>
       </c>
       <c r="B59" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6709,7 +6729,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574647</v>
+        <v>574555</v>
       </c>
       <c r="R59" t="n">
         <v>7088696</v>
@@ -6744,7 +6764,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6754,7 +6774,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6769,65 +6789,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339538</v>
+        <v>128341588</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574598</v>
+        <v>574445</v>
       </c>
       <c r="R60" t="n">
-        <v>7088728</v>
+        <v>7088594</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6854,24 +6869,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,12 +6886,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128343065</v>
+        <v>128340020</v>
       </c>
       <c r="B63" t="n">
-        <v>79031</v>
+        <v>78698</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574485</v>
+        <v>574526</v>
       </c>
       <c r="R63" t="n">
-        <v>7088660</v>
+        <v>7088741</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128340645</v>
+        <v>128339617</v>
       </c>
       <c r="B64" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,34 +7220,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574571</v>
+        <v>574563</v>
       </c>
       <c r="R64" t="n">
-        <v>7088636</v>
+        <v>7088745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7279,7 +7284,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7289,7 +7294,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7304,22 +7314,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128340020</v>
+        <v>128340645</v>
       </c>
       <c r="B65" t="n">
-        <v>78698</v>
+        <v>78789</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7327,21 +7337,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7351,13 +7361,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574526</v>
+        <v>574571</v>
       </c>
       <c r="R65" t="n">
-        <v>7088741</v>
+        <v>7088636</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7384,9 +7394,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7401,22 +7421,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128339617</v>
+        <v>128343065</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7424,42 +7444,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574563</v>
+        <v>574485</v>
       </c>
       <c r="R66" t="n">
-        <v>7088745</v>
+        <v>7088660</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7486,24 +7501,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7958,32 +7958,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340563</v>
+        <v>128339554</v>
       </c>
       <c r="B71" t="n">
-        <v>92838</v>
+        <v>80162</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,13 +7993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574549</v>
+        <v>574560</v>
       </c>
       <c r="R71" t="n">
-        <v>7088658</v>
+        <v>7088771</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8026,19 +8026,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8053,60 +8043,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128339554</v>
+        <v>128340344</v>
       </c>
       <c r="B72" t="n">
-        <v>80162</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574560</v>
+        <v>574557</v>
       </c>
       <c r="R72" t="n">
-        <v>7088771</v>
+        <v>7088695</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8133,9 +8128,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8150,22 +8160,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340344</v>
+        <v>128340563</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>92838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8173,39 +8183,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574557</v>
+        <v>574549</v>
       </c>
       <c r="R73" t="n">
-        <v>7088695</v>
+        <v>7088658</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8237,7 +8242,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8247,12 +8252,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8267,12 +8267,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340643</v>
+        <v>128339514</v>
       </c>
       <c r="B3" t="n">
-        <v>92645</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +803,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574570</v>
+        <v>574577</v>
       </c>
       <c r="R3" t="n">
-        <v>7088645</v>
+        <v>7088748</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +870,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,55 +887,50 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128339514</v>
+        <v>128338916</v>
       </c>
       <c r="B4" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574577</v>
+        <v>574622</v>
       </c>
       <c r="R4" t="n">
-        <v>7088748</v>
+        <v>7088618</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,53 +1006,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338916</v>
+        <v>128340643</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574622</v>
+        <v>574570</v>
       </c>
       <c r="R5" t="n">
-        <v>7088618</v>
+        <v>7088645</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,14 +1074,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340568</v>
+        <v>128339216</v>
       </c>
       <c r="B6" t="n">
-        <v>78698</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1124,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574551</v>
+        <v>574620</v>
       </c>
       <c r="R6" t="n">
-        <v>7088652</v>
+        <v>7088666</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,9 +1186,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,12 +1218,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1317,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341140</v>
+        <v>128340568</v>
       </c>
       <c r="B8" t="n">
-        <v>92645</v>
+        <v>78698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574438</v>
+        <v>574551</v>
       </c>
       <c r="R8" t="n">
-        <v>7088595</v>
+        <v>7088652</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,19 +1405,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,62 +1422,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128339216</v>
+        <v>128341140</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574620</v>
+        <v>574438</v>
       </c>
       <c r="R9" t="n">
-        <v>7088666</v>
+        <v>7088595</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2163,48 +2163,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>79031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R16" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2231,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,60 +2258,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,19 +2338,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2474,32 +2474,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340725</v>
+        <v>128343851</v>
       </c>
       <c r="B19" t="n">
-        <v>80163</v>
+        <v>92639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574548</v>
+        <v>574522</v>
       </c>
       <c r="R19" t="n">
-        <v>7088558</v>
+        <v>7088573</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128340679</v>
+        <v>128340725</v>
       </c>
       <c r="B20" t="n">
-        <v>92645</v>
+        <v>80163</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574565</v>
+        <v>574548</v>
       </c>
       <c r="R20" t="n">
-        <v>7088589</v>
+        <v>7088558</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,32 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343851</v>
+        <v>128340679</v>
       </c>
       <c r="B21" t="n">
-        <v>92639</v>
+        <v>92645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574522</v>
+        <v>574565</v>
       </c>
       <c r="R21" t="n">
-        <v>7088573</v>
+        <v>7088589</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2862,48 +2862,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128341564</v>
+        <v>128339039</v>
       </c>
       <c r="B23" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574445</v>
+        <v>574613</v>
       </c>
       <c r="R23" t="n">
-        <v>7088593</v>
+        <v>7088652</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,9 +2935,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,19 +2967,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128339039</v>
+        <v>128338853</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -2990,19 +3010,19 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574613</v>
+        <v>574647</v>
       </c>
       <c r="R24" t="n">
-        <v>7088652</v>
+        <v>7088580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,7 +3054,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3064,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3064,22 +3084,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338853</v>
+        <v>128340360</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3087,39 +3107,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574647</v>
+        <v>574548</v>
       </c>
       <c r="R25" t="n">
-        <v>7088580</v>
+        <v>7088705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3151,7 +3166,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3161,12 +3176,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3193,32 +3203,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128340360</v>
+        <v>128341564</v>
       </c>
       <c r="B26" t="n">
-        <v>79031</v>
+        <v>92645</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,13 +3238,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574548</v>
+        <v>574445</v>
       </c>
       <c r="R26" t="n">
-        <v>7088705</v>
+        <v>7088593</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3261,19 +3271,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,22 +3288,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128340549</v>
+        <v>128338795</v>
       </c>
       <c r="B27" t="n">
-        <v>90390</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,34 +3311,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574555</v>
+        <v>574657</v>
       </c>
       <c r="R27" t="n">
-        <v>7088647</v>
+        <v>7088592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3375,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3385,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339431</v>
+        <v>128340549</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>90390</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3418,39 +3428,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574614</v>
+        <v>574555</v>
       </c>
       <c r="R28" t="n">
-        <v>7088709</v>
+        <v>7088647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,7 +3487,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,12 +3497,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3512,22 +3512,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339483</v>
+        <v>128340667</v>
       </c>
       <c r="B29" t="n">
-        <v>56864</v>
+        <v>92645</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,42 +3535,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574580</v>
+        <v>574565</v>
       </c>
       <c r="R29" t="n">
-        <v>7088751</v>
+        <v>7088619</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3597,9 +3592,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3614,57 +3619,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128340667</v>
+        <v>128339431</v>
       </c>
       <c r="B30" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574565</v>
+        <v>574614</v>
       </c>
       <c r="R30" t="n">
-        <v>7088619</v>
+        <v>7088709</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3696,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3706,7 +3716,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,44 +3736,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339278</v>
+        <v>128339483</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3773,13 +3788,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574615</v>
+        <v>574580</v>
       </c>
       <c r="R31" t="n">
-        <v>7088675</v>
+        <v>7088751</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3806,24 +3821,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3838,19 +3838,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338795</v>
+        <v>128339278</v>
       </c>
       <c r="B32" t="n">
         <v>57672</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574657</v>
+        <v>574615</v>
       </c>
       <c r="R32" t="n">
-        <v>7088592</v>
+        <v>7088675</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,12 +3955,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128340692</v>
+        <v>128340357</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>79649</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,39 +4799,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574557</v>
+        <v>574526</v>
       </c>
       <c r="R41" t="n">
-        <v>7088560</v>
+        <v>7088741</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4864,11 +4859,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340357</v>
+        <v>128340692</v>
       </c>
       <c r="B42" t="n">
-        <v>79649</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,34 +4896,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574526</v>
+        <v>574557</v>
       </c>
       <c r="R42" t="n">
-        <v>7088741</v>
+        <v>7088560</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4966,6 +4961,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5741,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340512</v>
+        <v>128341543</v>
       </c>
       <c r="B50" t="n">
-        <v>92645</v>
+        <v>80170</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R50" t="n">
-        <v>7088660</v>
+        <v>7088593</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,19 +5809,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,22 +5826,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340602</v>
+        <v>128341658</v>
       </c>
       <c r="B51" t="n">
-        <v>92670</v>
+        <v>78698</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5859,21 +5849,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5883,13 +5873,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R51" t="n">
-        <v>7088642</v>
+        <v>7088595</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5916,19 +5906,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5943,22 +5923,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128341658</v>
+        <v>128339103</v>
       </c>
       <c r="B52" t="n">
-        <v>78698</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,34 +5946,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574445</v>
+        <v>574625</v>
       </c>
       <c r="R52" t="n">
-        <v>7088595</v>
+        <v>7088640</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6026,6 +6011,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,10 +6042,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B53" t="n">
-        <v>80170</v>
+        <v>92645</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,21 +6053,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6087,13 +6077,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6120,9 +6110,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6137,22 +6137,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339103</v>
+        <v>128340602</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>92670</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6160,42 +6160,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574625</v>
+        <v>574553</v>
       </c>
       <c r="R54" t="n">
-        <v>7088640</v>
+        <v>7088642</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6222,14 +6217,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6244,12 +6244,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128340020</v>
+        <v>128343065</v>
       </c>
       <c r="B63" t="n">
-        <v>78698</v>
+        <v>79031</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574526</v>
+        <v>574485</v>
       </c>
       <c r="R63" t="n">
-        <v>7088741</v>
+        <v>7088660</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128339617</v>
+        <v>128340645</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,39 +7220,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574563</v>
+        <v>574571</v>
       </c>
       <c r="R64" t="n">
-        <v>7088745</v>
+        <v>7088636</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7284,7 +7279,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7294,12 +7289,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7314,22 +7304,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128340645</v>
+        <v>128340020</v>
       </c>
       <c r="B65" t="n">
-        <v>78789</v>
+        <v>78698</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7337,21 +7327,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7361,13 +7351,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574571</v>
+        <v>574526</v>
       </c>
       <c r="R65" t="n">
-        <v>7088636</v>
+        <v>7088741</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7394,19 +7384,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7421,22 +7401,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128343065</v>
+        <v>128339617</v>
       </c>
       <c r="B66" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,37 +7424,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574485</v>
+        <v>574563</v>
       </c>
       <c r="R66" t="n">
-        <v>7088660</v>
+        <v>7088745</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7501,9 +7486,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7958,32 +7958,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128339554</v>
+        <v>128340563</v>
       </c>
       <c r="B71" t="n">
-        <v>80162</v>
+        <v>92838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,13 +7993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574560</v>
+        <v>574549</v>
       </c>
       <c r="R71" t="n">
-        <v>7088771</v>
+        <v>7088658</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8026,9 +8026,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8043,65 +8053,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340344</v>
+        <v>128339554</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>80162</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574557</v>
+        <v>574560</v>
       </c>
       <c r="R72" t="n">
-        <v>7088695</v>
+        <v>7088771</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8128,24 +8133,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8160,22 +8150,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340563</v>
+        <v>128340344</v>
       </c>
       <c r="B73" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8183,34 +8173,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574549</v>
+        <v>574557</v>
       </c>
       <c r="R73" t="n">
-        <v>7088658</v>
+        <v>7088695</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8242,7 +8237,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8252,7 +8247,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8267,12 +8267,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340579</v>
+        <v>128338916</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574542</v>
+        <v>574622</v>
       </c>
       <c r="R2" t="n">
-        <v>7088660</v>
+        <v>7088618</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +748,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339514</v>
+        <v>128340643</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>92650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,47 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574577</v>
+        <v>574570</v>
       </c>
       <c r="R3" t="n">
-        <v>7088748</v>
+        <v>7088645</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,9 +850,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338916</v>
+        <v>128340579</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574622</v>
+        <v>574542</v>
       </c>
       <c r="R4" t="n">
-        <v>7088618</v>
+        <v>7088660</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,14 +962,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340643</v>
+        <v>128339514</v>
       </c>
       <c r="B5" t="n">
-        <v>92645</v>
+        <v>56864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,37 +1017,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574570</v>
+        <v>574577</v>
       </c>
       <c r="R5" t="n">
-        <v>7088645</v>
+        <v>7088748</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1084,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,62 +1101,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339216</v>
+        <v>128341140</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574620</v>
+        <v>574438</v>
       </c>
       <c r="R6" t="n">
-        <v>7088666</v>
+        <v>7088595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340410</v>
+        <v>128339216</v>
       </c>
       <c r="B7" t="n">
-        <v>92661</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574543</v>
+        <v>574620</v>
       </c>
       <c r="R7" t="n">
-        <v>7088692</v>
+        <v>7088666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
         <v>128340568</v>
       </c>
       <c r="B8" t="n">
-        <v>78698</v>
+        <v>78699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341140</v>
+        <v>128340410</v>
       </c>
       <c r="B9" t="n">
-        <v>92645</v>
+        <v>92666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574438</v>
+        <v>574543</v>
       </c>
       <c r="R9" t="n">
-        <v>7088595</v>
+        <v>7088692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,12 +1529,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
         <v>128339922</v>
       </c>
       <c r="B10" t="n">
-        <v>78698</v>
+        <v>78699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>128341194</v>
       </c>
       <c r="B11" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>128342806</v>
       </c>
       <c r="B12" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128340548</v>
       </c>
       <c r="B13" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128339006</v>
       </c>
       <c r="B14" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128343119</v>
       </c>
       <c r="B15" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,48 +2163,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B16" t="n">
-        <v>79031</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R16" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,19 +2231,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,60 +2248,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B17" t="n">
-        <v>92645</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2328,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2370,7 +2370,7 @@
         <v>128341646</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,32 +2474,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343851</v>
+        <v>128340679</v>
       </c>
       <c r="B19" t="n">
-        <v>92639</v>
+        <v>92650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574522</v>
+        <v>574565</v>
       </c>
       <c r="R19" t="n">
-        <v>7088573</v>
+        <v>7088589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,32 +2571,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128340725</v>
+        <v>128343851</v>
       </c>
       <c r="B20" t="n">
-        <v>80163</v>
+        <v>92644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574548</v>
+        <v>574522</v>
       </c>
       <c r="R20" t="n">
-        <v>7088558</v>
+        <v>7088573</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128340679</v>
+        <v>128340725</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>80164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574565</v>
+        <v>574548</v>
       </c>
       <c r="R21" t="n">
-        <v>7088589</v>
+        <v>7088558</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2768,7 +2768,7 @@
         <v>128341522</v>
       </c>
       <c r="B22" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,53 +2862,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128339039</v>
+        <v>128341564</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574613</v>
+        <v>574445</v>
       </c>
       <c r="R23" t="n">
-        <v>7088652</v>
+        <v>7088593</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,24 +2930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2967,22 +2947,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338853</v>
+        <v>128339039</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,19 +2990,19 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574647</v>
+        <v>574613</v>
       </c>
       <c r="R24" t="n">
-        <v>7088580</v>
+        <v>7088652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3064,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3084,22 +3064,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128340360</v>
+        <v>128338853</v>
       </c>
       <c r="B25" t="n">
-        <v>79031</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,34 +3087,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574548</v>
+        <v>574647</v>
       </c>
       <c r="R25" t="n">
-        <v>7088705</v>
+        <v>7088580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3166,7 +3151,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3176,7 +3161,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,32 +3193,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128341564</v>
+        <v>128340360</v>
       </c>
       <c r="B26" t="n">
-        <v>92645</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,13 +3228,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574445</v>
+        <v>574548</v>
       </c>
       <c r="R26" t="n">
-        <v>7088593</v>
+        <v>7088705</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3271,9 +3261,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,22 +3288,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338795</v>
+        <v>128340549</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>90393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,39 +3311,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574657</v>
+        <v>574555</v>
       </c>
       <c r="R27" t="n">
-        <v>7088592</v>
+        <v>7088647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3385,12 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3417,32 +3407,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128340549</v>
+        <v>128340667</v>
       </c>
       <c r="B28" t="n">
-        <v>90390</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574555</v>
+        <v>574565</v>
       </c>
       <c r="R28" t="n">
-        <v>7088647</v>
+        <v>7088619</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,7 +3477,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3497,7 +3487,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,45 +3514,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128340667</v>
+        <v>128338795</v>
       </c>
       <c r="B29" t="n">
-        <v>92645</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574565</v>
+        <v>574657</v>
       </c>
       <c r="R29" t="n">
-        <v>7088619</v>
+        <v>7088592</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3589,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,7 +3599,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,32 +3631,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128339431</v>
+        <v>128339483</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574614</v>
+        <v>574580</v>
       </c>
       <c r="R30" t="n">
-        <v>7088709</v>
+        <v>7088751</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3704,24 +3704,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3736,44 +3721,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339483</v>
+        <v>128339278</v>
       </c>
       <c r="B31" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,13 +3773,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574580</v>
+        <v>574615</v>
       </c>
       <c r="R31" t="n">
-        <v>7088751</v>
+        <v>7088675</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3821,9 +3806,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3838,22 +3838,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128339278</v>
+        <v>128339431</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574615</v>
+        <v>574614</v>
       </c>
       <c r="R32" t="n">
-        <v>7088675</v>
+        <v>7088709</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3967,53 +3967,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339517</v>
+        <v>128339234</v>
       </c>
       <c r="B33" t="n">
-        <v>57669</v>
+        <v>80039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574599</v>
+        <v>574647</v>
       </c>
       <c r="R33" t="n">
-        <v>7088725</v>
+        <v>7088700</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4040,19 +4035,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,60 +4052,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339462</v>
+        <v>128343108</v>
       </c>
       <c r="B34" t="n">
-        <v>79031</v>
+        <v>56864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574615</v>
+        <v>574486</v>
       </c>
       <c r="R34" t="n">
-        <v>7088761</v>
+        <v>7088664</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4147,19 +4137,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4174,12 +4159,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4189,7 +4174,7 @@
         <v>128339640</v>
       </c>
       <c r="B35" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128340784</v>
+        <v>128339462</v>
       </c>
       <c r="B36" t="n">
-        <v>92673</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4289,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,13 +4313,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574541</v>
+        <v>574615</v>
       </c>
       <c r="R36" t="n">
-        <v>7088525</v>
+        <v>7088761</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4361,9 +4346,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4378,44 +4373,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128339234</v>
+        <v>128343025</v>
       </c>
       <c r="B37" t="n">
-        <v>80038</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574647</v>
+        <v>574482</v>
       </c>
       <c r="R37" t="n">
-        <v>7088700</v>
+        <v>7088688</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4487,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128343025</v>
+        <v>128340784</v>
       </c>
       <c r="B38" t="n">
-        <v>79031</v>
+        <v>92678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4498,21 +4493,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574482</v>
+        <v>574541</v>
       </c>
       <c r="R38" t="n">
-        <v>7088688</v>
+        <v>7088525</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4584,38 +4579,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128343108</v>
+        <v>128339517</v>
       </c>
       <c r="B39" t="n">
-        <v>56864</v>
+        <v>57670</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4624,13 +4619,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574486</v>
+        <v>574599</v>
       </c>
       <c r="R39" t="n">
-        <v>7088664</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4657,14 +4652,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Grop</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,22 +4679,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128339243</v>
+        <v>128340357</v>
       </c>
       <c r="B40" t="n">
-        <v>79031</v>
+        <v>79650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,21 +4702,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574646</v>
+        <v>574526</v>
       </c>
       <c r="R40" t="n">
-        <v>7088700</v>
+        <v>7088741</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128340357</v>
+        <v>128340692</v>
       </c>
       <c r="B41" t="n">
-        <v>79649</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,34 +4799,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574526</v>
+        <v>574557</v>
       </c>
       <c r="R41" t="n">
-        <v>7088741</v>
+        <v>7088560</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4859,6 +4864,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4885,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340692</v>
+        <v>128339243</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4896,39 +4906,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574557</v>
+        <v>574646</v>
       </c>
       <c r="R42" t="n">
-        <v>7088560</v>
+        <v>7088700</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4961,11 +4966,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,32 +4992,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128339546</v>
+        <v>128341581</v>
       </c>
       <c r="B43" t="n">
-        <v>92645</v>
+        <v>78699</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574558</v>
+        <v>574445</v>
       </c>
       <c r="R43" t="n">
-        <v>7088774</v>
+        <v>7088593</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5089,32 +5089,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128340722</v>
+        <v>128339546</v>
       </c>
       <c r="B44" t="n">
-        <v>80134</v>
+        <v>92650</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,13 +5124,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574563</v>
+        <v>574558</v>
       </c>
       <c r="R44" t="n">
-        <v>7088549</v>
+        <v>7088774</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5157,19 +5157,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5184,22 +5174,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128340649</v>
+        <v>128339432</v>
       </c>
       <c r="B45" t="n">
-        <v>79649</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5207,34 +5197,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574573</v>
+        <v>574618</v>
       </c>
       <c r="R45" t="n">
-        <v>7088640</v>
+        <v>7088746</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5266,7 +5261,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5276,7 +5271,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5303,10 +5303,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128339432</v>
+        <v>128340722</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5314,39 +5314,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574618</v>
+        <v>574563</v>
       </c>
       <c r="R46" t="n">
-        <v>7088746</v>
+        <v>7088549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,7 +5373,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5388,12 +5383,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5420,53 +5410,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128339678</v>
+        <v>128340649</v>
       </c>
       <c r="B47" t="n">
-        <v>56864</v>
+        <v>79650</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574545</v>
+        <v>574573</v>
       </c>
       <c r="R47" t="n">
-        <v>7088725</v>
+        <v>7088640</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5493,14 +5478,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5515,57 +5505,62 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128341581</v>
+        <v>128339678</v>
       </c>
       <c r="B48" t="n">
-        <v>78698</v>
+        <v>56864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574445</v>
+        <v>574545</v>
       </c>
       <c r="R48" t="n">
-        <v>7088593</v>
+        <v>7088725</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5598,6 +5593,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5627,7 +5627,7 @@
         <v>128338962</v>
       </c>
       <c r="B49" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B50" t="n">
-        <v>80170</v>
+        <v>92650</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R50" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,9 +5809,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5826,22 +5836,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128341658</v>
+        <v>128340602</v>
       </c>
       <c r="B51" t="n">
-        <v>78698</v>
+        <v>92675</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5849,21 +5859,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5873,13 +5883,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574445</v>
+        <v>574553</v>
       </c>
       <c r="R51" t="n">
-        <v>7088595</v>
+        <v>7088642</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5906,9 +5916,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5923,62 +5943,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128339103</v>
+        <v>128341543</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>80171</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R52" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6011,11 +6026,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6042,48 +6052,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128340512</v>
+        <v>128339103</v>
       </c>
       <c r="B53" t="n">
-        <v>92645</v>
+        <v>57673</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574550</v>
+        <v>574625</v>
       </c>
       <c r="R53" t="n">
-        <v>7088660</v>
+        <v>7088640</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6110,19 +6125,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6137,22 +6147,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128340602</v>
+        <v>128339352</v>
       </c>
       <c r="B54" t="n">
-        <v>92670</v>
+        <v>57673</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6160,34 +6170,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574553</v>
+        <v>574614</v>
       </c>
       <c r="R54" t="n">
-        <v>7088642</v>
+        <v>7088680</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6219,7 +6234,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6229,7 +6244,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6244,22 +6264,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128339352</v>
+        <v>128341658</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>78699</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6267,42 +6287,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574614</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088680</v>
+        <v>7088595</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6329,24 +6344,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,44 +6361,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339188</v>
+        <v>128339624</v>
       </c>
       <c r="B56" t="n">
-        <v>79031</v>
+        <v>92650</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574647</v>
+        <v>574580</v>
       </c>
       <c r="R56" t="n">
-        <v>7088696</v>
+        <v>7088767</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,19 +6441,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6468,65 +6458,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339538</v>
+        <v>128341588</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574598</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088728</v>
+        <v>7088594</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6553,24 +6538,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6585,22 +6555,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339624</v>
+        <v>128339929</v>
       </c>
       <c r="B58" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6632,13 +6602,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574580</v>
+        <v>574555</v>
       </c>
       <c r="R58" t="n">
-        <v>7088767</v>
+        <v>7088696</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6665,9 +6635,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6682,57 +6662,62 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339929</v>
+        <v>128339538</v>
       </c>
       <c r="B59" t="n">
-        <v>92645</v>
+        <v>57673</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574555</v>
+        <v>574598</v>
       </c>
       <c r="R59" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6764,7 +6749,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6774,7 +6759,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6801,32 +6791,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128341588</v>
+        <v>128339188</v>
       </c>
       <c r="B60" t="n">
-        <v>92645</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6836,13 +6826,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R60" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6869,9 +6859,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,44 +6886,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128339543</v>
+        <v>128343086</v>
       </c>
       <c r="B61" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574558</v>
+        <v>574491</v>
       </c>
       <c r="R61" t="n">
-        <v>7088774</v>
+        <v>7088668</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128343086</v>
+        <v>128339543</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574491</v>
+        <v>574558</v>
       </c>
       <c r="R62" t="n">
-        <v>7088668</v>
+        <v>7088774</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128343065</v>
+        <v>128339617</v>
       </c>
       <c r="B63" t="n">
-        <v>79031</v>
+        <v>57673</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,37 +7123,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574485</v>
+        <v>574563</v>
       </c>
       <c r="R63" t="n">
-        <v>7088660</v>
+        <v>7088745</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7180,9 +7185,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7197,22 +7217,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128340645</v>
+        <v>128340020</v>
       </c>
       <c r="B64" t="n">
-        <v>78789</v>
+        <v>78699</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,21 +7240,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7244,13 +7264,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574571</v>
+        <v>574526</v>
       </c>
       <c r="R64" t="n">
-        <v>7088636</v>
+        <v>7088741</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7277,19 +7297,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7304,22 +7314,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128340020</v>
+        <v>128343065</v>
       </c>
       <c r="B65" t="n">
-        <v>78698</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7327,21 +7337,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7351,10 +7361,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574526</v>
+        <v>574485</v>
       </c>
       <c r="R65" t="n">
-        <v>7088741</v>
+        <v>7088660</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7413,10 +7423,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128339617</v>
+        <v>128340645</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>78790</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7424,39 +7434,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574563</v>
+        <v>574571</v>
       </c>
       <c r="R66" t="n">
-        <v>7088745</v>
+        <v>7088636</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7488,7 +7493,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7498,12 +7503,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,22 +7518,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128339467</v>
+        <v>128341241</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>92666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7541,39 +7541,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574607</v>
+        <v>574529</v>
       </c>
       <c r="R67" t="n">
-        <v>7088708</v>
+        <v>7088560</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7605,7 +7600,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7615,12 +7610,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7635,12 +7625,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7650,7 +7640,7 @@
         <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>80163</v>
+        <v>80164</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7754,10 +7744,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341241</v>
+        <v>128339467</v>
       </c>
       <c r="B69" t="n">
-        <v>92661</v>
+        <v>57673</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7765,34 +7755,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574529</v>
+        <v>574607</v>
       </c>
       <c r="R69" t="n">
-        <v>7088560</v>
+        <v>7088708</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7824,7 +7819,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7834,7 +7829,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7849,22 +7849,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340363</v>
+        <v>128340563</v>
       </c>
       <c r="B70" t="n">
-        <v>79031</v>
+        <v>92843</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,13 +7896,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574523</v>
+        <v>574549</v>
       </c>
       <c r="R70" t="n">
-        <v>7088723</v>
+        <v>7088658</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7929,9 +7929,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7946,44 +7956,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340563</v>
+        <v>128339554</v>
       </c>
       <c r="B71" t="n">
-        <v>92838</v>
+        <v>80163</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,13 +8003,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574549</v>
+        <v>574560</v>
       </c>
       <c r="R71" t="n">
-        <v>7088658</v>
+        <v>7088771</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8026,19 +8036,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8053,60 +8053,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128339554</v>
+        <v>128340670</v>
       </c>
       <c r="B72" t="n">
-        <v>80162</v>
+        <v>57673</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574560</v>
+        <v>574568</v>
       </c>
       <c r="R72" t="n">
-        <v>7088771</v>
+        <v>7088607</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8133,9 +8138,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8150,22 +8170,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340344</v>
+        <v>128340933</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8202,10 +8222,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574557</v>
+        <v>574498</v>
       </c>
       <c r="R73" t="n">
-        <v>7088695</v>
+        <v>7088556</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8237,7 +8257,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8247,7 +8267,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8279,10 +8299,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340933</v>
+        <v>128341109</v>
       </c>
       <c r="B74" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8319,10 +8339,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574498</v>
+        <v>574429</v>
       </c>
       <c r="R74" t="n">
-        <v>7088556</v>
+        <v>7088591</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8354,7 +8374,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8364,7 +8384,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8396,10 +8416,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128341109</v>
+        <v>128340344</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8436,10 +8456,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574429</v>
+        <v>574557</v>
       </c>
       <c r="R75" t="n">
-        <v>7088591</v>
+        <v>7088695</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8471,7 +8491,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8481,7 +8501,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -8513,10 +8533,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340639</v>
+        <v>128340363</v>
       </c>
       <c r="B76" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8524,21 +8544,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8548,13 +8568,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574574</v>
+        <v>574523</v>
       </c>
       <c r="R76" t="n">
-        <v>7088635</v>
+        <v>7088723</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8581,19 +8601,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8608,22 +8618,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128340670</v>
+        <v>128340639</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>78791</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8631,39 +8641,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574568</v>
+        <v>574574</v>
       </c>
       <c r="R77" t="n">
-        <v>7088607</v>
+        <v>7088635</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8708,11 +8713,6 @@
           <t>16:22</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8725,12 +8725,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8740,7 +8740,7 @@
         <v>128340367</v>
       </c>
       <c r="B78" t="n">
-        <v>96598</v>
+        <v>96603</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>128339415</v>
       </c>
       <c r="B79" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -2163,45 +2163,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340635</v>
+        <v>128341646</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574554</v>
+        <v>574445</v>
       </c>
       <c r="R16" t="n">
-        <v>7088634</v>
+        <v>7088594</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2234,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,48 +2270,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,19 +2338,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,22 +2355,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341646</v>
+        <v>128338970</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,42 +2378,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574445</v>
+        <v>574649</v>
       </c>
       <c r="R18" t="n">
-        <v>7088594</v>
+        <v>7088609</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,14 +2435,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -6898,32 +6898,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128343086</v>
+        <v>128339543</v>
       </c>
       <c r="B61" t="n">
-        <v>57673</v>
+        <v>56864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574491</v>
+        <v>574558</v>
       </c>
       <c r="R61" t="n">
-        <v>7088668</v>
+        <v>7088774</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128339543</v>
+        <v>128343086</v>
       </c>
       <c r="B62" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574558</v>
+        <v>574491</v>
       </c>
       <c r="R62" t="n">
-        <v>7088774</v>
+        <v>7088668</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128339617</v>
+        <v>128340020</v>
       </c>
       <c r="B63" t="n">
-        <v>57673</v>
+        <v>78699</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,42 +7123,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574563</v>
+        <v>574526</v>
       </c>
       <c r="R63" t="n">
-        <v>7088745</v>
+        <v>7088741</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7185,24 +7180,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7217,22 +7197,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128340020</v>
+        <v>128339617</v>
       </c>
       <c r="B64" t="n">
-        <v>78699</v>
+        <v>57673</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7240,37 +7220,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574526</v>
+        <v>574563</v>
       </c>
       <c r="R64" t="n">
-        <v>7088741</v>
+        <v>7088745</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7297,9 +7282,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7314,12 +7314,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340563</v>
+        <v>128340639</v>
       </c>
       <c r="B70" t="n">
-        <v>92843</v>
+        <v>78791</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574549</v>
+        <v>574574</v>
       </c>
       <c r="R70" t="n">
-        <v>7088658</v>
+        <v>7088635</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128339554</v>
+        <v>128340563</v>
       </c>
       <c r="B71" t="n">
-        <v>80163</v>
+        <v>92843</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8003,13 +8003,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574560</v>
+        <v>574549</v>
       </c>
       <c r="R71" t="n">
-        <v>7088771</v>
+        <v>7088658</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8036,9 +8036,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8053,65 +8063,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340670</v>
+        <v>128339554</v>
       </c>
       <c r="B72" t="n">
-        <v>57673</v>
+        <v>80163</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574568</v>
+        <v>574560</v>
       </c>
       <c r="R72" t="n">
-        <v>7088607</v>
+        <v>7088771</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8138,24 +8143,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8170,19 +8160,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340933</v>
+        <v>128340670</v>
       </c>
       <c r="B73" t="n">
         <v>57673</v>
@@ -8213,7 +8203,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8222,10 +8212,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574498</v>
+        <v>574568</v>
       </c>
       <c r="R73" t="n">
-        <v>7088556</v>
+        <v>7088607</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8257,7 +8247,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8267,7 +8257,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8299,7 +8289,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128341109</v>
+        <v>128340933</v>
       </c>
       <c r="B74" t="n">
         <v>57673</v>
@@ -8339,10 +8329,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574429</v>
+        <v>574498</v>
       </c>
       <c r="R74" t="n">
-        <v>7088591</v>
+        <v>7088556</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8374,7 +8364,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8384,7 +8374,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8416,7 +8406,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128340344</v>
+        <v>128341109</v>
       </c>
       <c r="B75" t="n">
         <v>57673</v>
@@ -8456,10 +8446,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574557</v>
+        <v>574429</v>
       </c>
       <c r="R75" t="n">
-        <v>7088695</v>
+        <v>7088591</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,7 +8481,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8501,7 +8491,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -8533,10 +8523,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340363</v>
+        <v>128340344</v>
       </c>
       <c r="B76" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8544,37 +8534,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574523</v>
+        <v>574557</v>
       </c>
       <c r="R76" t="n">
-        <v>7088723</v>
+        <v>7088695</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8601,9 +8596,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8618,22 +8628,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128340639</v>
+        <v>128340363</v>
       </c>
       <c r="B77" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8641,21 +8651,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8665,13 +8675,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574574</v>
+        <v>574523</v>
       </c>
       <c r="R77" t="n">
-        <v>7088635</v>
+        <v>7088723</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8698,19 +8708,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8725,12 +8725,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128338916</v>
+        <v>128340643</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574622</v>
+        <v>574570</v>
       </c>
       <c r="R2" t="n">
-        <v>7088618</v>
+        <v>7088645</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,14 +743,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,60 +770,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340643</v>
+        <v>128338916</v>
       </c>
       <c r="B3" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574570</v>
+        <v>574622</v>
       </c>
       <c r="R3" t="n">
-        <v>7088645</v>
+        <v>7088618</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +855,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>128340579</v>
       </c>
       <c r="B4" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128339514</v>
       </c>
       <c r="B5" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128341140</v>
       </c>
       <c r="B6" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128339216</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340568</v>
+        <v>128340410</v>
       </c>
       <c r="B8" t="n">
-        <v>78699</v>
+        <v>92758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574551</v>
+        <v>574543</v>
       </c>
       <c r="R8" t="n">
-        <v>7088652</v>
+        <v>7088692</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,9 +1405,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340410</v>
+        <v>128340568</v>
       </c>
       <c r="B9" t="n">
-        <v>92666</v>
+        <v>78749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1479,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574543</v>
+        <v>574551</v>
       </c>
       <c r="R9" t="n">
-        <v>7088692</v>
+        <v>7088652</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,19 +1512,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B10" t="n">
-        <v>78699</v>
+        <v>80188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R10" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B11" t="n">
-        <v>80135</v>
+        <v>78749</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R11" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,7 +1758,7 @@
         <v>128342806</v>
       </c>
       <c r="B12" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,48 +1862,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340548</v>
+        <v>128339006</v>
       </c>
       <c r="B13" t="n">
-        <v>92650</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574550</v>
+        <v>574657</v>
       </c>
       <c r="R13" t="n">
-        <v>7088658</v>
+        <v>7088628</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,19 +1930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,22 +1947,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128339006</v>
+        <v>128343119</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574657</v>
+        <v>574495</v>
       </c>
       <c r="R14" t="n">
-        <v>7088628</v>
+        <v>7088662</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2066,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343119</v>
+        <v>128340548</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574495</v>
+        <v>574550</v>
       </c>
       <c r="R15" t="n">
-        <v>7088662</v>
+        <v>7088658</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,9 +2124,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,62 +2151,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341646</v>
+        <v>128340635</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574445</v>
+        <v>574554</v>
       </c>
       <c r="R16" t="n">
-        <v>7088594</v>
+        <v>7088634</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2239,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,45 +2260,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128341646</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574445</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088594</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,7 +2370,7 @@
         <v>128338970</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340679</v>
+        <v>128340725</v>
       </c>
       <c r="B19" t="n">
-        <v>92650</v>
+        <v>80217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574565</v>
+        <v>574548</v>
       </c>
       <c r="R19" t="n">
-        <v>7088589</v>
+        <v>7088558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,32 +2571,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128343851</v>
+        <v>128340679</v>
       </c>
       <c r="B20" t="n">
-        <v>92644</v>
+        <v>92742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574522</v>
+        <v>574565</v>
       </c>
       <c r="R20" t="n">
-        <v>7088573</v>
+        <v>7088589</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,32 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128340725</v>
+        <v>128343851</v>
       </c>
       <c r="B21" t="n">
-        <v>80164</v>
+        <v>92736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574548</v>
+        <v>574522</v>
       </c>
       <c r="R21" t="n">
-        <v>7088558</v>
+        <v>7088573</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2768,7 +2768,7 @@
         <v>128341522</v>
       </c>
       <c r="B22" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,32 +2862,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128341564</v>
+        <v>128340360</v>
       </c>
       <c r="B23" t="n">
-        <v>92650</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574445</v>
+        <v>574548</v>
       </c>
       <c r="R23" t="n">
-        <v>7088593</v>
+        <v>7088705</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,9 +2930,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,65 +2957,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128339039</v>
+        <v>128341564</v>
       </c>
       <c r="B24" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574613</v>
+        <v>574445</v>
       </c>
       <c r="R24" t="n">
-        <v>7088652</v>
+        <v>7088593</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3032,24 +3037,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3064,22 +3054,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338853</v>
+        <v>128339039</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,19 +3097,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574647</v>
+        <v>574613</v>
       </c>
       <c r="R25" t="n">
-        <v>7088580</v>
+        <v>7088652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3151,7 +3141,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3161,7 +3151,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3181,22 +3171,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128340360</v>
+        <v>128338853</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,34 +3194,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574548</v>
+        <v>574647</v>
       </c>
       <c r="R26" t="n">
-        <v>7088705</v>
+        <v>7088580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3273,7 +3268,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3300,48 +3300,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128340549</v>
+        <v>128339483</v>
       </c>
       <c r="B27" t="n">
-        <v>90393</v>
+        <v>56876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574555</v>
+        <v>574580</v>
       </c>
       <c r="R27" t="n">
-        <v>7088647</v>
+        <v>7088751</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3368,19 +3373,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3395,44 +3390,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128340667</v>
+        <v>128340549</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>90485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3442,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574565</v>
+        <v>574555</v>
       </c>
       <c r="R28" t="n">
-        <v>7088619</v>
+        <v>7088647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,7 +3472,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3487,7 +3482,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,50 +3509,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128338795</v>
+        <v>128340667</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574657</v>
+        <v>574565</v>
       </c>
       <c r="R29" t="n">
-        <v>7088592</v>
+        <v>7088619</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3589,7 +3579,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3599,12 +3589,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,32 +3616,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128339483</v>
+        <v>128339278</v>
       </c>
       <c r="B30" t="n">
-        <v>56864</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,13 +3656,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574580</v>
+        <v>574615</v>
       </c>
       <c r="R30" t="n">
-        <v>7088751</v>
+        <v>7088675</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3704,9 +3689,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,22 +3721,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339278</v>
+        <v>128339431</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574615</v>
+        <v>574614</v>
       </c>
       <c r="R31" t="n">
-        <v>7088675</v>
+        <v>7088709</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3850,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128339431</v>
+        <v>128338795</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574614</v>
+        <v>574657</v>
       </c>
       <c r="R32" t="n">
-        <v>7088709</v>
+        <v>7088592</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,44 +3955,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339234</v>
+        <v>128339640</v>
       </c>
       <c r="B33" t="n">
-        <v>80039</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574647</v>
+        <v>574554</v>
       </c>
       <c r="R33" t="n">
-        <v>7088700</v>
+        <v>7088750</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,9 +4035,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,65 +4062,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128343108</v>
+        <v>128339462</v>
       </c>
       <c r="B34" t="n">
-        <v>56864</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574486</v>
+        <v>574615</v>
       </c>
       <c r="R34" t="n">
-        <v>7088664</v>
+        <v>7088761</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4137,14 +4142,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Grop</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4159,44 +4169,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339640</v>
+        <v>128339234</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>80092</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4206,13 +4216,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574554</v>
+        <v>574647</v>
       </c>
       <c r="R35" t="n">
-        <v>7088750</v>
+        <v>7088700</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4239,19 +4249,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4266,22 +4266,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339462</v>
+        <v>128343025</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574615</v>
+        <v>574482</v>
       </c>
       <c r="R36" t="n">
-        <v>7088761</v>
+        <v>7088688</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4346,19 +4346,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4373,22 +4363,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343025</v>
+        <v>128340784</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>92770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4396,21 +4386,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574482</v>
+        <v>574541</v>
       </c>
       <c r="R37" t="n">
-        <v>7088688</v>
+        <v>7088525</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4482,10 +4472,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128340784</v>
+        <v>128339517</v>
       </c>
       <c r="B38" t="n">
-        <v>92678</v>
+        <v>57682</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4493,37 +4483,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574541</v>
+        <v>574599</v>
       </c>
       <c r="R38" t="n">
-        <v>7088525</v>
+        <v>7088725</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4550,9 +4545,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,50 +4572,50 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128339517</v>
+        <v>128343108</v>
       </c>
       <c r="B39" t="n">
-        <v>57670</v>
+        <v>56876</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4619,13 +4624,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574599</v>
+        <v>574486</v>
       </c>
       <c r="R39" t="n">
-        <v>7088725</v>
+        <v>7088664</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4652,19 +4657,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,12 +4679,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
         <v>128340357</v>
       </c>
       <c r="B40" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128340692</v>
+        <v>128339243</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,39 +4799,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574557</v>
+        <v>574646</v>
       </c>
       <c r="R41" t="n">
-        <v>7088560</v>
+        <v>7088700</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4864,11 +4859,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128339243</v>
+        <v>128340692</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,34 +4896,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574646</v>
+        <v>574557</v>
       </c>
       <c r="R42" t="n">
-        <v>7088700</v>
+        <v>7088560</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4966,6 +4961,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,10 +4992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341581</v>
+        <v>128340649</v>
       </c>
       <c r="B43" t="n">
-        <v>78699</v>
+        <v>79702</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,13 +5027,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574445</v>
+        <v>574573</v>
       </c>
       <c r="R43" t="n">
-        <v>7088593</v>
+        <v>7088640</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5060,9 +5060,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5077,44 +5087,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128339546</v>
+        <v>128341581</v>
       </c>
       <c r="B44" t="n">
-        <v>92650</v>
+        <v>78749</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5134,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574558</v>
+        <v>574445</v>
       </c>
       <c r="R44" t="n">
-        <v>7088774</v>
+        <v>7088593</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5186,53 +5196,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128339432</v>
+        <v>128339546</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574618</v>
+        <v>574558</v>
       </c>
       <c r="R45" t="n">
-        <v>7088746</v>
+        <v>7088774</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5259,24 +5264,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5291,22 +5281,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128340722</v>
+        <v>128339432</v>
       </c>
       <c r="B46" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5314,34 +5304,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574563</v>
+        <v>574618</v>
       </c>
       <c r="R46" t="n">
-        <v>7088549</v>
+        <v>7088746</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5373,7 +5368,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5383,7 +5378,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5410,48 +5410,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128340649</v>
+        <v>128339678</v>
       </c>
       <c r="B47" t="n">
-        <v>79650</v>
+        <v>56876</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574573</v>
+        <v>574545</v>
       </c>
       <c r="R47" t="n">
-        <v>7088640</v>
+        <v>7088725</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5478,19 +5483,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:23</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5505,65 +5505,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128339678</v>
+        <v>128340722</v>
       </c>
       <c r="B48" t="n">
-        <v>56864</v>
+        <v>80188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574545</v>
+        <v>574563</v>
       </c>
       <c r="R48" t="n">
-        <v>7088725</v>
+        <v>7088549</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5590,14 +5585,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5627,7 +5627,7 @@
         <v>128338962</v>
       </c>
       <c r="B49" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5741,32 +5741,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340512</v>
+        <v>128340602</v>
       </c>
       <c r="B50" t="n">
-        <v>92650</v>
+        <v>92767</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574550</v>
+        <v>574553</v>
       </c>
       <c r="R50" t="n">
-        <v>7088660</v>
+        <v>7088642</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5848,32 +5848,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340602</v>
+        <v>128340512</v>
       </c>
       <c r="B51" t="n">
-        <v>92675</v>
+        <v>92742</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574553</v>
+        <v>574550</v>
       </c>
       <c r="R51" t="n">
-        <v>7088642</v>
+        <v>7088660</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5958,7 +5958,7 @@
         <v>128341543</v>
       </c>
       <c r="B52" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>128339103</v>
       </c>
       <c r="B53" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128339352</v>
       </c>
       <c r="B54" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>128341658</v>
       </c>
       <c r="B55" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6373,48 +6373,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339624</v>
+        <v>128339538</v>
       </c>
       <c r="B56" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574580</v>
+        <v>574598</v>
       </c>
       <c r="R56" t="n">
-        <v>7088767</v>
+        <v>7088728</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,9 +6446,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6458,44 +6478,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341588</v>
+        <v>128339188</v>
       </c>
       <c r="B57" t="n">
-        <v>92650</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6505,13 +6525,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R57" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6538,9 +6558,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6555,22 +6585,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339929</v>
+        <v>128339624</v>
       </c>
       <c r="B58" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6602,13 +6632,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574555</v>
+        <v>574580</v>
       </c>
       <c r="R58" t="n">
-        <v>7088696</v>
+        <v>7088767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6635,19 +6665,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6662,65 +6682,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339538</v>
+        <v>128341588</v>
       </c>
       <c r="B59" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574598</v>
+        <v>574445</v>
       </c>
       <c r="R59" t="n">
-        <v>7088728</v>
+        <v>7088594</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6747,24 +6762,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6779,44 +6779,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339188</v>
+        <v>128339929</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>92742</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6826,7 +6826,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574647</v>
+        <v>574555</v>
       </c>
       <c r="R60" t="n">
         <v>7088696</v>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,44 +6886,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128339543</v>
+        <v>128343086</v>
       </c>
       <c r="B61" t="n">
-        <v>56864</v>
+        <v>57685</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574558</v>
+        <v>574491</v>
       </c>
       <c r="R61" t="n">
-        <v>7088774</v>
+        <v>7088668</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128343086</v>
+        <v>128339543</v>
       </c>
       <c r="B62" t="n">
-        <v>57673</v>
+        <v>56876</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574491</v>
+        <v>574558</v>
       </c>
       <c r="R62" t="n">
-        <v>7088668</v>
+        <v>7088774</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128340020</v>
+        <v>128340645</v>
       </c>
       <c r="B63" t="n">
-        <v>78699</v>
+        <v>78840</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574526</v>
+        <v>574571</v>
       </c>
       <c r="R63" t="n">
-        <v>7088741</v>
+        <v>7088636</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7180,9 +7180,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7197,22 +7207,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128339617</v>
+        <v>128340020</v>
       </c>
       <c r="B64" t="n">
-        <v>57673</v>
+        <v>78749</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,42 +7230,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574563</v>
+        <v>574526</v>
       </c>
       <c r="R64" t="n">
-        <v>7088745</v>
+        <v>7088741</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7282,24 +7287,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7314,22 +7304,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128343065</v>
+        <v>128339617</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7337,37 +7327,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574485</v>
+        <v>574563</v>
       </c>
       <c r="R65" t="n">
-        <v>7088660</v>
+        <v>7088745</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7394,9 +7389,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,22 +7421,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128340645</v>
+        <v>128343065</v>
       </c>
       <c r="B66" t="n">
-        <v>78790</v>
+        <v>79083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,21 +7444,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7458,13 +7468,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574571</v>
+        <v>574485</v>
       </c>
       <c r="R66" t="n">
-        <v>7088636</v>
+        <v>7088660</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7491,19 +7501,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7533,7 +7533,7 @@
         <v>128341241</v>
       </c>
       <c r="B67" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>128339467</v>
       </c>
       <c r="B69" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7861,32 +7861,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340639</v>
+        <v>128339554</v>
       </c>
       <c r="B70" t="n">
-        <v>78791</v>
+        <v>80216</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,13 +7896,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574574</v>
+        <v>574560</v>
       </c>
       <c r="R70" t="n">
-        <v>7088635</v>
+        <v>7088771</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7929,19 +7929,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7956,22 +7946,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340563</v>
+        <v>128340639</v>
       </c>
       <c r="B71" t="n">
-        <v>92843</v>
+        <v>78841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7979,21 +7969,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8003,10 +7993,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574549</v>
+        <v>574574</v>
       </c>
       <c r="R71" t="n">
-        <v>7088658</v>
+        <v>7088635</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8038,7 +8028,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8048,7 +8038,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8075,32 +8065,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128339554</v>
+        <v>128340563</v>
       </c>
       <c r="B72" t="n">
-        <v>80163</v>
+        <v>92935</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8110,13 +8100,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574560</v>
+        <v>574549</v>
       </c>
       <c r="R72" t="n">
-        <v>7088771</v>
+        <v>7088658</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8143,9 +8133,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8160,22 +8160,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340670</v>
+        <v>128340363</v>
       </c>
       <c r="B73" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8183,42 +8183,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574568</v>
+        <v>574523</v>
       </c>
       <c r="R73" t="n">
-        <v>7088607</v>
+        <v>7088723</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8245,24 +8240,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8277,22 +8257,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340933</v>
+        <v>128340670</v>
       </c>
       <c r="B74" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8320,7 +8300,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8329,10 +8309,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574498</v>
+        <v>574568</v>
       </c>
       <c r="R74" t="n">
-        <v>7088556</v>
+        <v>7088607</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8364,7 +8344,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8374,7 +8354,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8406,10 +8386,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128341109</v>
+        <v>128340933</v>
       </c>
       <c r="B75" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8446,10 +8426,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574429</v>
+        <v>574498</v>
       </c>
       <c r="R75" t="n">
-        <v>7088591</v>
+        <v>7088556</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8481,7 +8461,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8491,7 +8471,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -8523,10 +8503,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340344</v>
+        <v>128341109</v>
       </c>
       <c r="B76" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8563,10 +8543,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574557</v>
+        <v>574429</v>
       </c>
       <c r="R76" t="n">
-        <v>7088695</v>
+        <v>7088591</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8598,7 +8578,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8608,7 +8588,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -8640,10 +8620,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128340363</v>
+        <v>128340344</v>
       </c>
       <c r="B77" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8651,37 +8631,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574523</v>
+        <v>574557</v>
       </c>
       <c r="R77" t="n">
-        <v>7088723</v>
+        <v>7088695</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8708,9 +8693,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8725,12 +8725,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8740,7 +8740,7 @@
         <v>128340367</v>
       </c>
       <c r="B78" t="n">
-        <v>96603</v>
+        <v>96696</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>128339415</v>
       </c>
       <c r="B79" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340410</v>
+        <v>128340568</v>
       </c>
       <c r="B8" t="n">
-        <v>92758</v>
+        <v>78749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574543</v>
+        <v>574551</v>
       </c>
       <c r="R8" t="n">
-        <v>7088692</v>
+        <v>7088652</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,19 +1405,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340568</v>
+        <v>128340410</v>
       </c>
       <c r="B9" t="n">
-        <v>78749</v>
+        <v>92758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574551</v>
+        <v>574543</v>
       </c>
       <c r="R9" t="n">
-        <v>7088652</v>
+        <v>7088692</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,9 +1502,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>78749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R10" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B11" t="n">
-        <v>78749</v>
+        <v>80188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R11" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,48 +1862,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128339006</v>
+        <v>128340548</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574657</v>
+        <v>574550</v>
       </c>
       <c r="R13" t="n">
-        <v>7088628</v>
+        <v>7088658</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,9 +1930,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343119</v>
+        <v>128339006</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -1990,14 +2000,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574495</v>
+        <v>574657</v>
       </c>
       <c r="R14" t="n">
-        <v>7088662</v>
+        <v>7088628</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2056,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340548</v>
+        <v>128343119</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574550</v>
+        <v>574495</v>
       </c>
       <c r="R15" t="n">
-        <v>7088658</v>
+        <v>7088662</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,19 +2134,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,60 +2151,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R16" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2231,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,62 +2258,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341646</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574445</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088594</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2336,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128338970</v>
+        <v>128341646</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,37 +2378,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574649</v>
+        <v>574445</v>
       </c>
       <c r="R18" t="n">
-        <v>7088609</v>
+        <v>7088594</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2435,19 +2440,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,22 +2462,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340725</v>
+        <v>128340679</v>
       </c>
       <c r="B19" t="n">
-        <v>80217</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574548</v>
+        <v>574565</v>
       </c>
       <c r="R19" t="n">
-        <v>7088558</v>
+        <v>7088589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,32 +2571,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128340679</v>
+        <v>128343851</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>92736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574565</v>
+        <v>574522</v>
       </c>
       <c r="R20" t="n">
-        <v>7088589</v>
+        <v>7088573</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,32 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343851</v>
+        <v>128340725</v>
       </c>
       <c r="B21" t="n">
-        <v>92736</v>
+        <v>80217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574522</v>
+        <v>574548</v>
       </c>
       <c r="R21" t="n">
-        <v>7088573</v>
+        <v>7088558</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3300,53 +3300,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128339483</v>
+        <v>128340549</v>
       </c>
       <c r="B27" t="n">
-        <v>56876</v>
+        <v>90485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574580</v>
+        <v>574555</v>
       </c>
       <c r="R27" t="n">
-        <v>7088751</v>
+        <v>7088647</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3373,9 +3368,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3390,60 +3395,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128340549</v>
+        <v>128339483</v>
       </c>
       <c r="B28" t="n">
-        <v>90485</v>
+        <v>56876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574555</v>
+        <v>574580</v>
       </c>
       <c r="R28" t="n">
-        <v>7088647</v>
+        <v>7088751</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3470,19 +3480,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3497,12 +3497,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3967,48 +3967,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339640</v>
+        <v>128343108</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>56876</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574554</v>
+        <v>574486</v>
       </c>
       <c r="R33" t="n">
-        <v>7088750</v>
+        <v>7088664</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,19 +4040,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:52</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,22 +4062,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339462</v>
+        <v>128340784</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>92770</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,13 +4109,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574615</v>
+        <v>574541</v>
       </c>
       <c r="R34" t="n">
-        <v>7088761</v>
+        <v>7088525</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4142,19 +4142,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4169,44 +4159,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339234</v>
+        <v>128339640</v>
       </c>
       <c r="B35" t="n">
-        <v>80092</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,13 +4206,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574647</v>
+        <v>574554</v>
       </c>
       <c r="R35" t="n">
-        <v>7088700</v>
+        <v>7088750</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4249,9 +4239,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4266,19 +4266,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343025</v>
+        <v>128339462</v>
       </c>
       <c r="B36" t="n">
         <v>79083</v>
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574482</v>
+        <v>574615</v>
       </c>
       <c r="R36" t="n">
-        <v>7088688</v>
+        <v>7088761</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4346,9 +4346,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4363,22 +4373,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128340784</v>
+        <v>128343025</v>
       </c>
       <c r="B37" t="n">
-        <v>92770</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4386,21 +4396,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4410,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574541</v>
+        <v>574482</v>
       </c>
       <c r="R37" t="n">
-        <v>7088525</v>
+        <v>7088688</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4472,53 +4482,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128339517</v>
+        <v>128339234</v>
       </c>
       <c r="B38" t="n">
-        <v>57682</v>
+        <v>80092</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574599</v>
+        <v>574647</v>
       </c>
       <c r="R38" t="n">
-        <v>7088725</v>
+        <v>7088700</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4545,19 +4550,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4572,50 +4567,50 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128343108</v>
+        <v>128339517</v>
       </c>
       <c r="B39" t="n">
-        <v>56876</v>
+        <v>57682</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4624,13 +4619,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574486</v>
+        <v>574599</v>
       </c>
       <c r="R39" t="n">
-        <v>7088664</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4657,14 +4652,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Grop</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,22 +4679,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128340357</v>
+        <v>128340692</v>
       </c>
       <c r="B40" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,34 +4702,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574526</v>
+        <v>574557</v>
       </c>
       <c r="R40" t="n">
-        <v>7088741</v>
+        <v>7088560</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4762,6 +4767,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4788,10 +4798,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128339243</v>
+        <v>128340357</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,21 +4809,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4823,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574646</v>
+        <v>574526</v>
       </c>
       <c r="R41" t="n">
-        <v>7088700</v>
+        <v>7088741</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4885,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340692</v>
+        <v>128339243</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4896,39 +4906,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574557</v>
+        <v>574646</v>
       </c>
       <c r="R42" t="n">
-        <v>7088560</v>
+        <v>7088700</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4961,11 +4966,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,10 +4992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128340649</v>
+        <v>128341581</v>
       </c>
       <c r="B43" t="n">
-        <v>79702</v>
+        <v>78749</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,13 +5027,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574573</v>
+        <v>574445</v>
       </c>
       <c r="R43" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5060,19 +5060,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5087,44 +5077,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128341581</v>
+        <v>128339546</v>
       </c>
       <c r="B44" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5134,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574445</v>
+        <v>574558</v>
       </c>
       <c r="R44" t="n">
-        <v>7088593</v>
+        <v>7088774</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5196,32 +5186,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128339546</v>
+        <v>128340722</v>
       </c>
       <c r="B45" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,13 +5221,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574558</v>
+        <v>574563</v>
       </c>
       <c r="R45" t="n">
-        <v>7088774</v>
+        <v>7088549</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5264,9 +5254,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5281,22 +5281,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128339432</v>
+        <v>128340649</v>
       </c>
       <c r="B46" t="n">
-        <v>57685</v>
+        <v>79702</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5304,39 +5304,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574618</v>
+        <v>574573</v>
       </c>
       <c r="R46" t="n">
-        <v>7088746</v>
+        <v>7088640</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5368,7 +5363,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5378,12 +5373,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5410,32 +5400,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128339678</v>
+        <v>128339432</v>
       </c>
       <c r="B47" t="n">
-        <v>56876</v>
+        <v>57685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5450,13 +5440,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574545</v>
+        <v>574618</v>
       </c>
       <c r="R47" t="n">
-        <v>7088725</v>
+        <v>7088746</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5483,14 +5473,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Sandbad och spillning</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5505,60 +5505,65 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128340722</v>
+        <v>128339678</v>
       </c>
       <c r="B48" t="n">
-        <v>80188</v>
+        <v>56876</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574563</v>
+        <v>574545</v>
       </c>
       <c r="R48" t="n">
-        <v>7088549</v>
+        <v>7088725</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5585,19 +5590,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:31</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340602</v>
+        <v>128341658</v>
       </c>
       <c r="B50" t="n">
-        <v>92767</v>
+        <v>78749</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R50" t="n">
-        <v>7088642</v>
+        <v>7088595</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,19 +5809,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,44 +5826,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340512</v>
+        <v>128340602</v>
       </c>
       <c r="B51" t="n">
-        <v>92742</v>
+        <v>92767</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5883,10 +5873,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574550</v>
+        <v>574553</v>
       </c>
       <c r="R51" t="n">
-        <v>7088660</v>
+        <v>7088642</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5918,7 +5908,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5928,7 +5918,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5955,10 +5945,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B52" t="n">
-        <v>80224</v>
+        <v>92742</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,21 +5956,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5990,13 +5980,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R52" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6023,9 +6013,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6040,62 +6040,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128339103</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>57685</v>
+        <v>80224</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6128,11 +6123,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6159,7 +6149,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339352</v>
+        <v>128339103</v>
       </c>
       <c r="B54" t="n">
         <v>57685</v>
@@ -6199,13 +6189,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574614</v>
+        <v>574625</v>
       </c>
       <c r="R54" t="n">
-        <v>7088680</v>
+        <v>7088640</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6232,24 +6222,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6264,22 +6244,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341658</v>
+        <v>128339352</v>
       </c>
       <c r="B55" t="n">
-        <v>78749</v>
+        <v>57685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6287,37 +6267,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574614</v>
       </c>
       <c r="R55" t="n">
-        <v>7088595</v>
+        <v>7088680</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6344,9 +6329,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,65 +6361,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339538</v>
+        <v>128339624</v>
       </c>
       <c r="B56" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574598</v>
+        <v>574580</v>
       </c>
       <c r="R56" t="n">
-        <v>7088728</v>
+        <v>7088767</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6446,24 +6441,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6478,44 +6458,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339188</v>
+        <v>128341588</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6525,13 +6505,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574647</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088696</v>
+        <v>7088594</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6558,19 +6538,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6585,44 +6555,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339624</v>
+        <v>128339188</v>
       </c>
       <c r="B58" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6632,13 +6602,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574580</v>
+        <v>574647</v>
       </c>
       <c r="R58" t="n">
-        <v>7088767</v>
+        <v>7088696</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6665,9 +6635,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6682,19 +6662,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128341588</v>
+        <v>128339929</v>
       </c>
       <c r="B59" t="n">
         <v>92742</v>
@@ -6729,13 +6709,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574445</v>
+        <v>574555</v>
       </c>
       <c r="R59" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6762,9 +6742,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6779,57 +6769,62 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339929</v>
+        <v>128339538</v>
       </c>
       <c r="B60" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574555</v>
+        <v>574598</v>
       </c>
       <c r="R60" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6861,7 +6856,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6871,7 +6866,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128340645</v>
+        <v>128339617</v>
       </c>
       <c r="B63" t="n">
-        <v>78840</v>
+        <v>57685</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,34 +7123,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574571</v>
+        <v>574563</v>
       </c>
       <c r="R63" t="n">
-        <v>7088636</v>
+        <v>7088745</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7182,7 +7187,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7192,7 +7197,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7207,12 +7217,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7316,10 +7326,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128339617</v>
+        <v>128343065</v>
       </c>
       <c r="B65" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7327,42 +7337,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574563</v>
+        <v>574485</v>
       </c>
       <c r="R65" t="n">
-        <v>7088745</v>
+        <v>7088660</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7389,24 +7394,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7421,22 +7411,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128343065</v>
+        <v>128340645</v>
       </c>
       <c r="B66" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,21 +7434,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7468,13 +7458,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574485</v>
+        <v>574571</v>
       </c>
       <c r="R66" t="n">
-        <v>7088660</v>
+        <v>7088636</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7501,9 +7491,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7861,48 +7861,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128339554</v>
+        <v>128340670</v>
       </c>
       <c r="B70" t="n">
-        <v>80216</v>
+        <v>57685</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574560</v>
+        <v>574568</v>
       </c>
       <c r="R70" t="n">
-        <v>7088771</v>
+        <v>7088607</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7929,9 +7934,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7946,22 +7966,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340639</v>
+        <v>128340933</v>
       </c>
       <c r="B71" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7969,34 +7989,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574574</v>
+        <v>574498</v>
       </c>
       <c r="R71" t="n">
-        <v>7088635</v>
+        <v>7088556</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8028,7 +8053,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8038,7 +8063,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8053,22 +8083,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340563</v>
+        <v>128341109</v>
       </c>
       <c r="B72" t="n">
-        <v>92935</v>
+        <v>57685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8076,34 +8106,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574549</v>
+        <v>574429</v>
       </c>
       <c r="R72" t="n">
-        <v>7088658</v>
+        <v>7088591</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8135,7 +8170,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8145,7 +8180,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8160,22 +8200,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340363</v>
+        <v>128340344</v>
       </c>
       <c r="B73" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8183,37 +8223,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574523</v>
+        <v>574557</v>
       </c>
       <c r="R73" t="n">
-        <v>7088723</v>
+        <v>7088695</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8240,9 +8285,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8257,22 +8317,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340670</v>
+        <v>128340639</v>
       </c>
       <c r="B74" t="n">
-        <v>57685</v>
+        <v>78841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8280,39 +8340,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574568</v>
+        <v>574574</v>
       </c>
       <c r="R74" t="n">
-        <v>7088607</v>
+        <v>7088635</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8357,11 +8412,6 @@
           <t>16:22</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8374,22 +8424,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128340933</v>
+        <v>128340363</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8397,42 +8447,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574498</v>
+        <v>574523</v>
       </c>
       <c r="R75" t="n">
-        <v>7088556</v>
+        <v>7088723</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8459,24 +8504,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8491,65 +8521,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128341109</v>
+        <v>128339554</v>
       </c>
       <c r="B76" t="n">
-        <v>57685</v>
+        <v>80216</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574429</v>
+        <v>574560</v>
       </c>
       <c r="R76" t="n">
-        <v>7088591</v>
+        <v>7088771</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8576,24 +8601,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8608,22 +8618,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128340344</v>
+        <v>128340563</v>
       </c>
       <c r="B77" t="n">
-        <v>57685</v>
+        <v>92935</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8631,39 +8641,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574557</v>
+        <v>574549</v>
       </c>
       <c r="R77" t="n">
-        <v>7088695</v>
+        <v>7088658</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8695,7 +8700,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8705,12 +8710,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8725,12 +8725,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338916</v>
+        <v>128340579</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>56876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574622</v>
+        <v>574542</v>
       </c>
       <c r="R3" t="n">
-        <v>7088618</v>
+        <v>7088660</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,14 +855,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340579</v>
+        <v>128339514</v>
       </c>
       <c r="B4" t="n">
         <v>56876</v>
@@ -918,9 +928,14 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574542</v>
+        <v>574577</v>
       </c>
       <c r="R4" t="n">
-        <v>7088660</v>
+        <v>7088748</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,24 +977,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,55 +994,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128339514</v>
+        <v>128338916</v>
       </c>
       <c r="B5" t="n">
-        <v>56876</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1051,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574577</v>
+        <v>574622</v>
       </c>
       <c r="R5" t="n">
-        <v>7088748</v>
+        <v>7088618</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339216</v>
+        <v>128340568</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>78749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,42 +1231,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574620</v>
+        <v>574551</v>
       </c>
       <c r="R7" t="n">
-        <v>7088666</v>
+        <v>7088652</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,24 +1288,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340568</v>
+        <v>128340410</v>
       </c>
       <c r="B8" t="n">
-        <v>78749</v>
+        <v>92758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574551</v>
+        <v>574543</v>
       </c>
       <c r="R8" t="n">
-        <v>7088652</v>
+        <v>7088692</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,9 +1385,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340410</v>
+        <v>128339216</v>
       </c>
       <c r="B9" t="n">
-        <v>92758</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574543</v>
+        <v>574620</v>
       </c>
       <c r="R9" t="n">
-        <v>7088692</v>
+        <v>7088666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,12 +1529,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1862,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340548</v>
+        <v>128343119</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574550</v>
+        <v>574495</v>
       </c>
       <c r="R13" t="n">
-        <v>7088658</v>
+        <v>7088662</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,19 +1930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,60 +1947,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128339006</v>
+        <v>128340548</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574657</v>
+        <v>574550</v>
       </c>
       <c r="R14" t="n">
-        <v>7088628</v>
+        <v>7088658</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,9 +2027,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,19 +2054,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343119</v>
+        <v>128339006</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -2097,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574495</v>
+        <v>574657</v>
       </c>
       <c r="R15" t="n">
-        <v>7088662</v>
+        <v>7088628</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2163,48 +2163,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R16" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,19 +2231,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,60 +2248,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2328,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2969,48 +2969,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128341564</v>
+        <v>128339039</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574445</v>
+        <v>574613</v>
       </c>
       <c r="R24" t="n">
-        <v>7088593</v>
+        <v>7088652</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,9 +3042,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3054,19 +3074,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128339039</v>
+        <v>128338853</v>
       </c>
       <c r="B25" t="n">
         <v>57685</v>
@@ -3097,19 +3117,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574613</v>
+        <v>574647</v>
       </c>
       <c r="R25" t="n">
-        <v>7088652</v>
+        <v>7088580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3161,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3151,7 +3171,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3171,65 +3191,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338853</v>
+        <v>128341564</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574647</v>
+        <v>574445</v>
       </c>
       <c r="R26" t="n">
-        <v>7088580</v>
+        <v>7088593</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3256,24 +3271,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,12 +3288,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339483</v>
+        <v>128340667</v>
       </c>
       <c r="B28" t="n">
-        <v>56876</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3418,42 +3418,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574580</v>
+        <v>574565</v>
       </c>
       <c r="R28" t="n">
-        <v>7088751</v>
+        <v>7088619</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3480,9 +3475,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3497,22 +3502,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128340667</v>
+        <v>128339483</v>
       </c>
       <c r="B29" t="n">
-        <v>92742</v>
+        <v>56876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,37 +3525,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574565</v>
+        <v>574580</v>
       </c>
       <c r="R29" t="n">
-        <v>7088619</v>
+        <v>7088751</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3577,19 +3587,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,12 +3604,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128343108</v>
+        <v>128339234</v>
       </c>
       <c r="B33" t="n">
-        <v>56876</v>
+        <v>80092</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,39 +3978,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574486</v>
+        <v>574647</v>
       </c>
       <c r="R33" t="n">
-        <v>7088664</v>
+        <v>7088700</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4043,11 +4038,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Grop</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128340784</v>
+        <v>128339640</v>
       </c>
       <c r="B34" t="n">
-        <v>92770</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,21 +4075,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,13 +4099,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574541</v>
+        <v>574554</v>
       </c>
       <c r="R34" t="n">
-        <v>7088525</v>
+        <v>7088750</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4142,9 +4132,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4159,19 +4159,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339640</v>
+        <v>128339462</v>
       </c>
       <c r="B35" t="n">
         <v>79083</v>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574554</v>
+        <v>574615</v>
       </c>
       <c r="R35" t="n">
-        <v>7088750</v>
+        <v>7088761</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339462</v>
+        <v>128343025</v>
       </c>
       <c r="B36" t="n">
         <v>79083</v>
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574615</v>
+        <v>574482</v>
       </c>
       <c r="R36" t="n">
-        <v>7088761</v>
+        <v>7088688</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4346,19 +4346,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4373,22 +4363,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343025</v>
+        <v>128339517</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4396,37 +4386,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574482</v>
+        <v>574599</v>
       </c>
       <c r="R37" t="n">
-        <v>7088688</v>
+        <v>7088725</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4453,9 +4448,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4470,44 +4475,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128339234</v>
+        <v>128340784</v>
       </c>
       <c r="B38" t="n">
-        <v>80092</v>
+        <v>92770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4517,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574647</v>
+        <v>574541</v>
       </c>
       <c r="R38" t="n">
-        <v>7088700</v>
+        <v>7088525</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4579,38 +4584,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128339517</v>
+        <v>128343108</v>
       </c>
       <c r="B39" t="n">
-        <v>57682</v>
+        <v>56876</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4619,13 +4624,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574599</v>
+        <v>574486</v>
       </c>
       <c r="R39" t="n">
-        <v>7088725</v>
+        <v>7088664</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4652,19 +4657,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,22 +4679,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128340692</v>
+        <v>128339243</v>
       </c>
       <c r="B40" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,39 +4702,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574557</v>
+        <v>574646</v>
       </c>
       <c r="R40" t="n">
-        <v>7088560</v>
+        <v>7088700</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4767,11 +4762,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128339243</v>
+        <v>128340692</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,34 +4896,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574646</v>
+        <v>574557</v>
       </c>
       <c r="R42" t="n">
-        <v>7088700</v>
+        <v>7088560</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4966,6 +4961,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5089,32 +5089,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128339546</v>
+        <v>128340722</v>
       </c>
       <c r="B44" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,13 +5124,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574558</v>
+        <v>574563</v>
       </c>
       <c r="R44" t="n">
-        <v>7088774</v>
+        <v>7088549</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5157,9 +5157,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5174,22 +5184,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128340722</v>
+        <v>128340649</v>
       </c>
       <c r="B45" t="n">
-        <v>80188</v>
+        <v>79702</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5197,21 +5207,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5221,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574563</v>
+        <v>574573</v>
       </c>
       <c r="R45" t="n">
-        <v>7088549</v>
+        <v>7088640</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5256,7 +5266,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5266,7 +5276,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,10 +5303,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128340649</v>
+        <v>128339432</v>
       </c>
       <c r="B46" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5304,34 +5314,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574573</v>
+        <v>574618</v>
       </c>
       <c r="R46" t="n">
-        <v>7088640</v>
+        <v>7088746</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5363,7 +5378,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5373,7 +5388,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5400,32 +5420,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128339432</v>
+        <v>128339678</v>
       </c>
       <c r="B47" t="n">
-        <v>57685</v>
+        <v>56876</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,13 +5460,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574618</v>
+        <v>574545</v>
       </c>
       <c r="R47" t="n">
-        <v>7088746</v>
+        <v>7088725</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5473,24 +5493,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5505,22 +5515,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128339678</v>
+        <v>128339546</v>
       </c>
       <c r="B48" t="n">
-        <v>56876</v>
+        <v>92742</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5528,39 +5538,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574545</v>
+        <v>574558</v>
       </c>
       <c r="R48" t="n">
-        <v>7088725</v>
+        <v>7088774</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5593,11 +5598,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5741,32 +5741,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128341658</v>
+        <v>128340512</v>
       </c>
       <c r="B50" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R50" t="n">
-        <v>7088595</v>
+        <v>7088660</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,9 +5809,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5826,12 +5836,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5945,10 +5955,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128340512</v>
+        <v>128341543</v>
       </c>
       <c r="B52" t="n">
-        <v>92742</v>
+        <v>80224</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5956,21 +5966,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5980,13 +5990,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R52" t="n">
-        <v>7088660</v>
+        <v>7088593</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6013,19 +6023,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6040,57 +6040,62 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128339103</v>
       </c>
       <c r="B53" t="n">
-        <v>80224</v>
+        <v>57685</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574625</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088640</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6123,6 +6128,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6149,7 +6159,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339103</v>
+        <v>128339352</v>
       </c>
       <c r="B54" t="n">
         <v>57685</v>
@@ -6189,13 +6199,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574625</v>
+        <v>574614</v>
       </c>
       <c r="R54" t="n">
-        <v>7088640</v>
+        <v>7088680</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6222,14 +6232,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre och färska spår</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6244,22 +6264,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128339352</v>
+        <v>128341658</v>
       </c>
       <c r="B55" t="n">
-        <v>57685</v>
+        <v>78749</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6267,42 +6287,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574614</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088680</v>
+        <v>7088595</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6329,24 +6344,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,44 +6361,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339624</v>
+        <v>128339188</v>
       </c>
       <c r="B56" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574580</v>
+        <v>574647</v>
       </c>
       <c r="R56" t="n">
-        <v>7088767</v>
+        <v>7088696</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,9 +6441,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6458,12 +6468,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6567,32 +6577,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339188</v>
+        <v>128339624</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6602,13 +6612,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574647</v>
+        <v>574580</v>
       </c>
       <c r="R58" t="n">
-        <v>7088696</v>
+        <v>7088767</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6635,19 +6645,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6662,12 +6662,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128339617</v>
+        <v>128343065</v>
       </c>
       <c r="B63" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,42 +7123,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574563</v>
+        <v>574485</v>
       </c>
       <c r="R63" t="n">
-        <v>7088745</v>
+        <v>7088660</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7185,24 +7180,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7217,12 +7197,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7326,10 +7306,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128343065</v>
+        <v>128339617</v>
       </c>
       <c r="B65" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7337,37 +7317,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574485</v>
+        <v>574563</v>
       </c>
       <c r="R65" t="n">
-        <v>7088660</v>
+        <v>7088745</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7394,9 +7379,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,12 +7411,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340670</v>
+        <v>128340563</v>
       </c>
       <c r="B70" t="n">
-        <v>57685</v>
+        <v>92935</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,39 +7872,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574568</v>
+        <v>574549</v>
       </c>
       <c r="R70" t="n">
-        <v>7088607</v>
+        <v>7088658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7936,7 +7931,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7946,12 +7941,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7966,19 +7956,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340933</v>
+        <v>128340670</v>
       </c>
       <c r="B71" t="n">
         <v>57685</v>
@@ -8009,7 +7999,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8018,10 +8008,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574498</v>
+        <v>574568</v>
       </c>
       <c r="R71" t="n">
-        <v>7088556</v>
+        <v>7088607</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8053,7 +8043,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8063,7 +8053,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8095,7 +8085,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128341109</v>
+        <v>128340933</v>
       </c>
       <c r="B72" t="n">
         <v>57685</v>
@@ -8135,10 +8125,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574429</v>
+        <v>574498</v>
       </c>
       <c r="R72" t="n">
-        <v>7088591</v>
+        <v>7088556</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8170,7 +8160,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8180,7 +8170,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8212,7 +8202,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340344</v>
+        <v>128341109</v>
       </c>
       <c r="B73" t="n">
         <v>57685</v>
@@ -8252,10 +8242,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574557</v>
+        <v>574429</v>
       </c>
       <c r="R73" t="n">
-        <v>7088695</v>
+        <v>7088591</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8287,7 +8277,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8297,7 +8287,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8329,10 +8319,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340639</v>
+        <v>128340344</v>
       </c>
       <c r="B74" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8340,34 +8330,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574574</v>
+        <v>574557</v>
       </c>
       <c r="R74" t="n">
-        <v>7088635</v>
+        <v>7088695</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8399,7 +8394,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8409,7 +8404,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8424,22 +8424,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128340363</v>
+        <v>128340639</v>
       </c>
       <c r="B75" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8471,13 +8471,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574523</v>
+        <v>574574</v>
       </c>
       <c r="R75" t="n">
-        <v>7088723</v>
+        <v>7088635</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8504,9 +8504,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8521,44 +8531,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128339554</v>
+        <v>128340363</v>
       </c>
       <c r="B76" t="n">
-        <v>80216</v>
+        <v>79083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8568,10 +8578,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574560</v>
+        <v>574523</v>
       </c>
       <c r="R76" t="n">
-        <v>7088771</v>
+        <v>7088723</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8630,32 +8640,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128340563</v>
+        <v>128339554</v>
       </c>
       <c r="B77" t="n">
-        <v>92935</v>
+        <v>80216</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8665,13 +8675,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574549</v>
+        <v>574560</v>
       </c>
       <c r="R77" t="n">
-        <v>7088658</v>
+        <v>7088771</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8698,19 +8708,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8725,12 +8725,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128343119</v>
+        <v>128339006</v>
       </c>
       <c r="B13" t="n">
         <v>79083</v>
@@ -1893,14 +1893,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574495</v>
+        <v>574657</v>
       </c>
       <c r="R13" t="n">
-        <v>7088662</v>
+        <v>7088628</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340548</v>
+        <v>128343119</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574550</v>
+        <v>574495</v>
       </c>
       <c r="R14" t="n">
-        <v>7088658</v>
+        <v>7088662</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2027,19 +2027,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,60 +2044,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128339006</v>
+        <v>128340548</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574657</v>
+        <v>574550</v>
       </c>
       <c r="R15" t="n">
-        <v>7088628</v>
+        <v>7088658</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,9 +2124,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,12 +2151,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3300,48 +3300,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128340549</v>
+        <v>128339483</v>
       </c>
       <c r="B27" t="n">
-        <v>90485</v>
+        <v>56876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574555</v>
+        <v>574580</v>
       </c>
       <c r="R27" t="n">
-        <v>7088647</v>
+        <v>7088751</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3368,19 +3373,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3395,57 +3390,62 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128340667</v>
+        <v>128339278</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574565</v>
+        <v>574615</v>
       </c>
       <c r="R28" t="n">
-        <v>7088619</v>
+        <v>7088675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3487,7 +3487,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3502,44 +3507,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339483</v>
+        <v>128339431</v>
       </c>
       <c r="B29" t="n">
-        <v>56876</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,13 +3559,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574580</v>
+        <v>574614</v>
       </c>
       <c r="R29" t="n">
-        <v>7088751</v>
+        <v>7088709</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3587,9 +3592,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,19 +3624,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128339278</v>
+        <v>128338795</v>
       </c>
       <c r="B30" t="n">
         <v>57685</v>
@@ -3652,14 +3672,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574615</v>
+        <v>574657</v>
       </c>
       <c r="R30" t="n">
-        <v>7088675</v>
+        <v>7088592</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3691,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3701,12 +3721,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,22 +3741,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339431</v>
+        <v>128340549</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>90485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,39 +3764,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574614</v>
+        <v>574555</v>
       </c>
       <c r="R31" t="n">
-        <v>7088709</v>
+        <v>7088647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3823,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,12 +3833,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3838,62 +3848,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338795</v>
+        <v>128340667</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574657</v>
+        <v>574565</v>
       </c>
       <c r="R32" t="n">
-        <v>7088592</v>
+        <v>7088619</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,12 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,32 +3967,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339234</v>
+        <v>128343025</v>
       </c>
       <c r="B33" t="n">
-        <v>80092</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574647</v>
+        <v>574482</v>
       </c>
       <c r="R33" t="n">
-        <v>7088700</v>
+        <v>7088688</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339640</v>
+        <v>128339517</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4075,37 +4075,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574554</v>
+        <v>574599</v>
       </c>
       <c r="R34" t="n">
-        <v>7088750</v>
+        <v>7088725</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4134,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4144,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4159,22 +4164,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339462</v>
+        <v>128340784</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>92770</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4182,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4206,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574615</v>
+        <v>574541</v>
       </c>
       <c r="R35" t="n">
-        <v>7088761</v>
+        <v>7088525</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4239,19 +4244,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4266,57 +4261,62 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343025</v>
+        <v>128343108</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>56876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574482</v>
+        <v>574486</v>
       </c>
       <c r="R36" t="n">
-        <v>7088688</v>
+        <v>7088664</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4349,6 +4349,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,53 +4380,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128339517</v>
+        <v>128339234</v>
       </c>
       <c r="B37" t="n">
-        <v>57682</v>
+        <v>80092</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574599</v>
+        <v>574647</v>
       </c>
       <c r="R37" t="n">
-        <v>7088725</v>
+        <v>7088700</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4448,19 +4448,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,22 +4465,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128340784</v>
+        <v>128339640</v>
       </c>
       <c r="B38" t="n">
-        <v>92770</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4498,21 +4488,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,13 +4512,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574541</v>
+        <v>574554</v>
       </c>
       <c r="R38" t="n">
-        <v>7088525</v>
+        <v>7088750</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4555,9 +4545,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4572,65 +4572,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128343108</v>
+        <v>128339462</v>
       </c>
       <c r="B39" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574486</v>
+        <v>574615</v>
       </c>
       <c r="R39" t="n">
-        <v>7088664</v>
+        <v>7088761</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4657,14 +4652,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Grop</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,22 +4679,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128339243</v>
+        <v>128340692</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,34 +4702,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574646</v>
+        <v>574557</v>
       </c>
       <c r="R40" t="n">
-        <v>7088700</v>
+        <v>7088560</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4762,6 +4767,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4788,10 +4798,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128340357</v>
+        <v>128339243</v>
       </c>
       <c r="B41" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,21 +4809,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4823,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574526</v>
+        <v>574646</v>
       </c>
       <c r="R41" t="n">
-        <v>7088741</v>
+        <v>7088700</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4885,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340692</v>
+        <v>128340357</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>79702</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4896,39 +4906,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574557</v>
+        <v>574526</v>
       </c>
       <c r="R42" t="n">
-        <v>7088560</v>
+        <v>7088741</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4961,11 +4966,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6480,7 +6480,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341588</v>
+        <v>128339624</v>
       </c>
       <c r="B57" t="n">
         <v>92742</v>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574445</v>
+        <v>574580</v>
       </c>
       <c r="R57" t="n">
-        <v>7088594</v>
+        <v>7088767</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6577,7 +6577,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339624</v>
+        <v>128339929</v>
       </c>
       <c r="B58" t="n">
         <v>92742</v>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574580</v>
+        <v>574555</v>
       </c>
       <c r="R58" t="n">
-        <v>7088767</v>
+        <v>7088696</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6645,9 +6645,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6662,57 +6672,62 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339929</v>
+        <v>128339538</v>
       </c>
       <c r="B59" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574555</v>
+        <v>574598</v>
       </c>
       <c r="R59" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6744,7 +6759,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6754,7 +6769,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6781,53 +6801,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339538</v>
+        <v>128341588</v>
       </c>
       <c r="B60" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574598</v>
+        <v>574445</v>
       </c>
       <c r="R60" t="n">
-        <v>7088728</v>
+        <v>7088594</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6854,24 +6869,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,12 +6886,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7530,32 +7530,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341241</v>
+        <v>128342808</v>
       </c>
       <c r="B67" t="n">
-        <v>92758</v>
+        <v>80217</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574529</v>
+        <v>574453</v>
       </c>
       <c r="R67" t="n">
-        <v>7088560</v>
+        <v>7088593</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7625,57 +7625,62 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128342808</v>
+        <v>128339467</v>
       </c>
       <c r="B68" t="n">
-        <v>80217</v>
+        <v>57685</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574453</v>
+        <v>574607</v>
       </c>
       <c r="R68" t="n">
-        <v>7088593</v>
+        <v>7088708</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7707,7 +7712,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7717,7 +7722,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7744,10 +7754,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128339467</v>
+        <v>128341241</v>
       </c>
       <c r="B69" t="n">
-        <v>57685</v>
+        <v>92758</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7755,39 +7765,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574607</v>
+        <v>574529</v>
       </c>
       <c r="R69" t="n">
-        <v>7088708</v>
+        <v>7088560</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7819,7 +7824,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7829,12 +7834,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7849,12 +7849,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8737,48 +8737,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128340367</v>
+        <v>128339415</v>
       </c>
       <c r="B78" t="n">
-        <v>96696</v>
+        <v>57685</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>574519</v>
+        <v>574618</v>
       </c>
       <c r="R78" t="n">
-        <v>7088716</v>
+        <v>7088747</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,9 +8810,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8822,65 +8842,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128339415</v>
+        <v>128340367</v>
       </c>
       <c r="B79" t="n">
-        <v>57685</v>
+        <v>96696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574618</v>
+        <v>574519</v>
       </c>
       <c r="R79" t="n">
-        <v>7088747</v>
+        <v>7088716</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8907,24 +8922,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8939,12 +8939,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340643</v>
+        <v>128340579</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>56880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574570</v>
+        <v>574542</v>
       </c>
       <c r="R2" t="n">
-        <v>7088645</v>
+        <v>7088660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340579</v>
+        <v>128339514</v>
       </c>
       <c r="B3" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,9 +821,14 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574542</v>
+        <v>574577</v>
       </c>
       <c r="R3" t="n">
-        <v>7088660</v>
+        <v>7088748</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,24 +870,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,55 +887,50 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128339514</v>
+        <v>128338916</v>
       </c>
       <c r="B4" t="n">
-        <v>56876</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574577</v>
+        <v>574622</v>
       </c>
       <c r="R4" t="n">
-        <v>7088748</v>
+        <v>7088618</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,53 +1006,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338916</v>
+        <v>128340643</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574622</v>
+        <v>574570</v>
       </c>
       <c r="R5" t="n">
-        <v>7088618</v>
+        <v>7088645</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,14 +1074,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,57 +1101,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128341140</v>
+        <v>128339216</v>
       </c>
       <c r="B6" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574438</v>
+        <v>574620</v>
       </c>
       <c r="R6" t="n">
-        <v>7088595</v>
+        <v>7088666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340568</v>
+        <v>128341140</v>
       </c>
       <c r="B7" t="n">
-        <v>78749</v>
+        <v>92754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574551</v>
+        <v>574438</v>
       </c>
       <c r="R7" t="n">
-        <v>7088652</v>
+        <v>7088595</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,9 +1298,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1320,7 +1340,7 @@
         <v>128340410</v>
       </c>
       <c r="B8" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128339216</v>
+        <v>128340568</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>78753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,42 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574620</v>
+        <v>574551</v>
       </c>
       <c r="R9" t="n">
-        <v>7088666</v>
+        <v>7088652</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,24 +1512,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B10" t="n">
-        <v>78749</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R10" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341194</v>
+        <v>128342806</v>
       </c>
       <c r="B11" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574533</v>
+        <v>574452</v>
       </c>
       <c r="R11" t="n">
-        <v>7088534</v>
+        <v>7088593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342806</v>
+        <v>128339922</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>78753</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574452</v>
+        <v>574537</v>
       </c>
       <c r="R12" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,12 +1850,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1865,7 +1865,7 @@
         <v>128339006</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128343119</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>128340548</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,45 +2163,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340635</v>
+        <v>128341646</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574554</v>
+        <v>574445</v>
       </c>
       <c r="R16" t="n">
-        <v>7088634</v>
+        <v>7088594</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2234,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,48 +2270,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,19 +2338,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,22 +2355,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341646</v>
+        <v>128338970</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,42 +2378,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574445</v>
+        <v>574649</v>
       </c>
       <c r="R18" t="n">
-        <v>7088594</v>
+        <v>7088609</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,14 +2435,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,22 +2462,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340679</v>
+        <v>128340725</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574565</v>
+        <v>574548</v>
       </c>
       <c r="R19" t="n">
-        <v>7088589</v>
+        <v>7088558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,32 +2571,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128343851</v>
+        <v>128340679</v>
       </c>
       <c r="B20" t="n">
-        <v>92736</v>
+        <v>92754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574522</v>
+        <v>574565</v>
       </c>
       <c r="R20" t="n">
-        <v>7088573</v>
+        <v>7088589</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,32 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128340725</v>
+        <v>128343851</v>
       </c>
       <c r="B21" t="n">
-        <v>80217</v>
+        <v>92748</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574548</v>
+        <v>574522</v>
       </c>
       <c r="R21" t="n">
-        <v>7088558</v>
+        <v>7088573</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2768,7 +2768,7 @@
         <v>128341522</v>
       </c>
       <c r="B22" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,32 +2862,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128340360</v>
+        <v>128341564</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574548</v>
+        <v>574445</v>
       </c>
       <c r="R23" t="n">
-        <v>7088705</v>
+        <v>7088593</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,19 +2930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,22 +2947,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128339039</v>
+        <v>128340360</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,39 +2970,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574613</v>
+        <v>574548</v>
       </c>
       <c r="R24" t="n">
-        <v>7088652</v>
+        <v>7088705</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3044,7 +3029,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3054,12 +3039,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,22 +3054,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338853</v>
+        <v>128339039</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,19 +3097,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574647</v>
+        <v>574613</v>
       </c>
       <c r="R25" t="n">
-        <v>7088580</v>
+        <v>7088652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3161,7 +3141,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3171,7 +3151,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3191,60 +3171,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128341564</v>
+        <v>128338853</v>
       </c>
       <c r="B26" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R26" t="n">
-        <v>7088593</v>
+        <v>7088580</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3271,9 +3256,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,22 +3288,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128339483</v>
+        <v>128340667</v>
       </c>
       <c r="B27" t="n">
-        <v>56876</v>
+        <v>92754</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,42 +3311,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574580</v>
+        <v>574565</v>
       </c>
       <c r="R27" t="n">
-        <v>7088751</v>
+        <v>7088619</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3373,9 +3368,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3390,12 +3395,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3405,7 +3410,7 @@
         <v>128339278</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3527,7 @@
         <v>128339431</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3644,7 @@
         <v>128338795</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,48 +3758,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128340549</v>
+        <v>128339483</v>
       </c>
       <c r="B31" t="n">
-        <v>90485</v>
+        <v>56880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574555</v>
+        <v>574580</v>
       </c>
       <c r="R31" t="n">
-        <v>7088647</v>
+        <v>7088751</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3821,19 +3831,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,44 +3848,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128340667</v>
+        <v>128340549</v>
       </c>
       <c r="B32" t="n">
-        <v>92742</v>
+        <v>90497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574565</v>
+        <v>574555</v>
       </c>
       <c r="R32" t="n">
-        <v>7088619</v>
+        <v>7088647</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128343025</v>
+        <v>128339640</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574482</v>
+        <v>574554</v>
       </c>
       <c r="R33" t="n">
-        <v>7088688</v>
+        <v>7088750</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,9 +4035,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,22 +4062,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339517</v>
+        <v>128340784</v>
       </c>
       <c r="B34" t="n">
-        <v>57682</v>
+        <v>92782</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4075,42 +4085,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574599</v>
+        <v>574541</v>
       </c>
       <c r="R34" t="n">
-        <v>7088725</v>
+        <v>7088525</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4137,19 +4142,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,22 +4159,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128340784</v>
+        <v>128339462</v>
       </c>
       <c r="B35" t="n">
-        <v>92770</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,21 +4182,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4206,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574541</v>
+        <v>574615</v>
       </c>
       <c r="R35" t="n">
-        <v>7088525</v>
+        <v>7088761</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4244,9 +4239,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4261,22 +4266,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343108</v>
+        <v>128339234</v>
       </c>
       <c r="B36" t="n">
-        <v>56876</v>
+        <v>80096</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4284,39 +4289,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574486</v>
+        <v>574647</v>
       </c>
       <c r="R36" t="n">
-        <v>7088664</v>
+        <v>7088700</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4349,11 +4349,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Grop</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,32 +4375,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128339234</v>
+        <v>128343025</v>
       </c>
       <c r="B37" t="n">
-        <v>80092</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4415,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574647</v>
+        <v>574482</v>
       </c>
       <c r="R37" t="n">
-        <v>7088700</v>
+        <v>7088688</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4477,48 +4472,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128339640</v>
+        <v>128343108</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>56880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574554</v>
+        <v>574486</v>
       </c>
       <c r="R38" t="n">
-        <v>7088750</v>
+        <v>7088664</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4545,19 +4545,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:52</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4572,22 +4567,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128339462</v>
+        <v>128339517</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4595,37 +4590,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574615</v>
+        <v>574599</v>
       </c>
       <c r="R39" t="n">
-        <v>7088761</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4679,12 +4679,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
         <v>128340692</v>
       </c>
       <c r="B40" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128339243</v>
+        <v>128340357</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,21 +4809,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574646</v>
+        <v>574526</v>
       </c>
       <c r="R41" t="n">
-        <v>7088700</v>
+        <v>7088741</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340357</v>
+        <v>128339243</v>
       </c>
       <c r="B42" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,21 +4906,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574526</v>
+        <v>574646</v>
       </c>
       <c r="R42" t="n">
-        <v>7088741</v>
+        <v>7088700</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4992,45 +4992,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341581</v>
+        <v>128339678</v>
       </c>
       <c r="B43" t="n">
-        <v>78749</v>
+        <v>56880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574445</v>
+        <v>574545</v>
       </c>
       <c r="R43" t="n">
-        <v>7088593</v>
+        <v>7088725</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5063,6 +5068,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5089,32 +5099,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128340722</v>
+        <v>128339546</v>
       </c>
       <c r="B44" t="n">
-        <v>80188</v>
+        <v>92754</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,13 +5134,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574563</v>
+        <v>574558</v>
       </c>
       <c r="R44" t="n">
-        <v>7088549</v>
+        <v>7088774</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5157,19 +5167,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5184,22 +5184,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128340649</v>
+        <v>128339432</v>
       </c>
       <c r="B45" t="n">
-        <v>79702</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5207,34 +5207,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574573</v>
+        <v>574618</v>
       </c>
       <c r="R45" t="n">
-        <v>7088640</v>
+        <v>7088746</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5266,7 +5271,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5276,7 +5281,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5303,10 +5313,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128339432</v>
+        <v>128340649</v>
       </c>
       <c r="B46" t="n">
-        <v>57685</v>
+        <v>79706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5314,39 +5324,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574618</v>
+        <v>574573</v>
       </c>
       <c r="R46" t="n">
-        <v>7088746</v>
+        <v>7088640</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,7 +5383,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5388,12 +5393,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5420,53 +5420,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128339678</v>
+        <v>128340722</v>
       </c>
       <c r="B47" t="n">
-        <v>56876</v>
+        <v>80192</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574545</v>
+        <v>574563</v>
       </c>
       <c r="R47" t="n">
-        <v>7088725</v>
+        <v>7088549</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5493,14 +5488,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5515,44 +5515,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128339546</v>
+        <v>128341581</v>
       </c>
       <c r="B48" t="n">
-        <v>92742</v>
+        <v>78753</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574558</v>
+        <v>574445</v>
       </c>
       <c r="R48" t="n">
-        <v>7088774</v>
+        <v>7088593</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5627,7 +5627,7 @@
         <v>128338962</v>
       </c>
       <c r="B49" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5741,48 +5741,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340512</v>
+        <v>128339103</v>
       </c>
       <c r="B50" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574550</v>
+        <v>574625</v>
       </c>
       <c r="R50" t="n">
-        <v>7088660</v>
+        <v>7088640</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,19 +5814,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,22 +5836,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340602</v>
+        <v>128339352</v>
       </c>
       <c r="B51" t="n">
-        <v>92767</v>
+        <v>57689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5859,34 +5859,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574553</v>
+        <v>574614</v>
       </c>
       <c r="R51" t="n">
-        <v>7088642</v>
+        <v>7088680</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5918,7 +5923,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5928,7 +5933,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5943,22 +5953,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B52" t="n">
-        <v>80224</v>
+        <v>92754</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,21 +5976,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5990,13 +6000,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R52" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6023,9 +6033,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6040,22 +6060,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128339103</v>
+        <v>128341658</v>
       </c>
       <c r="B53" t="n">
-        <v>57685</v>
+        <v>78753</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,39 +6083,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088640</v>
+        <v>7088595</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6128,11 +6143,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6159,10 +6169,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339352</v>
+        <v>128340602</v>
       </c>
       <c r="B54" t="n">
-        <v>57685</v>
+        <v>92779</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6170,39 +6180,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574614</v>
+        <v>574553</v>
       </c>
       <c r="R54" t="n">
-        <v>7088680</v>
+        <v>7088642</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6234,7 +6239,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6244,12 +6249,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6264,44 +6264,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B55" t="n">
-        <v>78749</v>
+        <v>80228</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6314,7 +6314,7 @@
         <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6373,32 +6373,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339188</v>
+        <v>128339624</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574647</v>
+        <v>574580</v>
       </c>
       <c r="R56" t="n">
-        <v>7088696</v>
+        <v>7088767</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,19 +6441,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6468,22 +6458,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339624</v>
+        <v>128341588</v>
       </c>
       <c r="B57" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6515,10 +6505,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574580</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088767</v>
+        <v>7088594</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6580,7 +6570,7 @@
         <v>128339929</v>
       </c>
       <c r="B58" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6687,7 +6677,7 @@
         <v>128339538</v>
       </c>
       <c r="B59" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6801,32 +6791,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128341588</v>
+        <v>128339188</v>
       </c>
       <c r="B60" t="n">
-        <v>92742</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6836,13 +6826,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R60" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6869,9 +6859,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,12 +6886,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6901,7 +6901,7 @@
         <v>128343086</v>
       </c>
       <c r="B61" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>128339543</v>
       </c>
       <c r="B62" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128343065</v>
+        <v>128340020</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>78753</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574485</v>
+        <v>574526</v>
       </c>
       <c r="R63" t="n">
-        <v>7088660</v>
+        <v>7088741</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128340020</v>
+        <v>128339617</v>
       </c>
       <c r="B64" t="n">
-        <v>78749</v>
+        <v>57689</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,37 +7220,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574526</v>
+        <v>574563</v>
       </c>
       <c r="R64" t="n">
-        <v>7088741</v>
+        <v>7088745</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7277,9 +7282,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7294,22 +7314,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128339617</v>
+        <v>128343065</v>
       </c>
       <c r="B65" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7317,42 +7337,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574563</v>
+        <v>574485</v>
       </c>
       <c r="R65" t="n">
-        <v>7088745</v>
+        <v>7088660</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7379,24 +7394,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,12 +7411,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7426,7 +7426,7 @@
         <v>128340645</v>
       </c>
       <c r="B66" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>128342808</v>
       </c>
       <c r="B67" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7637,10 +7637,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128339467</v>
+        <v>128341241</v>
       </c>
       <c r="B68" t="n">
-        <v>57685</v>
+        <v>92770</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7648,39 +7648,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574607</v>
+        <v>574529</v>
       </c>
       <c r="R68" t="n">
-        <v>7088708</v>
+        <v>7088560</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7712,7 +7707,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7722,12 +7717,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7742,22 +7732,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341241</v>
+        <v>128339467</v>
       </c>
       <c r="B69" t="n">
-        <v>92758</v>
+        <v>57689</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7765,34 +7755,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574529</v>
+        <v>574607</v>
       </c>
       <c r="R69" t="n">
-        <v>7088560</v>
+        <v>7088708</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7824,7 +7819,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7834,7 +7829,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7849,22 +7849,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340563</v>
+        <v>128340670</v>
       </c>
       <c r="B70" t="n">
-        <v>92935</v>
+        <v>57689</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,34 +7872,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574549</v>
+        <v>574568</v>
       </c>
       <c r="R70" t="n">
-        <v>7088658</v>
+        <v>7088607</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7931,7 +7936,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7941,7 +7946,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7956,22 +7966,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340670</v>
+        <v>128340933</v>
       </c>
       <c r="B71" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7999,7 +8009,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8008,10 +8018,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574568</v>
+        <v>574498</v>
       </c>
       <c r="R71" t="n">
-        <v>7088607</v>
+        <v>7088556</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8043,7 +8053,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8053,7 +8063,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8085,10 +8095,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340933</v>
+        <v>128341109</v>
       </c>
       <c r="B72" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8125,10 +8135,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574498</v>
+        <v>574429</v>
       </c>
       <c r="R72" t="n">
-        <v>7088556</v>
+        <v>7088591</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8160,7 +8170,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8170,7 +8180,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8202,10 +8212,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128341109</v>
+        <v>128340344</v>
       </c>
       <c r="B73" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8242,10 +8252,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574429</v>
+        <v>574557</v>
       </c>
       <c r="R73" t="n">
-        <v>7088591</v>
+        <v>7088695</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8277,7 +8287,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8287,7 +8297,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8319,10 +8329,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340344</v>
+        <v>128340639</v>
       </c>
       <c r="B74" t="n">
-        <v>57685</v>
+        <v>78845</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8330,39 +8340,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574557</v>
+        <v>574574</v>
       </c>
       <c r="R74" t="n">
-        <v>7088695</v>
+        <v>7088635</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8394,7 +8399,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8404,12 +8409,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8424,22 +8424,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128340639</v>
+        <v>128340363</v>
       </c>
       <c r="B75" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8471,13 +8471,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574574</v>
+        <v>574523</v>
       </c>
       <c r="R75" t="n">
-        <v>7088635</v>
+        <v>7088723</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8504,19 +8504,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8531,44 +8521,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340363</v>
+        <v>128339554</v>
       </c>
       <c r="B76" t="n">
-        <v>79083</v>
+        <v>80220</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8578,10 +8568,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574523</v>
+        <v>574560</v>
       </c>
       <c r="R76" t="n">
-        <v>7088723</v>
+        <v>7088771</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8640,32 +8630,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128339554</v>
+        <v>128340563</v>
       </c>
       <c r="B77" t="n">
-        <v>80216</v>
+        <v>92947</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8675,13 +8665,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574560</v>
+        <v>574549</v>
       </c>
       <c r="R77" t="n">
-        <v>7088771</v>
+        <v>7088658</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8708,9 +8698,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8725,12 +8725,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8740,7 +8740,7 @@
         <v>128339415</v>
       </c>
       <c r="B78" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>128340367</v>
       </c>
       <c r="B79" t="n">
-        <v>96696</v>
+        <v>96708</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -1862,48 +1862,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128339006</v>
+        <v>128340548</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>92754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574657</v>
+        <v>574550</v>
       </c>
       <c r="R13" t="n">
-        <v>7088628</v>
+        <v>7088658</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,9 +1930,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343119</v>
+        <v>128339006</v>
       </c>
       <c r="B14" t="n">
         <v>79087</v>
@@ -1990,14 +2000,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574495</v>
+        <v>574657</v>
       </c>
       <c r="R14" t="n">
-        <v>7088662</v>
+        <v>7088628</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2056,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340548</v>
+        <v>128343119</v>
       </c>
       <c r="B15" t="n">
-        <v>92754</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574550</v>
+        <v>574495</v>
       </c>
       <c r="R15" t="n">
-        <v>7088658</v>
+        <v>7088662</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,19 +2134,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,12 +2151,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128340360</v>
+        <v>128339039</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,34 +2970,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574548</v>
+        <v>574613</v>
       </c>
       <c r="R24" t="n">
-        <v>7088705</v>
+        <v>7088652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3039,7 +3044,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3054,19 +3064,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128339039</v>
+        <v>128338853</v>
       </c>
       <c r="B25" t="n">
         <v>57689</v>
@@ -3097,19 +3107,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574613</v>
+        <v>574647</v>
       </c>
       <c r="R25" t="n">
-        <v>7088652</v>
+        <v>7088580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3151,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3151,7 +3161,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3171,22 +3181,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338853</v>
+        <v>128340360</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,39 +3204,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574647</v>
+        <v>574548</v>
       </c>
       <c r="R26" t="n">
-        <v>7088580</v>
+        <v>7088705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,7 +3263,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,12 +3273,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,32 +3407,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339278</v>
+        <v>128339483</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574615</v>
+        <v>574580</v>
       </c>
       <c r="R28" t="n">
-        <v>7088675</v>
+        <v>7088751</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3480,24 +3480,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3512,22 +3497,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339431</v>
+        <v>128340549</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>90497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,39 +3520,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574614</v>
+        <v>574555</v>
       </c>
       <c r="R29" t="n">
-        <v>7088709</v>
+        <v>7088647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,7 +3579,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3609,12 +3589,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3629,19 +3604,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128338795</v>
+        <v>128339278</v>
       </c>
       <c r="B30" t="n">
         <v>57689</v>
@@ -3677,14 +3652,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574657</v>
+        <v>574615</v>
       </c>
       <c r="R30" t="n">
-        <v>7088592</v>
+        <v>7088675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,7 +3691,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3726,12 +3701,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,44 +3721,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339483</v>
+        <v>128339431</v>
       </c>
       <c r="B31" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,13 +3773,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574580</v>
+        <v>574614</v>
       </c>
       <c r="R31" t="n">
-        <v>7088751</v>
+        <v>7088709</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,9 +3806,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,22 +3838,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128340549</v>
+        <v>128338795</v>
       </c>
       <c r="B32" t="n">
-        <v>90497</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,34 +3861,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574555</v>
+        <v>574657</v>
       </c>
       <c r="R32" t="n">
-        <v>7088647</v>
+        <v>7088592</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3935,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,48 +3967,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339640</v>
+        <v>128343108</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>56880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574554</v>
+        <v>574486</v>
       </c>
       <c r="R33" t="n">
-        <v>7088750</v>
+        <v>7088664</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,19 +4040,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:52</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,22 +4062,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128340784</v>
+        <v>128339517</v>
       </c>
       <c r="B34" t="n">
-        <v>92782</v>
+        <v>57686</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,37 +4085,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574541</v>
+        <v>574599</v>
       </c>
       <c r="R34" t="n">
-        <v>7088525</v>
+        <v>7088725</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4142,9 +4147,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4159,12 +4174,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4472,53 +4487,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128343108</v>
+        <v>128339640</v>
       </c>
       <c r="B38" t="n">
-        <v>56880</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574486</v>
+        <v>574554</v>
       </c>
       <c r="R38" t="n">
-        <v>7088664</v>
+        <v>7088750</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4545,14 +4555,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Grop</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,22 +4582,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128339517</v>
+        <v>128340784</v>
       </c>
       <c r="B39" t="n">
-        <v>57686</v>
+        <v>92782</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4590,42 +4605,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574599</v>
+        <v>574541</v>
       </c>
       <c r="R39" t="n">
-        <v>7088725</v>
+        <v>7088525</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4652,19 +4662,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,22 +4679,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128340692</v>
+        <v>128340357</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>79706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,39 +4702,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574557</v>
+        <v>574526</v>
       </c>
       <c r="R40" t="n">
-        <v>7088560</v>
+        <v>7088741</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4767,11 +4762,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4798,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128340357</v>
+        <v>128339243</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,21 +4799,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4833,10 +4823,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574526</v>
+        <v>574646</v>
       </c>
       <c r="R41" t="n">
-        <v>7088741</v>
+        <v>7088700</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4895,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128339243</v>
+        <v>128340692</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,34 +4896,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574646</v>
+        <v>574557</v>
       </c>
       <c r="R42" t="n">
-        <v>7088700</v>
+        <v>7088560</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4966,6 +4961,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,10 +4992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128339678</v>
+        <v>128339546</v>
       </c>
       <c r="B43" t="n">
-        <v>56880</v>
+        <v>92754</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5003,39 +5003,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574545</v>
+        <v>574558</v>
       </c>
       <c r="R43" t="n">
-        <v>7088725</v>
+        <v>7088774</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5068,11 +5063,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5099,48 +5089,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128339546</v>
+        <v>128339432</v>
       </c>
       <c r="B44" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574558</v>
+        <v>574618</v>
       </c>
       <c r="R44" t="n">
-        <v>7088774</v>
+        <v>7088746</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5167,9 +5162,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5184,22 +5194,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128339432</v>
+        <v>128340649</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>79706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5207,39 +5217,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574618</v>
+        <v>574573</v>
       </c>
       <c r="R45" t="n">
-        <v>7088746</v>
+        <v>7088640</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,7 +5276,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5281,12 +5286,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5313,10 +5313,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128340649</v>
+        <v>128341581</v>
       </c>
       <c r="B46" t="n">
-        <v>79706</v>
+        <v>78753</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5324,21 +5324,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5348,13 +5348,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574573</v>
+        <v>574445</v>
       </c>
       <c r="R46" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5381,19 +5381,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5408,60 +5398,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128340722</v>
+        <v>128339678</v>
       </c>
       <c r="B47" t="n">
-        <v>80192</v>
+        <v>56880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574563</v>
+        <v>574545</v>
       </c>
       <c r="R47" t="n">
-        <v>7088549</v>
+        <v>7088725</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5488,19 +5483,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:31</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5515,22 +5505,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128341581</v>
+        <v>128340722</v>
       </c>
       <c r="B48" t="n">
-        <v>78753</v>
+        <v>80192</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5538,21 +5528,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5562,13 +5552,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574445</v>
+        <v>574563</v>
       </c>
       <c r="R48" t="n">
-        <v>7088593</v>
+        <v>7088549</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5595,9 +5585,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5741,50 +5741,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128339103</v>
+        <v>128341543</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>80228</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R50" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5817,11 +5812,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5848,7 +5838,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128339352</v>
+        <v>128339103</v>
       </c>
       <c r="B51" t="n">
         <v>57689</v>
@@ -5888,13 +5878,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574614</v>
+        <v>574625</v>
       </c>
       <c r="R51" t="n">
-        <v>7088680</v>
+        <v>7088640</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5921,24 +5911,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5953,57 +5933,62 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128340512</v>
+        <v>128339352</v>
       </c>
       <c r="B52" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574550</v>
+        <v>574614</v>
       </c>
       <c r="R52" t="n">
-        <v>7088660</v>
+        <v>7088680</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6035,7 +6020,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6045,7 +6030,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6060,44 +6050,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341658</v>
+        <v>128340512</v>
       </c>
       <c r="B53" t="n">
-        <v>78753</v>
+        <v>92754</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6107,13 +6097,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R53" t="n">
-        <v>7088595</v>
+        <v>7088660</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6140,9 +6130,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6157,22 +6157,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128340602</v>
+        <v>128341658</v>
       </c>
       <c r="B54" t="n">
-        <v>92779</v>
+        <v>78753</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6204,13 +6204,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088642</v>
+        <v>7088595</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6237,19 +6237,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6264,44 +6254,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341543</v>
+        <v>128340602</v>
       </c>
       <c r="B55" t="n">
-        <v>80228</v>
+        <v>92779</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6311,13 +6301,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574553</v>
       </c>
       <c r="R55" t="n">
-        <v>7088593</v>
+        <v>7088642</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6344,9 +6334,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,12 +6361,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340670</v>
+        <v>128340363</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,42 +7872,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574568</v>
+        <v>574523</v>
       </c>
       <c r="R70" t="n">
-        <v>7088607</v>
+        <v>7088723</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7934,24 +7929,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7966,65 +7946,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340933</v>
+        <v>128339554</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>80220</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574498</v>
+        <v>574560</v>
       </c>
       <c r="R71" t="n">
-        <v>7088556</v>
+        <v>7088771</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8051,24 +8026,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8083,22 +8043,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128341109</v>
+        <v>128340563</v>
       </c>
       <c r="B72" t="n">
-        <v>57689</v>
+        <v>92947</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8106,39 +8066,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574429</v>
+        <v>574549</v>
       </c>
       <c r="R72" t="n">
-        <v>7088591</v>
+        <v>7088658</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8170,7 +8125,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8180,12 +8135,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8200,19 +8150,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340344</v>
+        <v>128340670</v>
       </c>
       <c r="B73" t="n">
         <v>57689</v>
@@ -8243,7 +8193,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8252,10 +8202,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574557</v>
+        <v>574568</v>
       </c>
       <c r="R73" t="n">
-        <v>7088695</v>
+        <v>7088607</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8287,7 +8237,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8297,7 +8247,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8329,10 +8279,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340639</v>
+        <v>128340933</v>
       </c>
       <c r="B74" t="n">
-        <v>78845</v>
+        <v>57689</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8340,34 +8290,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574574</v>
+        <v>574498</v>
       </c>
       <c r="R74" t="n">
-        <v>7088635</v>
+        <v>7088556</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8399,7 +8354,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8409,7 +8364,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8424,22 +8384,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128340363</v>
+        <v>128341109</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8447,37 +8407,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574523</v>
+        <v>574429</v>
       </c>
       <c r="R75" t="n">
-        <v>7088723</v>
+        <v>7088591</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8504,9 +8469,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8521,60 +8501,65 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128339554</v>
+        <v>128340344</v>
       </c>
       <c r="B76" t="n">
-        <v>80220</v>
+        <v>57689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574560</v>
+        <v>574557</v>
       </c>
       <c r="R76" t="n">
-        <v>7088771</v>
+        <v>7088695</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8601,9 +8586,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8618,22 +8618,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128340563</v>
+        <v>128340639</v>
       </c>
       <c r="B77" t="n">
-        <v>92947</v>
+        <v>78845</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8641,21 +8641,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8665,10 +8665,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>574549</v>
+        <v>574574</v>
       </c>
       <c r="R77" t="n">
-        <v>7088658</v>
+        <v>7088635</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340579</v>
+        <v>128340643</v>
       </c>
       <c r="B2" t="n">
-        <v>56880</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574542</v>
+        <v>574570</v>
       </c>
       <c r="R2" t="n">
-        <v>7088660</v>
+        <v>7088645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sandgrop</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339514</v>
+        <v>128340579</v>
       </c>
       <c r="B3" t="n">
         <v>56880</v>
@@ -821,14 +811,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574577</v>
+        <v>574542</v>
       </c>
       <c r="R3" t="n">
-        <v>7088748</v>
+        <v>7088660</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,9 +855,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,50 +887,55 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338916</v>
+        <v>128339514</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574622</v>
+        <v>574577</v>
       </c>
       <c r="R4" t="n">
-        <v>7088618</v>
+        <v>7088748</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -975,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,48 +1006,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340643</v>
+        <v>128338916</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574570</v>
+        <v>574622</v>
       </c>
       <c r="R5" t="n">
-        <v>7088645</v>
+        <v>7088618</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1079,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339216</v>
+        <v>128340410</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>92772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574620</v>
+        <v>574543</v>
       </c>
       <c r="R6" t="n">
-        <v>7088666</v>
+        <v>7088692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,12 +1208,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1233,7 +1223,7 @@
         <v>128341140</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340410</v>
+        <v>128340568</v>
       </c>
       <c r="B8" t="n">
-        <v>92770</v>
+        <v>78755</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574543</v>
+        <v>574551</v>
       </c>
       <c r="R8" t="n">
-        <v>7088692</v>
+        <v>7088652</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,19 +1395,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340568</v>
+        <v>128339216</v>
       </c>
       <c r="B9" t="n">
-        <v>78753</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,37 +1435,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574551</v>
+        <v>574620</v>
       </c>
       <c r="R9" t="n">
-        <v>7088652</v>
+        <v>7088666</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,9 +1497,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>78755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R10" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128342806</v>
+        <v>128341194</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574452</v>
+        <v>574533</v>
       </c>
       <c r="R11" t="n">
-        <v>7088593</v>
+        <v>7088534</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128339922</v>
+        <v>128342806</v>
       </c>
       <c r="B12" t="n">
-        <v>78753</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574537</v>
+        <v>574452</v>
       </c>
       <c r="R12" t="n">
-        <v>7088735</v>
+        <v>7088593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,60 +1850,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340548</v>
+        <v>128339006</v>
       </c>
       <c r="B13" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574550</v>
+        <v>574657</v>
       </c>
       <c r="R13" t="n">
-        <v>7088658</v>
+        <v>7088628</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,19 +1930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,22 +1947,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128339006</v>
+        <v>128343119</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574657</v>
+        <v>574495</v>
       </c>
       <c r="R14" t="n">
-        <v>7088628</v>
+        <v>7088662</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2066,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343119</v>
+        <v>128340548</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>92756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574495</v>
+        <v>574550</v>
       </c>
       <c r="R15" t="n">
-        <v>7088662</v>
+        <v>7088658</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,9 +2124,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,62 +2151,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341646</v>
+        <v>128340635</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574445</v>
+        <v>574554</v>
       </c>
       <c r="R16" t="n">
-        <v>7088594</v>
+        <v>7088634</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2239,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,48 +2260,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2328,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,22 +2355,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128338970</v>
+        <v>128341646</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,37 +2378,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574649</v>
+        <v>574445</v>
       </c>
       <c r="R18" t="n">
-        <v>7088609</v>
+        <v>7088594</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2435,19 +2440,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,44 +2462,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340725</v>
+        <v>128343851</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>92750</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574548</v>
+        <v>574522</v>
       </c>
       <c r="R19" t="n">
-        <v>7088558</v>
+        <v>7088573</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2574,7 +2574,7 @@
         <v>128340679</v>
       </c>
       <c r="B20" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,32 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343851</v>
+        <v>128340725</v>
       </c>
       <c r="B21" t="n">
-        <v>92748</v>
+        <v>80223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574522</v>
+        <v>574548</v>
       </c>
       <c r="R21" t="n">
-        <v>7088573</v>
+        <v>7088558</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2768,7 +2768,7 @@
         <v>128341522</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,32 +2862,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128341564</v>
+        <v>128340360</v>
       </c>
       <c r="B23" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574445</v>
+        <v>574548</v>
       </c>
       <c r="R23" t="n">
-        <v>7088593</v>
+        <v>7088705</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,9 +2930,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,12 +2957,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3193,32 +3203,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128340360</v>
+        <v>128341564</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>92756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,13 +3238,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574548</v>
+        <v>574445</v>
       </c>
       <c r="R26" t="n">
-        <v>7088705</v>
+        <v>7088593</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3261,19 +3271,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,44 +3288,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128340667</v>
+        <v>128340549</v>
       </c>
       <c r="B27" t="n">
-        <v>92754</v>
+        <v>90499</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574565</v>
+        <v>574555</v>
       </c>
       <c r="R27" t="n">
-        <v>7088619</v>
+        <v>7088647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128340549</v>
+        <v>128339278</v>
       </c>
       <c r="B29" t="n">
-        <v>90497</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,34 +3520,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574555</v>
+        <v>574615</v>
       </c>
       <c r="R29" t="n">
-        <v>7088647</v>
+        <v>7088675</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,7 +3584,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3589,7 +3594,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,19 +3614,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128339278</v>
+        <v>128339431</v>
       </c>
       <c r="B30" t="n">
         <v>57689</v>
@@ -3656,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574615</v>
+        <v>574614</v>
       </c>
       <c r="R30" t="n">
-        <v>7088675</v>
+        <v>7088709</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3691,7 +3701,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3701,7 +3711,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3733,7 +3743,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339431</v>
+        <v>128338795</v>
       </c>
       <c r="B31" t="n">
         <v>57689</v>
@@ -3769,14 +3779,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574614</v>
+        <v>574657</v>
       </c>
       <c r="R31" t="n">
-        <v>7088709</v>
+        <v>7088592</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,12 +3828,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3838,62 +3848,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338795</v>
+        <v>128340667</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574657</v>
+        <v>574565</v>
       </c>
       <c r="R32" t="n">
-        <v>7088592</v>
+        <v>7088619</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,12 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,38 +3967,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128343108</v>
+        <v>128339517</v>
       </c>
       <c r="B33" t="n">
-        <v>56880</v>
+        <v>57686</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574486</v>
+        <v>574599</v>
       </c>
       <c r="R33" t="n">
-        <v>7088664</v>
+        <v>7088725</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4040,14 +4040,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Grop</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,65 +4067,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339517</v>
+        <v>128339234</v>
       </c>
       <c r="B34" t="n">
-        <v>57686</v>
+        <v>80098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574599</v>
+        <v>574647</v>
       </c>
       <c r="R34" t="n">
-        <v>7088725</v>
+        <v>7088700</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4147,19 +4147,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4174,22 +4164,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339462</v>
+        <v>128340784</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>92784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4197,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574615</v>
+        <v>574541</v>
       </c>
       <c r="R35" t="n">
-        <v>7088761</v>
+        <v>7088525</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4254,19 +4244,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,44 +4261,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339234</v>
+        <v>128339640</v>
       </c>
       <c r="B36" t="n">
-        <v>80096</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,13 +4308,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574647</v>
+        <v>574554</v>
       </c>
       <c r="R36" t="n">
-        <v>7088700</v>
+        <v>7088750</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4361,9 +4341,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4378,22 +4368,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343025</v>
+        <v>128339462</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,13 +4415,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574482</v>
+        <v>574615</v>
       </c>
       <c r="R37" t="n">
-        <v>7088688</v>
+        <v>7088761</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4458,9 +4448,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,22 +4475,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128339640</v>
+        <v>128343025</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574554</v>
+        <v>574482</v>
       </c>
       <c r="R38" t="n">
-        <v>7088750</v>
+        <v>7088688</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4555,19 +4555,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4582,57 +4572,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128340784</v>
+        <v>128343108</v>
       </c>
       <c r="B39" t="n">
-        <v>92782</v>
+        <v>56880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574541</v>
+        <v>574486</v>
       </c>
       <c r="R39" t="n">
-        <v>7088525</v>
+        <v>7088664</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4665,6 +4660,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4691,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128340357</v>
+        <v>128339243</v>
       </c>
       <c r="B40" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,21 +4702,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574526</v>
+        <v>574646</v>
       </c>
       <c r="R40" t="n">
-        <v>7088741</v>
+        <v>7088700</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128339243</v>
+        <v>128340692</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,34 +4799,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574646</v>
+        <v>574557</v>
       </c>
       <c r="R41" t="n">
-        <v>7088700</v>
+        <v>7088560</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4859,6 +4864,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4885,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340692</v>
+        <v>128340357</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4896,39 +4906,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574557</v>
+        <v>574526</v>
       </c>
       <c r="R42" t="n">
-        <v>7088560</v>
+        <v>7088741</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4961,11 +4966,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,32 +4992,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128339546</v>
+        <v>128341581</v>
       </c>
       <c r="B43" t="n">
-        <v>92754</v>
+        <v>78755</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574558</v>
+        <v>574445</v>
       </c>
       <c r="R43" t="n">
-        <v>7088774</v>
+        <v>7088593</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5089,53 +5089,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128339432</v>
+        <v>128339546</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574618</v>
+        <v>574558</v>
       </c>
       <c r="R44" t="n">
-        <v>7088746</v>
+        <v>7088774</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5162,24 +5157,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5194,22 +5174,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128340649</v>
+        <v>128340722</v>
       </c>
       <c r="B45" t="n">
-        <v>79706</v>
+        <v>80194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5217,21 +5197,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5241,10 +5221,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574573</v>
+        <v>574563</v>
       </c>
       <c r="R45" t="n">
-        <v>7088640</v>
+        <v>7088549</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,7 +5256,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5286,7 +5266,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5313,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128341581</v>
+        <v>128340649</v>
       </c>
       <c r="B46" t="n">
-        <v>78753</v>
+        <v>79708</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5324,21 +5304,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5348,13 +5328,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574445</v>
+        <v>574573</v>
       </c>
       <c r="R46" t="n">
-        <v>7088593</v>
+        <v>7088640</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5381,9 +5361,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5398,44 +5388,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128339678</v>
+        <v>128339432</v>
       </c>
       <c r="B47" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5450,13 +5440,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574545</v>
+        <v>574618</v>
       </c>
       <c r="R47" t="n">
-        <v>7088725</v>
+        <v>7088746</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5483,14 +5473,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Sandbad och spillning</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5505,60 +5505,65 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128340722</v>
+        <v>128339678</v>
       </c>
       <c r="B48" t="n">
-        <v>80192</v>
+        <v>56880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574563</v>
+        <v>574545</v>
       </c>
       <c r="R48" t="n">
-        <v>7088549</v>
+        <v>7088725</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5585,19 +5590,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:31</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B50" t="n">
-        <v>80228</v>
+        <v>92756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R50" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,9 +5809,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5826,22 +5836,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128339103</v>
+        <v>128341658</v>
       </c>
       <c r="B51" t="n">
-        <v>57689</v>
+        <v>78755</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5849,39 +5859,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R51" t="n">
-        <v>7088640</v>
+        <v>7088595</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5914,11 +5919,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,7 +5945,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128339352</v>
+        <v>128339103</v>
       </c>
       <c r="B52" t="n">
         <v>57689</v>
@@ -5985,13 +5985,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574614</v>
+        <v>574625</v>
       </c>
       <c r="R52" t="n">
-        <v>7088680</v>
+        <v>7088640</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6018,24 +6018,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6050,57 +6040,62 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128340512</v>
+        <v>128339352</v>
       </c>
       <c r="B53" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574550</v>
+        <v>574614</v>
       </c>
       <c r="R53" t="n">
-        <v>7088660</v>
+        <v>7088680</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6132,7 +6127,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6142,7 +6137,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6157,22 +6157,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341658</v>
+        <v>128340602</v>
       </c>
       <c r="B54" t="n">
-        <v>78753</v>
+        <v>92781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6204,13 +6204,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574553</v>
       </c>
       <c r="R54" t="n">
-        <v>7088595</v>
+        <v>7088642</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6237,9 +6237,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6254,44 +6264,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128340602</v>
+        <v>128341543</v>
       </c>
       <c r="B55" t="n">
-        <v>92779</v>
+        <v>80230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6301,13 +6311,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088642</v>
+        <v>7088593</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6334,19 +6344,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,12 +6361,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6376,7 +6376,7 @@
         <v>128339624</v>
       </c>
       <c r="B56" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6470,10 +6470,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341588</v>
+        <v>128339929</v>
       </c>
       <c r="B57" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574445</v>
+        <v>574555</v>
       </c>
       <c r="R57" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6538,9 +6538,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6555,57 +6565,62 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339929</v>
+        <v>128339538</v>
       </c>
       <c r="B58" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574555</v>
+        <v>574598</v>
       </c>
       <c r="R58" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6637,7 +6652,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6647,7 +6662,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6674,53 +6694,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339538</v>
+        <v>128341588</v>
       </c>
       <c r="B59" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574598</v>
+        <v>574445</v>
       </c>
       <c r="R59" t="n">
-        <v>7088728</v>
+        <v>7088594</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6747,24 +6762,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6779,12 +6779,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6794,7 +6794,7 @@
         <v>128339188</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6898,32 +6898,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128343086</v>
+        <v>128339543</v>
       </c>
       <c r="B61" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574491</v>
+        <v>574558</v>
       </c>
       <c r="R61" t="n">
-        <v>7088668</v>
+        <v>7088774</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128339543</v>
+        <v>128343086</v>
       </c>
       <c r="B62" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574558</v>
+        <v>574491</v>
       </c>
       <c r="R62" t="n">
-        <v>7088774</v>
+        <v>7088668</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128340020</v>
+        <v>128343065</v>
       </c>
       <c r="B63" t="n">
-        <v>78753</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574526</v>
+        <v>574485</v>
       </c>
       <c r="R63" t="n">
-        <v>7088741</v>
+        <v>7088660</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128339617</v>
+        <v>128340645</v>
       </c>
       <c r="B64" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,39 +7220,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574563</v>
+        <v>574571</v>
       </c>
       <c r="R64" t="n">
-        <v>7088745</v>
+        <v>7088636</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7284,7 +7279,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7294,12 +7289,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7314,22 +7304,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128343065</v>
+        <v>128339617</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7337,37 +7327,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574485</v>
+        <v>574563</v>
       </c>
       <c r="R65" t="n">
-        <v>7088660</v>
+        <v>7088745</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7394,9 +7389,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,22 +7421,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128340645</v>
+        <v>128340020</v>
       </c>
       <c r="B66" t="n">
-        <v>78844</v>
+        <v>78755</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,21 +7444,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7458,13 +7468,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574571</v>
+        <v>574526</v>
       </c>
       <c r="R66" t="n">
-        <v>7088636</v>
+        <v>7088741</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7491,19 +7501,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,44 +7518,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128342808</v>
+        <v>128341241</v>
       </c>
       <c r="B67" t="n">
-        <v>80221</v>
+        <v>92772</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574453</v>
+        <v>574529</v>
       </c>
       <c r="R67" t="n">
-        <v>7088593</v>
+        <v>7088560</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7625,44 +7625,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128341241</v>
+        <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>92770</v>
+        <v>80223</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574529</v>
+        <v>574453</v>
       </c>
       <c r="R68" t="n">
-        <v>7088560</v>
+        <v>7088593</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7732,12 +7732,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340363</v>
+        <v>128340563</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>92949</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,13 +7896,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574523</v>
+        <v>574549</v>
       </c>
       <c r="R70" t="n">
-        <v>7088723</v>
+        <v>7088658</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7929,9 +7929,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7946,44 +7956,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128339554</v>
+        <v>128340363</v>
       </c>
       <c r="B71" t="n">
-        <v>80220</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,10 +8003,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574560</v>
+        <v>574523</v>
       </c>
       <c r="R71" t="n">
-        <v>7088771</v>
+        <v>7088723</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8055,32 +8065,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340563</v>
+        <v>128339554</v>
       </c>
       <c r="B72" t="n">
-        <v>92947</v>
+        <v>80222</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8090,13 +8100,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574549</v>
+        <v>574560</v>
       </c>
       <c r="R72" t="n">
-        <v>7088658</v>
+        <v>7088771</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8123,19 +8133,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8150,12 +8150,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8633,7 +8633,7 @@
         <v>128340639</v>
       </c>
       <c r="B77" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8737,53 +8737,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128339415</v>
+        <v>128340367</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>96710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>574618</v>
+        <v>574519</v>
       </c>
       <c r="R78" t="n">
-        <v>7088747</v>
+        <v>7088716</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8810,24 +8805,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8842,60 +8822,65 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128340367</v>
+        <v>128339415</v>
       </c>
       <c r="B79" t="n">
-        <v>96708</v>
+        <v>57689</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574519</v>
+        <v>574618</v>
       </c>
       <c r="R79" t="n">
-        <v>7088716</v>
+        <v>7088747</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8922,9 +8907,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8939,12 +8939,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340579</v>
+        <v>128338916</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574542</v>
+        <v>574622</v>
       </c>
       <c r="R3" t="n">
-        <v>7088660</v>
+        <v>7088618</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,24 +855,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +877,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128339514</v>
+        <v>128340579</v>
       </c>
       <c r="B4" t="n">
         <v>56880</v>
@@ -928,14 +918,9 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574577</v>
+        <v>574542</v>
       </c>
       <c r="R4" t="n">
-        <v>7088748</v>
+        <v>7088660</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +962,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,50 +994,55 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338916</v>
+        <v>128339514</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574622</v>
+        <v>574577</v>
       </c>
       <c r="R5" t="n">
-        <v>7088618</v>
+        <v>7088748</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,11 +1087,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340410</v>
+        <v>128339216</v>
       </c>
       <c r="B6" t="n">
-        <v>92772</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574543</v>
+        <v>574620</v>
       </c>
       <c r="R6" t="n">
-        <v>7088692</v>
+        <v>7088666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,44 +1218,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128341140</v>
+        <v>128340568</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574438</v>
+        <v>574551</v>
       </c>
       <c r="R7" t="n">
-        <v>7088595</v>
+        <v>7088652</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,19 +1298,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,44 +1315,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340568</v>
+        <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>78755</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574551</v>
+        <v>574438</v>
       </c>
       <c r="R8" t="n">
-        <v>7088652</v>
+        <v>7088595</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,9 +1395,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128339216</v>
+        <v>128340410</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>92772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,39 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574620</v>
+        <v>574543</v>
       </c>
       <c r="R9" t="n">
-        <v>7088666</v>
+        <v>7088692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B10" t="n">
-        <v>78755</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R10" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341194</v>
+        <v>128342806</v>
       </c>
       <c r="B11" t="n">
         <v>80194</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574533</v>
+        <v>574452</v>
       </c>
       <c r="R11" t="n">
-        <v>7088534</v>
+        <v>7088593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342806</v>
+        <v>128339922</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>78755</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574452</v>
+        <v>574537</v>
       </c>
       <c r="R12" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,60 +1850,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128339006</v>
+        <v>128340548</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574657</v>
+        <v>574550</v>
       </c>
       <c r="R13" t="n">
-        <v>7088628</v>
+        <v>7088658</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,9 +1930,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343119</v>
+        <v>128339006</v>
       </c>
       <c r="B14" t="n">
         <v>79089</v>
@@ -1990,14 +2000,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574495</v>
+        <v>574657</v>
       </c>
       <c r="R14" t="n">
-        <v>7088662</v>
+        <v>7088628</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2056,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340548</v>
+        <v>128343119</v>
       </c>
       <c r="B15" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574550</v>
+        <v>574495</v>
       </c>
       <c r="R15" t="n">
-        <v>7088658</v>
+        <v>7088662</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,19 +2134,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,60 +2151,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R16" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2231,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,60 +2258,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,19 +2338,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2474,32 +2474,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343851</v>
+        <v>128340679</v>
       </c>
       <c r="B19" t="n">
-        <v>92750</v>
+        <v>92756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574522</v>
+        <v>574565</v>
       </c>
       <c r="R19" t="n">
-        <v>7088573</v>
+        <v>7088589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,32 +2571,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128340679</v>
+        <v>128343851</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>92750</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574565</v>
+        <v>574522</v>
       </c>
       <c r="R20" t="n">
-        <v>7088589</v>
+        <v>7088573</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2969,53 +2969,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128339039</v>
+        <v>128341564</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574613</v>
+        <v>574445</v>
       </c>
       <c r="R24" t="n">
-        <v>7088652</v>
+        <v>7088593</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3042,24 +3037,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,19 +3054,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338853</v>
+        <v>128339039</v>
       </c>
       <c r="B25" t="n">
         <v>57689</v>
@@ -3117,19 +3097,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574647</v>
+        <v>574613</v>
       </c>
       <c r="R25" t="n">
-        <v>7088580</v>
+        <v>7088652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3161,7 +3141,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3171,7 +3151,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3191,60 +3171,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128341564</v>
+        <v>128338853</v>
       </c>
       <c r="B26" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R26" t="n">
-        <v>7088593</v>
+        <v>7088580</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3271,9 +3256,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,12 +3288,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3407,32 +3407,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339483</v>
+        <v>128339278</v>
       </c>
       <c r="B28" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574580</v>
+        <v>574615</v>
       </c>
       <c r="R28" t="n">
-        <v>7088751</v>
+        <v>7088675</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3480,9 +3480,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3497,19 +3512,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339278</v>
+        <v>128339431</v>
       </c>
       <c r="B29" t="n">
         <v>57689</v>
@@ -3549,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574615</v>
+        <v>574614</v>
       </c>
       <c r="R29" t="n">
-        <v>7088675</v>
+        <v>7088709</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3599,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3594,7 +3609,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3626,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128339431</v>
+        <v>128338795</v>
       </c>
       <c r="B30" t="n">
         <v>57689</v>
@@ -3662,14 +3677,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574614</v>
+        <v>574657</v>
       </c>
       <c r="R30" t="n">
-        <v>7088709</v>
+        <v>7088592</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3701,7 +3716,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3711,12 +3726,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3731,62 +3746,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128338795</v>
+        <v>128340667</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574657</v>
+        <v>574565</v>
       </c>
       <c r="R31" t="n">
-        <v>7088592</v>
+        <v>7088619</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3818,7 +3828,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,12 +3838,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128340667</v>
+        <v>128339483</v>
       </c>
       <c r="B32" t="n">
-        <v>92756</v>
+        <v>56880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,37 +3876,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574565</v>
+        <v>574580</v>
       </c>
       <c r="R32" t="n">
-        <v>7088619</v>
+        <v>7088751</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3928,19 +3938,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,22 +3955,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339517</v>
+        <v>128340784</v>
       </c>
       <c r="B33" t="n">
-        <v>57686</v>
+        <v>92784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,42 +3978,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574599</v>
+        <v>574541</v>
       </c>
       <c r="R33" t="n">
-        <v>7088725</v>
+        <v>7088525</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4040,19 +4035,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,60 +4052,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339234</v>
+        <v>128339517</v>
       </c>
       <c r="B34" t="n">
-        <v>80098</v>
+        <v>57686</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574647</v>
+        <v>574599</v>
       </c>
       <c r="R34" t="n">
-        <v>7088700</v>
+        <v>7088725</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4147,9 +4137,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,22 +4164,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128340784</v>
+        <v>128339640</v>
       </c>
       <c r="B35" t="n">
-        <v>92784</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574541</v>
+        <v>574554</v>
       </c>
       <c r="R35" t="n">
-        <v>7088525</v>
+        <v>7088750</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4244,9 +4244,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4261,19 +4271,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339640</v>
+        <v>128339462</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4308,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574554</v>
+        <v>574615</v>
       </c>
       <c r="R36" t="n">
-        <v>7088750</v>
+        <v>7088761</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4343,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4353,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,32 +4390,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128339462</v>
+        <v>128339234</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>80098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4415,13 +4425,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574615</v>
+        <v>574647</v>
       </c>
       <c r="R37" t="n">
-        <v>7088761</v>
+        <v>7088700</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4448,19 +4458,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,12 +4475,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128339243</v>
+        <v>128340357</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,21 +4702,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574646</v>
+        <v>574526</v>
       </c>
       <c r="R40" t="n">
-        <v>7088700</v>
+        <v>7088741</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128340692</v>
+        <v>128339243</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,39 +4799,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574557</v>
+        <v>574646</v>
       </c>
       <c r="R41" t="n">
-        <v>7088560</v>
+        <v>7088700</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4864,11 +4859,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340357</v>
+        <v>128340692</v>
       </c>
       <c r="B42" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,34 +4896,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574526</v>
+        <v>574557</v>
       </c>
       <c r="R42" t="n">
-        <v>7088741</v>
+        <v>7088560</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4966,6 +4961,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5741,32 +5741,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340512</v>
+        <v>128341658</v>
       </c>
       <c r="B50" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R50" t="n">
-        <v>7088660</v>
+        <v>7088595</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,19 +5809,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,44 +5826,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128341658</v>
+        <v>128340512</v>
       </c>
       <c r="B51" t="n">
-        <v>78755</v>
+        <v>92756</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5883,13 +5873,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R51" t="n">
-        <v>7088595</v>
+        <v>7088660</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5916,9 +5906,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5933,62 +5933,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128339103</v>
+        <v>128341543</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>80230</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R52" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6021,11 +6016,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,10 +6042,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128339352</v>
+        <v>128340602</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>92781</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,39 +6053,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574614</v>
+        <v>574553</v>
       </c>
       <c r="R53" t="n">
-        <v>7088680</v>
+        <v>7088642</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6127,7 +6112,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6137,12 +6122,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6157,22 +6137,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128340602</v>
+        <v>128339103</v>
       </c>
       <c r="B54" t="n">
-        <v>92781</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6180,37 +6160,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574553</v>
+        <v>574625</v>
       </c>
       <c r="R54" t="n">
-        <v>7088642</v>
+        <v>7088640</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6237,19 +6222,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:19</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6264,60 +6244,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341543</v>
+        <v>128339352</v>
       </c>
       <c r="B55" t="n">
-        <v>80230</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574614</v>
       </c>
       <c r="R55" t="n">
-        <v>7088593</v>
+        <v>7088680</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6344,9 +6329,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,44 +6361,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339624</v>
+        <v>128339188</v>
       </c>
       <c r="B56" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574580</v>
+        <v>574647</v>
       </c>
       <c r="R56" t="n">
-        <v>7088767</v>
+        <v>7088696</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,9 +6441,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6458,19 +6468,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339929</v>
+        <v>128339624</v>
       </c>
       <c r="B57" t="n">
         <v>92756</v>
@@ -6505,13 +6515,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574555</v>
+        <v>574580</v>
       </c>
       <c r="R57" t="n">
-        <v>7088696</v>
+        <v>7088767</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6538,19 +6548,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6565,65 +6565,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339538</v>
+        <v>128341588</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574598</v>
+        <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088728</v>
+        <v>7088594</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6650,24 +6645,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6682,19 +6662,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128341588</v>
+        <v>128339929</v>
       </c>
       <c r="B59" t="n">
         <v>92756</v>
@@ -6729,13 +6709,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574445</v>
+        <v>574555</v>
       </c>
       <c r="R59" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6762,9 +6742,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6779,22 +6769,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339188</v>
+        <v>128339538</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6802,34 +6792,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574647</v>
+        <v>574598</v>
       </c>
       <c r="R60" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6861,7 +6856,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6871,7 +6866,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,44 +6886,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128339543</v>
+        <v>128343086</v>
       </c>
       <c r="B61" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574558</v>
+        <v>574491</v>
       </c>
       <c r="R61" t="n">
-        <v>7088774</v>
+        <v>7088668</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128343086</v>
+        <v>128339543</v>
       </c>
       <c r="B62" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574491</v>
+        <v>574558</v>
       </c>
       <c r="R62" t="n">
-        <v>7088668</v>
+        <v>7088774</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128343065</v>
+        <v>128340020</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574485</v>
+        <v>574526</v>
       </c>
       <c r="R63" t="n">
-        <v>7088660</v>
+        <v>7088741</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128340645</v>
+        <v>128343065</v>
       </c>
       <c r="B64" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574571</v>
+        <v>574485</v>
       </c>
       <c r="R64" t="n">
-        <v>7088636</v>
+        <v>7088660</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7277,19 +7277,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7304,22 +7294,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128339617</v>
+        <v>128340645</v>
       </c>
       <c r="B65" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7327,39 +7317,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574563</v>
+        <v>574571</v>
       </c>
       <c r="R65" t="n">
-        <v>7088745</v>
+        <v>7088636</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7391,7 +7376,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7401,12 +7386,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7421,22 +7401,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128340020</v>
+        <v>128339617</v>
       </c>
       <c r="B66" t="n">
-        <v>78755</v>
+        <v>57689</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,37 +7424,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574526</v>
+        <v>574563</v>
       </c>
       <c r="R66" t="n">
-        <v>7088741</v>
+        <v>7088745</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7501,9 +7486,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,44 +7518,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341241</v>
+        <v>128342808</v>
       </c>
       <c r="B67" t="n">
-        <v>92772</v>
+        <v>80223</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574529</v>
+        <v>574453</v>
       </c>
       <c r="R67" t="n">
-        <v>7088560</v>
+        <v>7088593</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7625,44 +7625,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128342808</v>
+        <v>128341241</v>
       </c>
       <c r="B68" t="n">
-        <v>80223</v>
+        <v>92772</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574453</v>
+        <v>574529</v>
       </c>
       <c r="R68" t="n">
-        <v>7088593</v>
+        <v>7088560</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7732,12 +7732,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8065,48 +8065,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128339554</v>
+        <v>128340670</v>
       </c>
       <c r="B72" t="n">
-        <v>80222</v>
+        <v>57689</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574560</v>
+        <v>574568</v>
       </c>
       <c r="R72" t="n">
-        <v>7088771</v>
+        <v>7088607</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8133,9 +8138,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8150,19 +8170,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340670</v>
+        <v>128340933</v>
       </c>
       <c r="B73" t="n">
         <v>57689</v>
@@ -8193,7 +8213,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8202,10 +8222,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574568</v>
+        <v>574498</v>
       </c>
       <c r="R73" t="n">
-        <v>7088607</v>
+        <v>7088556</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8237,7 +8257,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8247,7 +8267,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8279,7 +8299,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340933</v>
+        <v>128341109</v>
       </c>
       <c r="B74" t="n">
         <v>57689</v>
@@ -8319,10 +8339,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574498</v>
+        <v>574429</v>
       </c>
       <c r="R74" t="n">
-        <v>7088556</v>
+        <v>7088591</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8354,7 +8374,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8364,7 +8384,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8396,7 +8416,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128341109</v>
+        <v>128340344</v>
       </c>
       <c r="B75" t="n">
         <v>57689</v>
@@ -8436,10 +8456,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574429</v>
+        <v>574557</v>
       </c>
       <c r="R75" t="n">
-        <v>7088591</v>
+        <v>7088695</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8471,7 +8491,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8481,7 +8501,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -8513,53 +8533,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340344</v>
+        <v>128339554</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574557</v>
+        <v>574560</v>
       </c>
       <c r="R76" t="n">
-        <v>7088695</v>
+        <v>7088771</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8586,24 +8601,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8618,12 +8618,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -2862,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128340360</v>
+        <v>128339039</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,34 +2873,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574548</v>
+        <v>574613</v>
       </c>
       <c r="R23" t="n">
-        <v>7088705</v>
+        <v>7088652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2932,7 +2937,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2942,7 +2947,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,60 +2967,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128341564</v>
+        <v>128338853</v>
       </c>
       <c r="B24" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R24" t="n">
-        <v>7088593</v>
+        <v>7088580</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,9 +3052,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3054,65 +3084,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128339039</v>
+        <v>128341564</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574613</v>
+        <v>574445</v>
       </c>
       <c r="R25" t="n">
-        <v>7088652</v>
+        <v>7088593</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3139,24 +3164,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3171,22 +3181,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338853</v>
+        <v>128340360</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,39 +3204,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574647</v>
+        <v>574548</v>
       </c>
       <c r="R26" t="n">
-        <v>7088580</v>
+        <v>7088705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,7 +3263,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,12 +3273,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3300,32 +3300,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128340549</v>
+        <v>128340667</v>
       </c>
       <c r="B27" t="n">
-        <v>90499</v>
+        <v>92756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574555</v>
+        <v>574565</v>
       </c>
       <c r="R27" t="n">
-        <v>7088647</v>
+        <v>7088619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,32 +3407,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339278</v>
+        <v>128339483</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574615</v>
+        <v>574580</v>
       </c>
       <c r="R28" t="n">
-        <v>7088675</v>
+        <v>7088751</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3480,24 +3480,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3512,22 +3497,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339431</v>
+        <v>128340549</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>90499</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,39 +3520,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574614</v>
+        <v>574555</v>
       </c>
       <c r="R29" t="n">
-        <v>7088709</v>
+        <v>7088647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,7 +3579,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3609,12 +3589,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3629,19 +3604,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128338795</v>
+        <v>128339278</v>
       </c>
       <c r="B30" t="n">
         <v>57689</v>
@@ -3677,14 +3652,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574657</v>
+        <v>574615</v>
       </c>
       <c r="R30" t="n">
-        <v>7088592</v>
+        <v>7088675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,7 +3691,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3726,12 +3701,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,57 +3721,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128340667</v>
+        <v>128339431</v>
       </c>
       <c r="B31" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574565</v>
+        <v>574614</v>
       </c>
       <c r="R31" t="n">
-        <v>7088619</v>
+        <v>7088709</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3808,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3838,7 +3818,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,44 +3838,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128339483</v>
+        <v>128338795</v>
       </c>
       <c r="B32" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3901,17 +3886,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574580</v>
+        <v>574657</v>
       </c>
       <c r="R32" t="n">
-        <v>7088751</v>
+        <v>7088592</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3938,9 +3923,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,12 +3955,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339640</v>
+        <v>128339462</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574554</v>
+        <v>574615</v>
       </c>
       <c r="R35" t="n">
-        <v>7088750</v>
+        <v>7088761</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339462</v>
+        <v>128339234</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>80098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574615</v>
+        <v>574647</v>
       </c>
       <c r="R36" t="n">
-        <v>7088761</v>
+        <v>7088700</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4351,19 +4351,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4378,44 +4368,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128339234</v>
+        <v>128343025</v>
       </c>
       <c r="B37" t="n">
-        <v>80098</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574647</v>
+        <v>574482</v>
       </c>
       <c r="R37" t="n">
-        <v>7088700</v>
+        <v>7088688</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4487,45 +4477,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128343025</v>
+        <v>128343108</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>56880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574482</v>
+        <v>574486</v>
       </c>
       <c r="R38" t="n">
-        <v>7088688</v>
+        <v>7088664</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4558,6 +4553,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4584,53 +4584,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128343108</v>
+        <v>128339640</v>
       </c>
       <c r="B39" t="n">
-        <v>56880</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574486</v>
+        <v>574554</v>
       </c>
       <c r="R39" t="n">
-        <v>7088664</v>
+        <v>7088750</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4657,14 +4652,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Grop</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,12 +4679,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5838,10 +5838,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340512</v>
+        <v>128341543</v>
       </c>
       <c r="B51" t="n">
-        <v>92756</v>
+        <v>80230</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5849,21 +5849,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5873,13 +5873,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R51" t="n">
-        <v>7088660</v>
+        <v>7088593</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5906,19 +5906,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5933,44 +5923,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128341543</v>
+        <v>128340602</v>
       </c>
       <c r="B52" t="n">
-        <v>80230</v>
+        <v>92781</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5980,13 +5970,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574445</v>
+        <v>574553</v>
       </c>
       <c r="R52" t="n">
-        <v>7088593</v>
+        <v>7088642</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6013,9 +6003,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6030,22 +6030,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128340602</v>
+        <v>128339103</v>
       </c>
       <c r="B53" t="n">
-        <v>92781</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6053,37 +6053,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574553</v>
+        <v>574625</v>
       </c>
       <c r="R53" t="n">
-        <v>7088642</v>
+        <v>7088640</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6110,19 +6115,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:19</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6137,19 +6137,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339103</v>
+        <v>128339352</v>
       </c>
       <c r="B54" t="n">
         <v>57689</v>
@@ -6189,13 +6189,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574625</v>
+        <v>574614</v>
       </c>
       <c r="R54" t="n">
-        <v>7088640</v>
+        <v>7088680</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6222,14 +6222,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre och färska spår</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6244,62 +6254,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128339352</v>
+        <v>128340512</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574614</v>
+        <v>574550</v>
       </c>
       <c r="R55" t="n">
-        <v>7088680</v>
+        <v>7088660</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6331,7 +6336,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6341,12 +6346,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,22 +6361,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339188</v>
+        <v>128339538</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6384,34 +6384,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574647</v>
+        <v>574598</v>
       </c>
       <c r="R56" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6443,7 +6448,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6453,7 +6458,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6468,12 +6478,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6781,10 +6791,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339538</v>
+        <v>128339188</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6792,39 +6802,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574598</v>
+        <v>574647</v>
       </c>
       <c r="R60" t="n">
-        <v>7088728</v>
+        <v>7088696</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6856,7 +6861,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6866,12 +6871,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,12 +6886,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7861,32 +7861,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340563</v>
+        <v>128339554</v>
       </c>
       <c r="B70" t="n">
-        <v>92949</v>
+        <v>80222</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,13 +7896,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574549</v>
+        <v>574560</v>
       </c>
       <c r="R70" t="n">
-        <v>7088658</v>
+        <v>7088771</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7929,19 +7929,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7956,22 +7946,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340363</v>
+        <v>128340563</v>
       </c>
       <c r="B71" t="n">
-        <v>79089</v>
+        <v>92949</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7979,21 +7969,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8003,13 +7993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574523</v>
+        <v>574549</v>
       </c>
       <c r="R71" t="n">
-        <v>7088723</v>
+        <v>7088658</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8036,9 +8026,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8053,12 +8053,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8533,32 +8533,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128339554</v>
+        <v>128340363</v>
       </c>
       <c r="B76" t="n">
-        <v>80222</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574560</v>
+        <v>574523</v>
       </c>
       <c r="R76" t="n">
-        <v>7088771</v>
+        <v>7088723</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8737,48 +8737,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128340367</v>
+        <v>128339415</v>
       </c>
       <c r="B78" t="n">
-        <v>96710</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>574519</v>
+        <v>574618</v>
       </c>
       <c r="R78" t="n">
-        <v>7088716</v>
+        <v>7088747</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,9 +8810,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8822,65 +8842,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128339415</v>
+        <v>128340367</v>
       </c>
       <c r="B79" t="n">
-        <v>57689</v>
+        <v>96710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574618</v>
+        <v>574519</v>
       </c>
       <c r="R79" t="n">
-        <v>7088747</v>
+        <v>7088716</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8907,24 +8922,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8939,12 +8939,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340643</v>
+        <v>128338916</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574570</v>
+        <v>574622</v>
       </c>
       <c r="R2" t="n">
-        <v>7088645</v>
+        <v>7088618</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +748,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,65 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338916</v>
+        <v>128340643</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>92757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574622</v>
+        <v>574570</v>
       </c>
       <c r="R3" t="n">
-        <v>7088618</v>
+        <v>7088645</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,14 +850,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339216</v>
+        <v>128340568</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>78755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574620</v>
+        <v>574551</v>
       </c>
       <c r="R6" t="n">
-        <v>7088666</v>
+        <v>7088652</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,24 +1181,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340568</v>
+        <v>128340410</v>
       </c>
       <c r="B7" t="n">
-        <v>78755</v>
+        <v>92773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574551</v>
+        <v>574543</v>
       </c>
       <c r="R7" t="n">
-        <v>7088652</v>
+        <v>7088692</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,9 +1278,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,12 +1305,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1330,7 +1320,7 @@
         <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340410</v>
+        <v>128339216</v>
       </c>
       <c r="B9" t="n">
-        <v>92772</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574543</v>
+        <v>574620</v>
       </c>
       <c r="R9" t="n">
-        <v>7088692</v>
+        <v>7088666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B10" t="n">
-        <v>80194</v>
+        <v>78755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R10" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128342806</v>
+        <v>128341194</v>
       </c>
       <c r="B11" t="n">
         <v>80194</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574452</v>
+        <v>574533</v>
       </c>
       <c r="R11" t="n">
-        <v>7088593</v>
+        <v>7088534</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128339922</v>
+        <v>128342806</v>
       </c>
       <c r="B12" t="n">
-        <v>78755</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574537</v>
+        <v>574452</v>
       </c>
       <c r="R12" t="n">
-        <v>7088735</v>
+        <v>7088593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,60 +1850,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340548</v>
+        <v>128339006</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574550</v>
+        <v>574657</v>
       </c>
       <c r="R13" t="n">
-        <v>7088658</v>
+        <v>7088628</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,19 +1930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,19 +1947,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128339006</v>
+        <v>128343119</v>
       </c>
       <c r="B14" t="n">
         <v>79089</v>
@@ -2000,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574657</v>
+        <v>574495</v>
       </c>
       <c r="R14" t="n">
-        <v>7088628</v>
+        <v>7088662</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2066,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343119</v>
+        <v>128340548</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574495</v>
+        <v>574550</v>
       </c>
       <c r="R15" t="n">
-        <v>7088662</v>
+        <v>7088658</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,9 +2124,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,60 +2151,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R16" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,19 +2231,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,60 +2248,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,9 +2328,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2477,7 +2477,7 @@
         <v>128340679</v>
       </c>
       <c r="B19" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>128343851</v>
       </c>
       <c r="B20" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,53 +2862,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128339039</v>
+        <v>128341564</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>92757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574613</v>
+        <v>574445</v>
       </c>
       <c r="R23" t="n">
-        <v>7088652</v>
+        <v>7088593</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2935,24 +2930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2967,22 +2947,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338853</v>
+        <v>128340360</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2990,39 +2970,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574647</v>
+        <v>574548</v>
       </c>
       <c r="R24" t="n">
-        <v>7088580</v>
+        <v>7088705</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,7 +3029,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3064,12 +3039,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,48 +3066,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128341564</v>
+        <v>128338853</v>
       </c>
       <c r="B25" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574445</v>
+        <v>574647</v>
       </c>
       <c r="R25" t="n">
-        <v>7088593</v>
+        <v>7088580</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3164,9 +3139,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3181,22 +3171,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128340360</v>
+        <v>128339039</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,34 +3194,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574548</v>
+        <v>574613</v>
       </c>
       <c r="R26" t="n">
-        <v>7088705</v>
+        <v>7088652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3273,7 +3268,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3288,12 +3288,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
         <v>128340667</v>
       </c>
       <c r="B27" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3407,53 +3407,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128339483</v>
+        <v>128340549</v>
       </c>
       <c r="B28" t="n">
-        <v>56880</v>
+        <v>90499</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574580</v>
+        <v>574555</v>
       </c>
       <c r="R28" t="n">
-        <v>7088751</v>
+        <v>7088647</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3480,9 +3475,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3497,22 +3502,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128340549</v>
+        <v>128339431</v>
       </c>
       <c r="B29" t="n">
-        <v>90499</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,34 +3525,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574555</v>
+        <v>574614</v>
       </c>
       <c r="R29" t="n">
-        <v>7088647</v>
+        <v>7088709</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,7 +3589,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3589,7 +3599,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,12 +3619,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3733,32 +3748,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339431</v>
+        <v>128339483</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3773,13 +3788,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574614</v>
+        <v>574580</v>
       </c>
       <c r="R31" t="n">
-        <v>7088709</v>
+        <v>7088751</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3806,24 +3821,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3838,12 +3838,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128340784</v>
+        <v>128339640</v>
       </c>
       <c r="B33" t="n">
-        <v>92784</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574541</v>
+        <v>574554</v>
       </c>
       <c r="R33" t="n">
-        <v>7088525</v>
+        <v>7088750</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,9 +4035,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,22 +4062,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339517</v>
+        <v>128339462</v>
       </c>
       <c r="B34" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4075,42 +4085,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574599</v>
+        <v>574615</v>
       </c>
       <c r="R34" t="n">
-        <v>7088725</v>
+        <v>7088761</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4164,19 +4169,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339462</v>
+        <v>128343025</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -4211,13 +4216,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574615</v>
+        <v>574482</v>
       </c>
       <c r="R35" t="n">
-        <v>7088761</v>
+        <v>7088688</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4244,19 +4249,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4271,22 +4266,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339234</v>
+        <v>128343108</v>
       </c>
       <c r="B36" t="n">
-        <v>80098</v>
+        <v>56880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,34 +4289,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574647</v>
+        <v>574486</v>
       </c>
       <c r="R36" t="n">
-        <v>7088700</v>
+        <v>7088664</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4354,6 +4354,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343025</v>
+        <v>128340784</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>92785</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4391,21 +4396,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4415,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574482</v>
+        <v>574541</v>
       </c>
       <c r="R37" t="n">
-        <v>7088688</v>
+        <v>7088525</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4477,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128343108</v>
+        <v>128339234</v>
       </c>
       <c r="B38" t="n">
-        <v>56880</v>
+        <v>80098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4488,39 +4493,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574486</v>
+        <v>574647</v>
       </c>
       <c r="R38" t="n">
-        <v>7088664</v>
+        <v>7088700</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4553,11 +4553,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Grop</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4584,10 +4579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128339640</v>
+        <v>128339517</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4595,37 +4590,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574554</v>
+        <v>574599</v>
       </c>
       <c r="R39" t="n">
-        <v>7088750</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,12 +4679,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4992,32 +4992,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341581</v>
+        <v>128339546</v>
       </c>
       <c r="B43" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574445</v>
+        <v>574558</v>
       </c>
       <c r="R43" t="n">
-        <v>7088593</v>
+        <v>7088774</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5089,32 +5089,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128339546</v>
+        <v>128341581</v>
       </c>
       <c r="B44" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574558</v>
+        <v>574445</v>
       </c>
       <c r="R44" t="n">
-        <v>7088774</v>
+        <v>7088593</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128340722</v>
+        <v>128339432</v>
       </c>
       <c r="B45" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5197,34 +5197,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574563</v>
+        <v>574618</v>
       </c>
       <c r="R45" t="n">
-        <v>7088549</v>
+        <v>7088746</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5256,7 +5261,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5266,7 +5271,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,48 +5303,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128340649</v>
+        <v>128339678</v>
       </c>
       <c r="B46" t="n">
-        <v>79708</v>
+        <v>56880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574573</v>
+        <v>574545</v>
       </c>
       <c r="R46" t="n">
-        <v>7088640</v>
+        <v>7088725</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5361,19 +5376,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:23</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5388,22 +5398,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128339432</v>
+        <v>128340722</v>
       </c>
       <c r="B47" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5411,39 +5421,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574618</v>
+        <v>574563</v>
       </c>
       <c r="R47" t="n">
-        <v>7088746</v>
+        <v>7088549</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,7 +5480,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5485,12 +5490,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5517,53 +5517,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128339678</v>
+        <v>128340649</v>
       </c>
       <c r="B48" t="n">
-        <v>56880</v>
+        <v>79708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574545</v>
+        <v>574573</v>
       </c>
       <c r="R48" t="n">
-        <v>7088725</v>
+        <v>7088640</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5590,14 +5585,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128341658</v>
+        <v>128340602</v>
       </c>
       <c r="B50" t="n">
-        <v>78755</v>
+        <v>92782</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574445</v>
+        <v>574553</v>
       </c>
       <c r="R50" t="n">
-        <v>7088595</v>
+        <v>7088642</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,9 +5809,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5826,22 +5836,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B51" t="n">
-        <v>80230</v>
+        <v>92757</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5849,21 +5859,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5873,13 +5883,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R51" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5906,9 +5916,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5923,22 +5943,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128340602</v>
+        <v>128341658</v>
       </c>
       <c r="B52" t="n">
-        <v>92781</v>
+        <v>78755</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5946,21 +5966,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5970,13 +5990,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R52" t="n">
-        <v>7088642</v>
+        <v>7088595</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6003,19 +6023,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6030,62 +6040,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128339103</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>80230</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574625</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088640</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6118,11 +6123,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6266,48 +6266,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128340512</v>
+        <v>128339103</v>
       </c>
       <c r="B55" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574550</v>
+        <v>574625</v>
       </c>
       <c r="R55" t="n">
-        <v>7088660</v>
+        <v>7088640</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6334,19 +6339,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,65 +6361,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339538</v>
+        <v>128339624</v>
       </c>
       <c r="B56" t="n">
-        <v>57689</v>
+        <v>92757</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574598</v>
+        <v>574580</v>
       </c>
       <c r="R56" t="n">
-        <v>7088728</v>
+        <v>7088767</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6446,24 +6441,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6478,22 +6458,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339624</v>
+        <v>128341588</v>
       </c>
       <c r="B57" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6525,10 +6505,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574580</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088767</v>
+        <v>7088594</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6587,10 +6567,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341588</v>
+        <v>128339929</v>
       </c>
       <c r="B58" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6622,13 +6602,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574445</v>
+        <v>574555</v>
       </c>
       <c r="R58" t="n">
-        <v>7088594</v>
+        <v>7088696</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6655,9 +6635,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6672,44 +6662,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339929</v>
+        <v>128339188</v>
       </c>
       <c r="B59" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6719,7 +6709,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574555</v>
+        <v>574647</v>
       </c>
       <c r="R59" t="n">
         <v>7088696</v>
@@ -6754,7 +6744,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6764,7 +6754,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6779,22 +6769,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339188</v>
+        <v>128339538</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6802,34 +6792,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574647</v>
+        <v>574598</v>
       </c>
       <c r="R60" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6861,7 +6856,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6871,7 +6866,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,44 +6886,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128343086</v>
+        <v>128339543</v>
       </c>
       <c r="B61" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574491</v>
+        <v>574558</v>
       </c>
       <c r="R61" t="n">
-        <v>7088668</v>
+        <v>7088774</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128339543</v>
+        <v>128343086</v>
       </c>
       <c r="B62" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574558</v>
+        <v>574491</v>
       </c>
       <c r="R62" t="n">
-        <v>7088774</v>
+        <v>7088668</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128340020</v>
+        <v>128339617</v>
       </c>
       <c r="B63" t="n">
-        <v>78755</v>
+        <v>57689</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,37 +7123,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574526</v>
+        <v>574563</v>
       </c>
       <c r="R63" t="n">
-        <v>7088741</v>
+        <v>7088745</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7180,9 +7185,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7197,12 +7217,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7306,10 +7326,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128340645</v>
+        <v>128340020</v>
       </c>
       <c r="B65" t="n">
-        <v>78846</v>
+        <v>78755</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7317,21 +7337,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7341,13 +7361,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574571</v>
+        <v>574526</v>
       </c>
       <c r="R65" t="n">
-        <v>7088636</v>
+        <v>7088741</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7374,19 +7394,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7401,22 +7411,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128339617</v>
+        <v>128340645</v>
       </c>
       <c r="B66" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7424,39 +7434,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574563</v>
+        <v>574571</v>
       </c>
       <c r="R66" t="n">
-        <v>7088745</v>
+        <v>7088636</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7488,7 +7493,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7498,12 +7503,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,57 +7518,62 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128342808</v>
+        <v>128339467</v>
       </c>
       <c r="B67" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574453</v>
+        <v>574607</v>
       </c>
       <c r="R67" t="n">
-        <v>7088593</v>
+        <v>7088708</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7600,7 +7605,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7610,7 +7615,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7640,7 +7650,7 @@
         <v>128341241</v>
       </c>
       <c r="B68" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7744,50 +7754,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128339467</v>
+        <v>128342808</v>
       </c>
       <c r="B69" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574607</v>
+        <v>574453</v>
       </c>
       <c r="R69" t="n">
-        <v>7088708</v>
+        <v>7088593</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7819,7 +7824,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7829,12 +7834,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7861,32 +7861,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128339554</v>
+        <v>128340363</v>
       </c>
       <c r="B70" t="n">
-        <v>80222</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574560</v>
+        <v>574523</v>
       </c>
       <c r="R70" t="n">
-        <v>7088771</v>
+        <v>7088723</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7961,7 +7961,7 @@
         <v>128340563</v>
       </c>
       <c r="B71" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8065,53 +8065,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340670</v>
+        <v>128339554</v>
       </c>
       <c r="B72" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574568</v>
+        <v>574560</v>
       </c>
       <c r="R72" t="n">
-        <v>7088607</v>
+        <v>7088771</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8138,24 +8133,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8170,12 +8150,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8299,7 +8279,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128341109</v>
+        <v>128340344</v>
       </c>
       <c r="B74" t="n">
         <v>57689</v>
@@ -8339,10 +8319,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574429</v>
+        <v>574557</v>
       </c>
       <c r="R74" t="n">
-        <v>7088591</v>
+        <v>7088695</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8374,7 +8354,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8384,7 +8364,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8416,7 +8396,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128340344</v>
+        <v>128341109</v>
       </c>
       <c r="B75" t="n">
         <v>57689</v>
@@ -8456,10 +8436,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574557</v>
+        <v>574429</v>
       </c>
       <c r="R75" t="n">
-        <v>7088695</v>
+        <v>7088591</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,7 +8471,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8501,7 +8481,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -8533,10 +8513,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340363</v>
+        <v>128340670</v>
       </c>
       <c r="B76" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8544,37 +8524,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574523</v>
+        <v>574568</v>
       </c>
       <c r="R76" t="n">
-        <v>7088723</v>
+        <v>7088607</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8601,9 +8586,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8618,12 +8618,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8737,53 +8737,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128339415</v>
+        <v>128340367</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>96711</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>574618</v>
+        <v>574519</v>
       </c>
       <c r="R78" t="n">
-        <v>7088747</v>
+        <v>7088716</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8810,24 +8805,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8842,60 +8822,65 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128340367</v>
+        <v>128339415</v>
       </c>
       <c r="B79" t="n">
-        <v>96710</v>
+        <v>57689</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>574519</v>
+        <v>574618</v>
       </c>
       <c r="R79" t="n">
-        <v>7088716</v>
+        <v>7088747</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8922,9 +8907,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8939,12 +8939,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128338916</v>
+        <v>128340579</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>56880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574622</v>
+        <v>574542</v>
       </c>
       <c r="R2" t="n">
-        <v>7088618</v>
+        <v>7088660</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,14 +748,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340643</v>
+        <v>128339514</v>
       </c>
       <c r="B3" t="n">
-        <v>92757</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +803,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574570</v>
+        <v>574577</v>
       </c>
       <c r="R3" t="n">
-        <v>7088645</v>
+        <v>7088748</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +870,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +887,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340579</v>
+        <v>128338916</v>
       </c>
       <c r="B4" t="n">
-        <v>56880</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574542</v>
+        <v>574622</v>
       </c>
       <c r="R4" t="n">
-        <v>7088660</v>
+        <v>7088618</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,24 +972,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128339514</v>
+        <v>128340643</v>
       </c>
       <c r="B5" t="n">
-        <v>56880</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,47 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574577</v>
+        <v>574570</v>
       </c>
       <c r="R5" t="n">
-        <v>7088748</v>
+        <v>7088645</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,9 +1074,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,44 +1101,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340568</v>
+        <v>128341140</v>
       </c>
       <c r="B6" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574551</v>
+        <v>574438</v>
       </c>
       <c r="R6" t="n">
-        <v>7088652</v>
+        <v>7088595</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,9 +1181,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340410</v>
+        <v>128339216</v>
       </c>
       <c r="B7" t="n">
-        <v>92773</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574543</v>
+        <v>574620</v>
       </c>
       <c r="R7" t="n">
-        <v>7088692</v>
+        <v>7088666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,44 +1325,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341140</v>
+        <v>128340568</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>78755</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574438</v>
+        <v>574551</v>
       </c>
       <c r="R8" t="n">
-        <v>7088595</v>
+        <v>7088652</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,19 +1405,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128339216</v>
+        <v>128340410</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>92773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,39 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574620</v>
+        <v>574543</v>
       </c>
       <c r="R9" t="n">
-        <v>7088666</v>
+        <v>7088692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,12 +1529,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1862,48 +1862,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128339006</v>
+        <v>128340548</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574657</v>
+        <v>574550</v>
       </c>
       <c r="R13" t="n">
-        <v>7088628</v>
+        <v>7088658</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,9 +1930,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,19 +1957,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343119</v>
+        <v>128339006</v>
       </c>
       <c r="B14" t="n">
         <v>79089</v>
@@ -1990,14 +2000,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574495</v>
+        <v>574657</v>
       </c>
       <c r="R14" t="n">
-        <v>7088662</v>
+        <v>7088628</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2056,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340548</v>
+        <v>128343119</v>
       </c>
       <c r="B15" t="n">
-        <v>92757</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574550</v>
+        <v>574495</v>
       </c>
       <c r="R15" t="n">
-        <v>7088658</v>
+        <v>7088662</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,19 +2134,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,60 +2151,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R16" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2231,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,60 +2258,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338970</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574649</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088609</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,19 +2338,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,12 +2355,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338853</v>
+        <v>128339039</v>
       </c>
       <c r="B25" t="n">
         <v>57689</v>
@@ -3097,19 +3097,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574647</v>
+        <v>574613</v>
       </c>
       <c r="R25" t="n">
-        <v>7088580</v>
+        <v>7088652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3171,19 +3171,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128339039</v>
+        <v>128338853</v>
       </c>
       <c r="B26" t="n">
         <v>57689</v>
@@ -3214,19 +3214,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574613</v>
+        <v>574647</v>
       </c>
       <c r="R26" t="n">
-        <v>7088652</v>
+        <v>7088580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3288,12 +3288,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339640</v>
+        <v>128340784</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>92785</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574554</v>
+        <v>574541</v>
       </c>
       <c r="R33" t="n">
-        <v>7088750</v>
+        <v>7088525</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,19 +4035,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,19 +4052,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339462</v>
+        <v>128339640</v>
       </c>
       <c r="B34" t="n">
         <v>79089</v>
@@ -4109,10 +4099,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574615</v>
+        <v>574554</v>
       </c>
       <c r="R34" t="n">
-        <v>7088761</v>
+        <v>7088750</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,7 +4134,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4154,7 +4144,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,7 +4171,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128343025</v>
+        <v>128339462</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -4216,13 +4206,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574482</v>
+        <v>574615</v>
       </c>
       <c r="R35" t="n">
-        <v>7088688</v>
+        <v>7088761</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4249,9 +4239,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4266,62 +4266,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343108</v>
+        <v>128343025</v>
       </c>
       <c r="B36" t="n">
-        <v>56880</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574486</v>
+        <v>574482</v>
       </c>
       <c r="R36" t="n">
-        <v>7088664</v>
+        <v>7088688</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4354,11 +4349,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Grop</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,45 +4375,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128340784</v>
+        <v>128343108</v>
       </c>
       <c r="B37" t="n">
-        <v>92785</v>
+        <v>56880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574541</v>
+        <v>574486</v>
       </c>
       <c r="R37" t="n">
-        <v>7088525</v>
+        <v>7088664</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4456,6 +4451,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4691,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128340357</v>
+        <v>128339243</v>
       </c>
       <c r="B40" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,21 +4702,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574526</v>
+        <v>574646</v>
       </c>
       <c r="R40" t="n">
-        <v>7088741</v>
+        <v>7088700</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128339243</v>
+        <v>128340357</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574646</v>
+        <v>574526</v>
       </c>
       <c r="R41" t="n">
-        <v>7088700</v>
+        <v>7088741</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4992,32 +4992,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128339546</v>
+        <v>128341581</v>
       </c>
       <c r="B43" t="n">
-        <v>92757</v>
+        <v>78755</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574558</v>
+        <v>574445</v>
       </c>
       <c r="R43" t="n">
-        <v>7088774</v>
+        <v>7088593</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5089,32 +5089,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128341581</v>
+        <v>128339546</v>
       </c>
       <c r="B44" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574445</v>
+        <v>574558</v>
       </c>
       <c r="R44" t="n">
-        <v>7088593</v>
+        <v>7088774</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340512</v>
+        <v>128341543</v>
       </c>
       <c r="B51" t="n">
-        <v>92757</v>
+        <v>80230</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5883,13 +5883,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R51" t="n">
-        <v>7088660</v>
+        <v>7088593</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5916,19 +5916,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5943,22 +5933,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128341658</v>
+        <v>128339352</v>
       </c>
       <c r="B52" t="n">
-        <v>78755</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,37 +5956,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574445</v>
+        <v>574614</v>
       </c>
       <c r="R52" t="n">
-        <v>7088595</v>
+        <v>7088680</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6023,9 +6018,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6040,22 +6050,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128340512</v>
       </c>
       <c r="B53" t="n">
-        <v>80230</v>
+        <v>92757</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,21 +6073,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6087,13 +6097,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574550</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088660</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6120,9 +6130,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6137,22 +6157,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128339352</v>
+        <v>128341658</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>78755</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6160,42 +6180,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574614</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088680</v>
+        <v>7088595</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6222,24 +6237,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6254,12 +6254,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128339467</v>
+        <v>128341241</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
+        <v>92773</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7541,39 +7541,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574607</v>
+        <v>574529</v>
       </c>
       <c r="R67" t="n">
-        <v>7088708</v>
+        <v>7088560</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7605,7 +7600,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7615,12 +7610,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7635,44 +7625,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128341241</v>
+        <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>92773</v>
+        <v>80223</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7682,10 +7672,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574529</v>
+        <v>574453</v>
       </c>
       <c r="R68" t="n">
-        <v>7088560</v>
+        <v>7088593</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7717,7 +7707,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7727,7 +7717,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7742,57 +7732,62 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128342808</v>
+        <v>128339467</v>
       </c>
       <c r="B69" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574453</v>
+        <v>574607</v>
       </c>
       <c r="R69" t="n">
-        <v>7088593</v>
+        <v>7088708</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7824,7 +7819,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7834,7 +7829,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340579</v>
+        <v>128340643</v>
       </c>
       <c r="B2" t="n">
-        <v>56880</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574542</v>
+        <v>574570</v>
       </c>
       <c r="R2" t="n">
-        <v>7088660</v>
+        <v>7088645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sandgrop</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128339514</v>
+        <v>128340579</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,14 +811,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574577</v>
+        <v>574542</v>
       </c>
       <c r="R3" t="n">
-        <v>7088748</v>
+        <v>7088660</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,9 +855,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,50 +887,55 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338916</v>
+        <v>128339514</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>56907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574622</v>
+        <v>574577</v>
       </c>
       <c r="R4" t="n">
-        <v>7088618</v>
+        <v>7088748</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -975,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,48 +1006,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340643</v>
+        <v>128338916</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574570</v>
+        <v>574622</v>
       </c>
       <c r="R5" t="n">
-        <v>7088645</v>
+        <v>7088618</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1079,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,44 +1101,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128341140</v>
+        <v>128340410</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574438</v>
+        <v>574543</v>
       </c>
       <c r="R6" t="n">
-        <v>7088595</v>
+        <v>7088692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339216</v>
+        <v>128340568</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>78782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,42 +1231,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574620</v>
+        <v>574551</v>
       </c>
       <c r="R7" t="n">
-        <v>7088666</v>
+        <v>7088652</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,24 +1288,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,44 +1305,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340568</v>
+        <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>78755</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574551</v>
+        <v>574438</v>
       </c>
       <c r="R8" t="n">
-        <v>7088652</v>
+        <v>7088595</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,9 +1385,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340410</v>
+        <v>128339216</v>
       </c>
       <c r="B9" t="n">
-        <v>92773</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574543</v>
+        <v>574620</v>
       </c>
       <c r="R9" t="n">
-        <v>7088692</v>
+        <v>7088666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128339922</v>
+        <v>128341194</v>
       </c>
       <c r="B10" t="n">
-        <v>78755</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574537</v>
+        <v>574533</v>
       </c>
       <c r="R10" t="n">
-        <v>7088735</v>
+        <v>7088534</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341194</v>
+        <v>128342806</v>
       </c>
       <c r="B11" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574533</v>
+        <v>574452</v>
       </c>
       <c r="R11" t="n">
-        <v>7088534</v>
+        <v>7088593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342806</v>
+        <v>128339922</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>78782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574452</v>
+        <v>574537</v>
       </c>
       <c r="R12" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,44 +1850,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340548</v>
+        <v>128343119</v>
       </c>
       <c r="B13" t="n">
-        <v>92757</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574550</v>
+        <v>574495</v>
       </c>
       <c r="R13" t="n">
-        <v>7088658</v>
+        <v>7088662</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,19 +1930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,12 +1947,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1972,7 +1962,7 @@
         <v>128339006</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343119</v>
+        <v>128340548</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574495</v>
+        <v>574550</v>
       </c>
       <c r="R15" t="n">
-        <v>7088662</v>
+        <v>7088658</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,9 +2124,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,12 +2151,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
         <v>128338970</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,45 +2270,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340635</v>
+        <v>128341646</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574554</v>
+        <v>574445</v>
       </c>
       <c r="R17" t="n">
-        <v>7088634</v>
+        <v>7088594</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,50 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341646</v>
+        <v>128340635</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574445</v>
+        <v>574554</v>
       </c>
       <c r="R18" t="n">
-        <v>7088594</v>
+        <v>7088634</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2443,11 +2448,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,32 +2474,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340679</v>
+        <v>128343851</v>
       </c>
       <c r="B19" t="n">
-        <v>92757</v>
+        <v>92778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574565</v>
+        <v>574522</v>
       </c>
       <c r="R19" t="n">
-        <v>7088589</v>
+        <v>7088573</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2571,32 +2571,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128343851</v>
+        <v>128340725</v>
       </c>
       <c r="B20" t="n">
-        <v>92751</v>
+        <v>80250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574522</v>
+        <v>574548</v>
       </c>
       <c r="R20" t="n">
-        <v>7088573</v>
+        <v>7088558</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128340725</v>
+        <v>128340679</v>
       </c>
       <c r="B21" t="n">
-        <v>80223</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574548</v>
+        <v>574565</v>
       </c>
       <c r="R21" t="n">
-        <v>7088558</v>
+        <v>7088589</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2768,7 +2768,7 @@
         <v>128341522</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,32 +2862,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128341564</v>
+        <v>128340360</v>
       </c>
       <c r="B23" t="n">
-        <v>92757</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574445</v>
+        <v>574548</v>
       </c>
       <c r="R23" t="n">
-        <v>7088593</v>
+        <v>7088705</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,9 +2930,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,44 +2957,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128340360</v>
+        <v>128341564</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,13 +3004,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574548</v>
+        <v>574445</v>
       </c>
       <c r="R24" t="n">
-        <v>7088705</v>
+        <v>7088593</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3027,19 +3037,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3054,12 +3054,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
         <v>128339039</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>128338853</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128340667</v>
+        <v>128340549</v>
       </c>
       <c r="B27" t="n">
-        <v>92757</v>
+        <v>90526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574565</v>
+        <v>574555</v>
       </c>
       <c r="R27" t="n">
-        <v>7088619</v>
+        <v>7088647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,32 +3407,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128340549</v>
+        <v>128340667</v>
       </c>
       <c r="B28" t="n">
-        <v>90499</v>
+        <v>92784</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574555</v>
+        <v>574565</v>
       </c>
       <c r="R28" t="n">
-        <v>7088647</v>
+        <v>7088619</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,32 +3514,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339431</v>
+        <v>128339483</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>56907</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,13 +3554,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574614</v>
+        <v>574580</v>
       </c>
       <c r="R29" t="n">
-        <v>7088709</v>
+        <v>7088751</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3587,24 +3587,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3619,12 +3604,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3634,7 +3619,7 @@
         <v>128339278</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3748,32 +3733,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339483</v>
+        <v>128339431</v>
       </c>
       <c r="B31" t="n">
-        <v>56880</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,13 +3773,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574580</v>
+        <v>574614</v>
       </c>
       <c r="R31" t="n">
-        <v>7088751</v>
+        <v>7088709</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3821,9 +3806,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3838,12 +3838,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3853,7 +3853,7 @@
         <v>128338795</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,32 +3967,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128340784</v>
+        <v>128339234</v>
       </c>
       <c r="B33" t="n">
-        <v>92785</v>
+        <v>80125</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574541</v>
+        <v>574647</v>
       </c>
       <c r="R33" t="n">
-        <v>7088525</v>
+        <v>7088700</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128339640</v>
+        <v>128343025</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574554</v>
+        <v>574482</v>
       </c>
       <c r="R34" t="n">
-        <v>7088750</v>
+        <v>7088688</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4132,19 +4132,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4159,22 +4149,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339462</v>
+        <v>128339640</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4206,10 +4196,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574615</v>
+        <v>574554</v>
       </c>
       <c r="R35" t="n">
-        <v>7088761</v>
+        <v>7088750</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4241,7 +4231,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4251,7 +4241,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,10 +4268,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343025</v>
+        <v>128339462</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4313,13 +4303,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574482</v>
+        <v>574615</v>
       </c>
       <c r="R36" t="n">
-        <v>7088688</v>
+        <v>7088761</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4346,9 +4336,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4363,62 +4363,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343108</v>
+        <v>128340784</v>
       </c>
       <c r="B37" t="n">
-        <v>56880</v>
+        <v>92812</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574486</v>
+        <v>574541</v>
       </c>
       <c r="R37" t="n">
-        <v>7088664</v>
+        <v>7088525</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4451,11 +4446,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Grop</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4482,48 +4472,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128339234</v>
+        <v>128339517</v>
       </c>
       <c r="B38" t="n">
-        <v>80098</v>
+        <v>57713</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574647</v>
+        <v>574599</v>
       </c>
       <c r="R38" t="n">
-        <v>7088700</v>
+        <v>7088725</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4550,9 +4545,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,50 +4572,50 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128339517</v>
+        <v>128343108</v>
       </c>
       <c r="B39" t="n">
-        <v>57686</v>
+        <v>56907</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4619,13 +4624,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574599</v>
+        <v>574486</v>
       </c>
       <c r="R39" t="n">
-        <v>7088725</v>
+        <v>7088664</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4652,19 +4657,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Grop</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,22 +4679,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128339243</v>
+        <v>128340357</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,21 +4702,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574646</v>
+        <v>574526</v>
       </c>
       <c r="R40" t="n">
-        <v>7088700</v>
+        <v>7088741</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128340357</v>
+        <v>128339243</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,21 +4799,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574526</v>
+        <v>574646</v>
       </c>
       <c r="R41" t="n">
-        <v>7088741</v>
+        <v>7088700</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4888,7 +4888,7 @@
         <v>128340692</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341581</v>
+        <v>128340722</v>
       </c>
       <c r="B43" t="n">
-        <v>78755</v>
+        <v>80221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,13 +5027,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574445</v>
+        <v>574563</v>
       </c>
       <c r="R43" t="n">
-        <v>7088593</v>
+        <v>7088549</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5060,9 +5060,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5077,44 +5087,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128339546</v>
+        <v>128340649</v>
       </c>
       <c r="B44" t="n">
-        <v>92757</v>
+        <v>79735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,13 +5134,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574558</v>
+        <v>574573</v>
       </c>
       <c r="R44" t="n">
-        <v>7088774</v>
+        <v>7088640</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5157,9 +5167,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5174,65 +5194,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128339432</v>
+        <v>128339546</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574618</v>
+        <v>574558</v>
       </c>
       <c r="R45" t="n">
-        <v>7088746</v>
+        <v>7088774</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5259,24 +5274,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5291,62 +5291,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128339678</v>
+        <v>128341581</v>
       </c>
       <c r="B46" t="n">
-        <v>56880</v>
+        <v>78782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574545</v>
+        <v>574445</v>
       </c>
       <c r="R46" t="n">
-        <v>7088725</v>
+        <v>7088593</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5379,11 +5374,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5410,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128340722</v>
+        <v>128339432</v>
       </c>
       <c r="B47" t="n">
-        <v>80194</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5421,34 +5411,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574563</v>
+        <v>574618</v>
       </c>
       <c r="R47" t="n">
-        <v>7088549</v>
+        <v>7088746</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,7 +5475,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5490,7 +5485,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5517,48 +5517,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128340649</v>
+        <v>128339678</v>
       </c>
       <c r="B48" t="n">
-        <v>79708</v>
+        <v>56907</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574573</v>
+        <v>574545</v>
       </c>
       <c r="R48" t="n">
-        <v>7088640</v>
+        <v>7088725</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5585,19 +5590,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:23</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sandbad och spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5612,12 +5612,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5627,7 +5627,7 @@
         <v>128338962</v>
       </c>
       <c r="B49" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>128340602</v>
       </c>
       <c r="B50" t="n">
-        <v>92782</v>
+        <v>92809</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5848,45 +5848,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128341543</v>
+        <v>128339103</v>
       </c>
       <c r="B51" t="n">
-        <v>80230</v>
+        <v>57716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574445</v>
+        <v>574625</v>
       </c>
       <c r="R51" t="n">
-        <v>7088593</v>
+        <v>7088640</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5919,6 +5924,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5948,7 +5958,7 @@
         <v>128339352</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6062,10 +6072,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128340512</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>92757</v>
+        <v>80257</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6073,21 +6083,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6097,13 +6107,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574550</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088660</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6130,19 +6140,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6157,12 +6157,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
         <v>128341658</v>
       </c>
       <c r="B54" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6266,53 +6266,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128339103</v>
+        <v>128340512</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574625</v>
+        <v>574550</v>
       </c>
       <c r="R55" t="n">
-        <v>7088640</v>
+        <v>7088660</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6339,14 +6334,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,44 +6361,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339624</v>
+        <v>128339188</v>
       </c>
       <c r="B56" t="n">
-        <v>92757</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574580</v>
+        <v>574647</v>
       </c>
       <c r="R56" t="n">
-        <v>7088767</v>
+        <v>7088696</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6441,9 +6441,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6458,22 +6468,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341588</v>
+        <v>128339624</v>
       </c>
       <c r="B57" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6505,10 +6515,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574445</v>
+        <v>574580</v>
       </c>
       <c r="R57" t="n">
-        <v>7088594</v>
+        <v>7088767</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6567,10 +6577,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128339929</v>
+        <v>128341588</v>
       </c>
       <c r="B58" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6602,13 +6612,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574555</v>
+        <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088696</v>
+        <v>7088594</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6635,19 +6645,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6662,44 +6662,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339188</v>
+        <v>128339929</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574647</v>
+        <v>574555</v>
       </c>
       <c r="R59" t="n">
         <v>7088696</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6769,12 +6769,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6784,7 +6784,7 @@
         <v>128339538</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>128339543</v>
       </c>
       <c r="B61" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>128343086</v>
       </c>
       <c r="B62" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128339617</v>
+        <v>128343065</v>
       </c>
       <c r="B63" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,42 +7123,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574563</v>
+        <v>574485</v>
       </c>
       <c r="R63" t="n">
-        <v>7088745</v>
+        <v>7088660</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7185,24 +7180,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7217,22 +7197,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128343065</v>
+        <v>128340645</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7240,21 +7220,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7264,13 +7244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574485</v>
+        <v>574571</v>
       </c>
       <c r="R64" t="n">
-        <v>7088660</v>
+        <v>7088636</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7297,9 +7277,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7314,12 +7304,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7329,7 +7319,7 @@
         <v>128340020</v>
       </c>
       <c r="B65" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7423,10 +7413,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128340645</v>
+        <v>128339617</v>
       </c>
       <c r="B66" t="n">
-        <v>78846</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,34 +7424,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574571</v>
+        <v>574563</v>
       </c>
       <c r="R66" t="n">
-        <v>7088636</v>
+        <v>7088745</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7493,7 +7488,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7503,7 +7498,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7533,7 +7533,7 @@
         <v>128341241</v>
       </c>
       <c r="B67" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7637,45 +7637,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128342808</v>
+        <v>128339467</v>
       </c>
       <c r="B68" t="n">
-        <v>80223</v>
+        <v>57716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574453</v>
+        <v>574607</v>
       </c>
       <c r="R68" t="n">
-        <v>7088593</v>
+        <v>7088708</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7707,7 +7712,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7717,7 +7722,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7744,50 +7754,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128339467</v>
+        <v>128342808</v>
       </c>
       <c r="B69" t="n">
-        <v>57689</v>
+        <v>80250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574607</v>
+        <v>574453</v>
       </c>
       <c r="R69" t="n">
-        <v>7088708</v>
+        <v>7088593</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7819,7 +7824,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7829,12 +7834,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7861,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340363</v>
+        <v>128340563</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>92977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,13 +7896,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574523</v>
+        <v>574549</v>
       </c>
       <c r="R70" t="n">
-        <v>7088723</v>
+        <v>7088658</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7929,9 +7929,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7946,44 +7956,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128340563</v>
+        <v>128339554</v>
       </c>
       <c r="B71" t="n">
-        <v>92950</v>
+        <v>80249</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7993,13 +8003,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574549</v>
+        <v>574560</v>
       </c>
       <c r="R71" t="n">
-        <v>7088658</v>
+        <v>7088771</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8026,19 +8036,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8053,44 +8053,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128339554</v>
+        <v>128340363</v>
       </c>
       <c r="B72" t="n">
-        <v>80222</v>
+        <v>79116</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8100,10 +8100,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574560</v>
+        <v>574523</v>
       </c>
       <c r="R72" t="n">
-        <v>7088771</v>
+        <v>7088723</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8162,10 +8162,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340933</v>
+        <v>128340670</v>
       </c>
       <c r="B73" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574498</v>
+        <v>574568</v>
       </c>
       <c r="R73" t="n">
-        <v>7088556</v>
+        <v>7088607</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8279,10 +8279,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340344</v>
+        <v>128340933</v>
       </c>
       <c r="B74" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8319,10 +8319,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574557</v>
+        <v>574498</v>
       </c>
       <c r="R74" t="n">
-        <v>7088695</v>
+        <v>7088556</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8399,7 +8399,7 @@
         <v>128341109</v>
       </c>
       <c r="B75" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340670</v>
+        <v>128340344</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574568</v>
+        <v>574557</v>
       </c>
       <c r="R76" t="n">
-        <v>7088607</v>
+        <v>7088695</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -8633,7 +8633,7 @@
         <v>128340639</v>
       </c>
       <c r="B77" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>128340367</v>
       </c>
       <c r="B78" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>128339415</v>
       </c>
       <c r="B79" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33205-2025 artfynd.xlsx
+++ b/artfynd/A 33205-2025 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340410</v>
+        <v>128340568</v>
       </c>
       <c r="B6" t="n">
-        <v>92800</v>
+        <v>78782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574543</v>
+        <v>574551</v>
       </c>
       <c r="R6" t="n">
-        <v>7088692</v>
+        <v>7088652</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,19 +1181,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340568</v>
+        <v>128340410</v>
       </c>
       <c r="B7" t="n">
-        <v>78782</v>
+        <v>92800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574551</v>
+        <v>574543</v>
       </c>
       <c r="R7" t="n">
-        <v>7088652</v>
+        <v>7088692</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,9 +1278,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,12 +1305,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341194</v>
+        <v>128339922</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>78782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574533</v>
+        <v>574537</v>
       </c>
       <c r="R10" t="n">
-        <v>7088534</v>
+        <v>7088735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128342806</v>
+        <v>128341194</v>
       </c>
       <c r="B11" t="n">
         <v>80221</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574452</v>
+        <v>574533</v>
       </c>
       <c r="R11" t="n">
-        <v>7088593</v>
+        <v>7088534</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128339922</v>
+        <v>128342806</v>
       </c>
       <c r="B12" t="n">
-        <v>78782</v>
+        <v>80221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574537</v>
+        <v>574452</v>
       </c>
       <c r="R12" t="n">
-        <v>7088735</v>
+        <v>7088593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,19 +1850,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128343119</v>
+        <v>128339006</v>
       </c>
       <c r="B13" t="n">
         <v>79116</v>
@@ -1893,14 +1893,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574495</v>
+        <v>574657</v>
       </c>
       <c r="R13" t="n">
-        <v>7088662</v>
+        <v>7088628</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128339006</v>
+        <v>128343119</v>
       </c>
       <c r="B14" t="n">
         <v>79116</v>
@@ -1990,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574657</v>
+        <v>574495</v>
       </c>
       <c r="R14" t="n">
-        <v>7088628</v>
+        <v>7088662</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338970</v>
+        <v>128341646</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,37 +2174,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574649</v>
+        <v>574445</v>
       </c>
       <c r="R16" t="n">
-        <v>7088609</v>
+        <v>7088594</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,19 +2236,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,62 +2258,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341646</v>
+        <v>128340635</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574445</v>
+        <v>574554</v>
       </c>
       <c r="R17" t="n">
-        <v>7088594</v>
+        <v>7088634</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,48 +2367,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340635</v>
+        <v>128338970</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574554</v>
+        <v>574649</v>
       </c>
       <c r="R18" t="n">
-        <v>7088634</v>
+        <v>7088609</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,9 +2435,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128340725</v>
+        <v>128340679</v>
       </c>
       <c r="B20" t="n">
-        <v>80250</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574548</v>
+        <v>574565</v>
       </c>
       <c r="R20" t="n">
-        <v>7088558</v>
+        <v>7088589</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128340679</v>
+        <v>128340725</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>80250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574565</v>
+        <v>574548</v>
       </c>
       <c r="R21" t="n">
-        <v>7088589</v>
+        <v>7088558</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2862,32 +2862,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128340360</v>
+        <v>128341564</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>92784</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574548</v>
+        <v>574445</v>
       </c>
       <c r="R23" t="n">
-        <v>7088705</v>
+        <v>7088593</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,19 +2930,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,44 +2947,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128341564</v>
+        <v>128340360</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,13 +2994,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574445</v>
+        <v>574548</v>
       </c>
       <c r="R24" t="n">
-        <v>7088593</v>
+        <v>7088705</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,9 +3027,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3054,12 +3054,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3407,45 +3407,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128340667</v>
+        <v>128338795</v>
       </c>
       <c r="B28" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574565</v>
+        <v>574657</v>
       </c>
       <c r="R28" t="n">
-        <v>7088619</v>
+        <v>7088592</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3487,7 +3492,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128339483</v>
+        <v>128340667</v>
       </c>
       <c r="B29" t="n">
-        <v>56907</v>
+        <v>92784</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3525,42 +3535,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574580</v>
+        <v>574565</v>
       </c>
       <c r="R29" t="n">
-        <v>7088751</v>
+        <v>7088619</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3587,9 +3592,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,44 +3619,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128339278</v>
+        <v>128339483</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>56907</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3656,13 +3671,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574615</v>
+        <v>574580</v>
       </c>
       <c r="R30" t="n">
-        <v>7088675</v>
+        <v>7088751</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3689,24 +3704,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,19 +3721,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128339431</v>
+        <v>128339278</v>
       </c>
       <c r="B31" t="n">
         <v>57716</v>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574614</v>
+        <v>574615</v>
       </c>
       <c r="R31" t="n">
-        <v>7088709</v>
+        <v>7088675</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3850,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338795</v>
+        <v>128339431</v>
       </c>
       <c r="B32" t="n">
         <v>57716</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574657</v>
+        <v>574614</v>
       </c>
       <c r="R32" t="n">
-        <v>7088592</v>
+        <v>7088709</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,60 +3955,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128339234</v>
+        <v>128339517</v>
       </c>
       <c r="B33" t="n">
-        <v>80125</v>
+        <v>57713</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574647</v>
+        <v>574599</v>
       </c>
       <c r="R33" t="n">
-        <v>7088700</v>
+        <v>7088725</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4035,9 +4040,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,22 +4067,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128343025</v>
+        <v>128340784</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>92812</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4075,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4099,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574482</v>
+        <v>574541</v>
       </c>
       <c r="R34" t="n">
-        <v>7088688</v>
+        <v>7088525</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4161,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128339640</v>
+        <v>128339234</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>80125</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4196,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574554</v>
+        <v>574647</v>
       </c>
       <c r="R35" t="n">
-        <v>7088750</v>
+        <v>7088700</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4229,19 +4244,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,19 +4261,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128339462</v>
+        <v>128339640</v>
       </c>
       <c r="B36" t="n">
         <v>79116</v>
@@ -4303,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574615</v>
+        <v>574554</v>
       </c>
       <c r="R36" t="n">
-        <v>7088761</v>
+        <v>7088750</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4338,7 +4343,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4348,7 +4353,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128340784</v>
+        <v>128339462</v>
       </c>
       <c r="B37" t="n">
-        <v>92812</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4386,21 +4391,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4410,13 +4415,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574541</v>
+        <v>574615</v>
       </c>
       <c r="R37" t="n">
-        <v>7088525</v>
+        <v>7088761</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4443,9 +4448,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4460,22 +4475,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128339517</v>
+        <v>128343025</v>
       </c>
       <c r="B38" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4483,42 +4498,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574599</v>
+        <v>574482</v>
       </c>
       <c r="R38" t="n">
-        <v>7088725</v>
+        <v>7088688</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4545,19 +4555,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4572,12 +4572,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128339243</v>
+        <v>128340692</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4799,34 +4799,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574646</v>
+        <v>574557</v>
       </c>
       <c r="R41" t="n">
-        <v>7088700</v>
+        <v>7088560</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4859,6 +4864,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4885,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128340692</v>
+        <v>128339243</v>
       </c>
       <c r="B42" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4896,39 +4906,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574557</v>
+        <v>574646</v>
       </c>
       <c r="R42" t="n">
-        <v>7088560</v>
+        <v>7088700</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4961,11 +4966,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5206,32 +5206,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128339546</v>
+        <v>128341581</v>
       </c>
       <c r="B45" t="n">
-        <v>92784</v>
+        <v>78782</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574558</v>
+        <v>574445</v>
       </c>
       <c r="R45" t="n">
-        <v>7088774</v>
+        <v>7088593</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5303,32 +5303,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128341581</v>
+        <v>128339546</v>
       </c>
       <c r="B46" t="n">
-        <v>78782</v>
+        <v>92784</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5338,10 +5338,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574445</v>
+        <v>574558</v>
       </c>
       <c r="R46" t="n">
-        <v>7088593</v>
+        <v>7088774</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5741,32 +5741,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340602</v>
+        <v>128341543</v>
       </c>
       <c r="B50" t="n">
-        <v>92809</v>
+        <v>80257</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574553</v>
+        <v>574445</v>
       </c>
       <c r="R50" t="n">
-        <v>7088642</v>
+        <v>7088593</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5809,19 +5809,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,65 +5826,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128339103</v>
+        <v>128340512</v>
       </c>
       <c r="B51" t="n">
-        <v>57716</v>
+        <v>92784</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574625</v>
+        <v>574550</v>
       </c>
       <c r="R51" t="n">
-        <v>7088640</v>
+        <v>7088660</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5921,14 +5906,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre och färska spår</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5943,22 +5933,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128339352</v>
+        <v>128340602</v>
       </c>
       <c r="B52" t="n">
-        <v>57716</v>
+        <v>92809</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,39 +5956,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574614</v>
+        <v>574553</v>
       </c>
       <c r="R52" t="n">
-        <v>7088680</v>
+        <v>7088642</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6030,7 +6015,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6040,12 +6025,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6060,60 +6040,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128339352</v>
       </c>
       <c r="B53" t="n">
-        <v>80257</v>
+        <v>57716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574614</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088680</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6140,9 +6125,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6157,12 +6157,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6266,48 +6266,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128340512</v>
+        <v>128339103</v>
       </c>
       <c r="B55" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574550</v>
+        <v>574625</v>
       </c>
       <c r="R55" t="n">
-        <v>7088660</v>
+        <v>7088640</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6334,19 +6339,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre och färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6361,44 +6361,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128339188</v>
+        <v>128339929</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>92784</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574647</v>
+        <v>574555</v>
       </c>
       <c r="R56" t="n">
         <v>7088696</v>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6468,19 +6468,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128339624</v>
+        <v>128341588</v>
       </c>
       <c r="B57" t="n">
         <v>92784</v>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574580</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088767</v>
+        <v>7088594</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6577,7 +6577,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341588</v>
+        <v>128339624</v>
       </c>
       <c r="B58" t="n">
         <v>92784</v>
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574445</v>
+        <v>574580</v>
       </c>
       <c r="R58" t="n">
-        <v>7088594</v>
+        <v>7088767</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6674,45 +6674,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128339929</v>
+        <v>128339538</v>
       </c>
       <c r="B59" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574555</v>
+        <v>574598</v>
       </c>
       <c r="R59" t="n">
-        <v>7088696</v>
+        <v>7088728</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6744,7 +6749,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6754,7 +6759,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6781,10 +6791,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128339538</v>
+        <v>128339188</v>
       </c>
       <c r="B60" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6792,39 +6802,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574598</v>
+        <v>574647</v>
       </c>
       <c r="R60" t="n">
-        <v>7088728</v>
+        <v>7088696</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6856,7 +6861,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6866,12 +6871,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6886,44 +6886,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128339543</v>
+        <v>128343086</v>
       </c>
       <c r="B61" t="n">
-        <v>56907</v>
+        <v>57716</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574558</v>
+        <v>574491</v>
       </c>
       <c r="R61" t="n">
-        <v>7088774</v>
+        <v>7088668</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Sandgrop</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128343086</v>
+        <v>128339543</v>
       </c>
       <c r="B62" t="n">
-        <v>57716</v>
+        <v>56907</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574491</v>
+        <v>574558</v>
       </c>
       <c r="R62" t="n">
-        <v>7088668</v>
+        <v>7088774</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Sandgrop</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128343065</v>
+        <v>128340020</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>78782</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7123,21 +7123,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574485</v>
+        <v>574526</v>
       </c>
       <c r="R63" t="n">
-        <v>7088660</v>
+        <v>7088741</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128340645</v>
+        <v>128339617</v>
       </c>
       <c r="B64" t="n">
-        <v>78873</v>
+        <v>57716</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7220,34 +7220,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574571</v>
+        <v>574563</v>
       </c>
       <c r="R64" t="n">
-        <v>7088636</v>
+        <v>7088745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7279,7 +7284,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7289,7 +7294,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7304,22 +7314,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128340020</v>
+        <v>128343065</v>
       </c>
       <c r="B65" t="n">
-        <v>78782</v>
+        <v>79116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7327,21 +7337,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7351,10 +7361,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574526</v>
+        <v>574485</v>
       </c>
       <c r="R65" t="n">
-        <v>7088741</v>
+        <v>7088660</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7413,10 +7423,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128339617</v>
+        <v>128340645</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>78873</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7424,39 +7434,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574563</v>
+        <v>574571</v>
       </c>
       <c r="R66" t="n">
-        <v>7088745</v>
+        <v>7088636</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7488,7 +7493,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7498,12 +7503,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,44 +7518,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341241</v>
+        <v>128342808</v>
       </c>
       <c r="B67" t="n">
-        <v>92800</v>
+        <v>80250</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574529</v>
+        <v>574453</v>
       </c>
       <c r="R67" t="n">
-        <v>7088560</v>
+        <v>7088593</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7625,22 +7625,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128339467</v>
+        <v>128341241</v>
       </c>
       <c r="B68" t="n">
-        <v>57716</v>
+        <v>92800</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7648,39 +7648,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>574607</v>
+        <v>574529</v>
       </c>
       <c r="R68" t="n">
-        <v>7088708</v>
+        <v>7088560</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7712,7 +7707,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7722,12 +7717,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7742,57 +7732,62 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128342808</v>
+        <v>128339467</v>
       </c>
       <c r="B69" t="n">
-        <v>80250</v>
+        <v>57716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574453</v>
+        <v>574607</v>
       </c>
       <c r="R69" t="n">
-        <v>7088593</v>
+        <v>7088708</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7824,7 +7819,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7834,7 +7829,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7861,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128340563</v>
+        <v>128340344</v>
       </c>
       <c r="B70" t="n">
-        <v>92977</v>
+        <v>57716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7872,34 +7872,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574549</v>
+        <v>574557</v>
       </c>
       <c r="R70" t="n">
-        <v>7088658</v>
+        <v>7088695</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7931,7 +7936,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7941,7 +7946,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7956,44 +7966,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128339554</v>
+        <v>128340363</v>
       </c>
       <c r="B71" t="n">
-        <v>80249</v>
+        <v>79116</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8003,10 +8013,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574560</v>
+        <v>574523</v>
       </c>
       <c r="R71" t="n">
-        <v>7088771</v>
+        <v>7088723</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8065,10 +8075,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128340363</v>
+        <v>128340563</v>
       </c>
       <c r="B72" t="n">
-        <v>79116</v>
+        <v>92977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8076,21 +8086,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8100,13 +8110,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574523</v>
+        <v>574549</v>
       </c>
       <c r="R72" t="n">
-        <v>7088723</v>
+        <v>7088658</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8133,9 +8143,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8150,65 +8170,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128340670</v>
+        <v>128339554</v>
       </c>
       <c r="B73" t="n">
-        <v>57716</v>
+        <v>80249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574568</v>
+        <v>574560</v>
       </c>
       <c r="R73" t="n">
-        <v>7088607</v>
+        <v>7088771</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8235,24 +8250,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8267,19 +8267,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128340933</v>
+        <v>128340670</v>
       </c>
       <c r="B74" t="n">
         <v>57716</v>
@@ -8310,7 +8310,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8319,10 +8319,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574498</v>
+        <v>574568</v>
       </c>
       <c r="R74" t="n">
-        <v>7088556</v>
+        <v>7088607</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8396,7 +8396,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128341109</v>
+        <v>128340933</v>
       </c>
       <c r="B75" t="n">
         <v>57716</v>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574429</v>
+        <v>574498</v>
       </c>
       <c r="R75" t="n">
-        <v>7088591</v>
+        <v>7088556</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -8513,7 +8513,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128340344</v>
+        <v>128341109</v>
       </c>
       <c r="B76" t="n">
         <v>57716</v>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>574557</v>
+        <v>574429</v>
       </c>
       <c r="R76" t="n">
-        <v>7088695</v>
+        <v>7088591</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
